--- a/public/RTMify_Requirements_Tracking_Template.xlsx
+++ b/public/RTMify_Requirements_Tracking_Template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="133">
   <si>
     <t>RTMify — Requirements Tracking Template</t>
   </si>
@@ -406,7 +406,7 @@
     <t>User Need iD</t>
   </si>
   <si>
-    <t>Test Group ID</t>
+    <t>Test Group IDs</t>
   </si>
   <si>
     <t>Lifecycle Status</t>
@@ -436,13 +436,16 @@
     <t>The system SHALL NOT be broken</t>
   </si>
   <si>
-    <t>TG-001</t>
+    <t>TG-001, TG-002</t>
   </si>
   <si>
     <t>Draft</t>
   </si>
   <si>
     <t>wip</t>
+  </si>
+  <si>
+    <t>Test Group ID</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -452,6 +455,9 @@
   </si>
   <si>
     <t>Test Method</t>
+  </si>
+  <si>
+    <t>TG-001</t>
   </si>
   <si>
     <t>T-001</t>
@@ -983,7 +989,9 @@
     <xf borderId="0" fillId="21" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="21" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="21" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -33404,7 +33412,7 @@
       <c r="D1" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="50" t="s">
         <v>90</v>
       </c>
       <c r="F1" s="49" t="s">
@@ -33470,7 +33478,7 @@
       <c r="D3" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="61" t="s">
         <v>100</v>
       </c>
       <c r="F3" s="60" t="s">
@@ -33488,7 +33496,7 @@
       <c r="B4" s="54"/>
       <c r="C4" s="55"/>
       <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
+      <c r="E4" s="54"/>
       <c r="F4" s="55"/>
       <c r="G4" s="54"/>
     </row>
@@ -33496,7 +33504,7 @@
       <c r="B5" s="54"/>
       <c r="C5" s="55"/>
       <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
+      <c r="E5" s="54"/>
       <c r="F5" s="55"/>
       <c r="G5" s="54"/>
     </row>
@@ -33504,7 +33512,7 @@
       <c r="B6" s="54"/>
       <c r="C6" s="55"/>
       <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
+      <c r="E6" s="54"/>
       <c r="F6" s="55"/>
       <c r="G6" s="54"/>
     </row>
@@ -33512,7 +33520,7 @@
       <c r="B7" s="54"/>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
+      <c r="E7" s="54"/>
       <c r="F7" s="55"/>
       <c r="G7" s="54"/>
     </row>
@@ -33520,7 +33528,7 @@
       <c r="B8" s="54"/>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
+      <c r="E8" s="54"/>
       <c r="F8" s="55"/>
       <c r="G8" s="54"/>
     </row>
@@ -33528,7 +33536,7 @@
       <c r="B9" s="54"/>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
+      <c r="E9" s="54"/>
       <c r="F9" s="55"/>
       <c r="G9" s="54"/>
     </row>
@@ -33536,7 +33544,7 @@
       <c r="B10" s="54"/>
       <c r="C10" s="55"/>
       <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="E10" s="54"/>
       <c r="F10" s="55"/>
       <c r="G10" s="54"/>
     </row>
@@ -33544,7 +33552,7 @@
       <c r="B11" s="54"/>
       <c r="C11" s="55"/>
       <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
+      <c r="E11" s="54"/>
       <c r="F11" s="55"/>
       <c r="G11" s="54"/>
     </row>
@@ -33552,7 +33560,7 @@
       <c r="B12" s="54"/>
       <c r="C12" s="55"/>
       <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
+      <c r="E12" s="54"/>
       <c r="F12" s="55"/>
       <c r="G12" s="54"/>
     </row>
@@ -33560,7 +33568,7 @@
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
       <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
+      <c r="E13" s="54"/>
       <c r="F13" s="55"/>
       <c r="G13" s="54"/>
     </row>
@@ -33568,7 +33576,7 @@
       <c r="B14" s="54"/>
       <c r="C14" s="55"/>
       <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
+      <c r="E14" s="54"/>
       <c r="F14" s="55"/>
       <c r="G14" s="54"/>
     </row>
@@ -33576,7 +33584,7 @@
       <c r="B15" s="54"/>
       <c r="C15" s="55"/>
       <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
+      <c r="E15" s="54"/>
       <c r="F15" s="55"/>
       <c r="G15" s="54"/>
     </row>
@@ -33584,7 +33592,7 @@
       <c r="B16" s="54"/>
       <c r="C16" s="55"/>
       <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
+      <c r="E16" s="54"/>
       <c r="F16" s="55"/>
       <c r="G16" s="54"/>
     </row>
@@ -33592,7 +33600,7 @@
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
       <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
+      <c r="E17" s="54"/>
       <c r="F17" s="55"/>
       <c r="G17" s="54"/>
     </row>
@@ -33600,7 +33608,7 @@
       <c r="B18" s="54"/>
       <c r="C18" s="55"/>
       <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
+      <c r="E18" s="54"/>
       <c r="F18" s="55"/>
       <c r="G18" s="54"/>
     </row>
@@ -33608,7 +33616,7 @@
       <c r="B19" s="54"/>
       <c r="C19" s="55"/>
       <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
+      <c r="E19" s="54"/>
       <c r="F19" s="55"/>
       <c r="G19" s="54"/>
     </row>
@@ -33616,7 +33624,7 @@
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
       <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
+      <c r="E20" s="54"/>
       <c r="F20" s="55"/>
       <c r="G20" s="54"/>
     </row>
@@ -33624,7 +33632,7 @@
       <c r="B21" s="54"/>
       <c r="C21" s="55"/>
       <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
+      <c r="E21" s="54"/>
       <c r="F21" s="55"/>
       <c r="G21" s="54"/>
     </row>
@@ -33632,7 +33640,7 @@
       <c r="B22" s="54"/>
       <c r="C22" s="55"/>
       <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
+      <c r="E22" s="54"/>
       <c r="F22" s="55"/>
       <c r="G22" s="54"/>
     </row>
@@ -33640,7 +33648,7 @@
       <c r="B23" s="54"/>
       <c r="C23" s="55"/>
       <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
+      <c r="E23" s="54"/>
       <c r="F23" s="55"/>
       <c r="G23" s="54"/>
     </row>
@@ -33648,7 +33656,7 @@
       <c r="B24" s="54"/>
       <c r="C24" s="55"/>
       <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
+      <c r="E24" s="54"/>
       <c r="F24" s="55"/>
       <c r="G24" s="54"/>
     </row>
@@ -33656,7 +33664,7 @@
       <c r="B25" s="54"/>
       <c r="C25" s="55"/>
       <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
+      <c r="E25" s="54"/>
       <c r="F25" s="55"/>
       <c r="G25" s="54"/>
     </row>
@@ -33664,7 +33672,7 @@
       <c r="B26" s="54"/>
       <c r="C26" s="55"/>
       <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
+      <c r="E26" s="54"/>
       <c r="F26" s="55"/>
       <c r="G26" s="54"/>
     </row>
@@ -33672,7 +33680,7 @@
       <c r="B27" s="54"/>
       <c r="C27" s="55"/>
       <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
+      <c r="E27" s="54"/>
       <c r="F27" s="55"/>
       <c r="G27" s="54"/>
     </row>
@@ -33680,7 +33688,7 @@
       <c r="B28" s="54"/>
       <c r="C28" s="55"/>
       <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
+      <c r="E28" s="54"/>
       <c r="F28" s="55"/>
       <c r="G28" s="54"/>
     </row>
@@ -33688,7 +33696,7 @@
       <c r="B29" s="54"/>
       <c r="C29" s="55"/>
       <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
+      <c r="E29" s="54"/>
       <c r="F29" s="55"/>
       <c r="G29" s="54"/>
     </row>
@@ -33696,7 +33704,7 @@
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
       <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
+      <c r="E30" s="54"/>
       <c r="F30" s="55"/>
       <c r="G30" s="54"/>
     </row>
@@ -33704,7 +33712,7 @@
       <c r="B31" s="54"/>
       <c r="C31" s="55"/>
       <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
+      <c r="E31" s="54"/>
       <c r="F31" s="55"/>
       <c r="G31" s="54"/>
     </row>
@@ -33712,7 +33720,7 @@
       <c r="B32" s="54"/>
       <c r="C32" s="55"/>
       <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
+      <c r="E32" s="54"/>
       <c r="F32" s="55"/>
       <c r="G32" s="54"/>
     </row>
@@ -33720,7 +33728,7 @@
       <c r="B33" s="54"/>
       <c r="C33" s="55"/>
       <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
+      <c r="E33" s="54"/>
       <c r="F33" s="55"/>
       <c r="G33" s="54"/>
     </row>
@@ -33728,7 +33736,7 @@
       <c r="B34" s="54"/>
       <c r="C34" s="55"/>
       <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
+      <c r="E34" s="54"/>
       <c r="F34" s="55"/>
       <c r="G34" s="54"/>
     </row>
@@ -33736,7 +33744,7 @@
       <c r="B35" s="54"/>
       <c r="C35" s="55"/>
       <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
+      <c r="E35" s="54"/>
       <c r="F35" s="55"/>
       <c r="G35" s="54"/>
     </row>
@@ -33744,7 +33752,7 @@
       <c r="B36" s="54"/>
       <c r="C36" s="55"/>
       <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
+      <c r="E36" s="54"/>
       <c r="F36" s="55"/>
       <c r="G36" s="54"/>
     </row>
@@ -33752,7 +33760,7 @@
       <c r="B37" s="54"/>
       <c r="C37" s="55"/>
       <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
+      <c r="E37" s="54"/>
       <c r="F37" s="55"/>
       <c r="G37" s="54"/>
     </row>
@@ -33760,7 +33768,7 @@
       <c r="B38" s="54"/>
       <c r="C38" s="55"/>
       <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
+      <c r="E38" s="54"/>
       <c r="F38" s="55"/>
       <c r="G38" s="54"/>
     </row>
@@ -33768,7 +33776,7 @@
       <c r="B39" s="54"/>
       <c r="C39" s="55"/>
       <c r="D39" s="55"/>
-      <c r="E39" s="55"/>
+      <c r="E39" s="54"/>
       <c r="F39" s="55"/>
       <c r="G39" s="54"/>
     </row>
@@ -33776,7 +33784,7 @@
       <c r="B40" s="54"/>
       <c r="C40" s="55"/>
       <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
+      <c r="E40" s="54"/>
       <c r="F40" s="55"/>
       <c r="G40" s="54"/>
     </row>
@@ -33784,7 +33792,7 @@
       <c r="B41" s="54"/>
       <c r="C41" s="55"/>
       <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
+      <c r="E41" s="54"/>
       <c r="F41" s="55"/>
       <c r="G41" s="54"/>
     </row>
@@ -33792,7 +33800,7 @@
       <c r="B42" s="54"/>
       <c r="C42" s="55"/>
       <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
+      <c r="E42" s="54"/>
       <c r="F42" s="55"/>
       <c r="G42" s="54"/>
     </row>
@@ -33800,7 +33808,7 @@
       <c r="B43" s="54"/>
       <c r="C43" s="55"/>
       <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
+      <c r="E43" s="54"/>
       <c r="F43" s="55"/>
       <c r="G43" s="54"/>
     </row>
@@ -33808,7 +33816,7 @@
       <c r="B44" s="54"/>
       <c r="C44" s="55"/>
       <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
+      <c r="E44" s="54"/>
       <c r="F44" s="55"/>
       <c r="G44" s="54"/>
     </row>
@@ -33816,7 +33824,7 @@
       <c r="B45" s="54"/>
       <c r="C45" s="55"/>
       <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
+      <c r="E45" s="54"/>
       <c r="F45" s="55"/>
       <c r="G45" s="54"/>
     </row>
@@ -33824,7 +33832,7 @@
       <c r="B46" s="54"/>
       <c r="C46" s="55"/>
       <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
+      <c r="E46" s="54"/>
       <c r="F46" s="55"/>
       <c r="G46" s="54"/>
     </row>
@@ -33832,7 +33840,7 @@
       <c r="B47" s="54"/>
       <c r="C47" s="55"/>
       <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
+      <c r="E47" s="54"/>
       <c r="F47" s="55"/>
       <c r="G47" s="54"/>
     </row>
@@ -33840,7 +33848,7 @@
       <c r="B48" s="54"/>
       <c r="C48" s="55"/>
       <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
+      <c r="E48" s="54"/>
       <c r="F48" s="55"/>
       <c r="G48" s="54"/>
     </row>
@@ -33848,7 +33856,7 @@
       <c r="B49" s="54"/>
       <c r="C49" s="55"/>
       <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
+      <c r="E49" s="54"/>
       <c r="F49" s="55"/>
       <c r="G49" s="54"/>
     </row>
@@ -33856,7 +33864,7 @@
       <c r="B50" s="54"/>
       <c r="C50" s="55"/>
       <c r="D50" s="55"/>
-      <c r="E50" s="55"/>
+      <c r="E50" s="54"/>
       <c r="F50" s="55"/>
       <c r="G50" s="54"/>
     </row>
@@ -33864,7 +33872,7 @@
       <c r="B51" s="54"/>
       <c r="C51" s="55"/>
       <c r="D51" s="55"/>
-      <c r="E51" s="55"/>
+      <c r="E51" s="54"/>
       <c r="F51" s="55"/>
       <c r="G51" s="54"/>
     </row>
@@ -33872,7 +33880,7 @@
       <c r="B52" s="54"/>
       <c r="C52" s="55"/>
       <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
+      <c r="E52" s="54"/>
       <c r="F52" s="55"/>
       <c r="G52" s="54"/>
     </row>
@@ -33880,7 +33888,7 @@
       <c r="B53" s="54"/>
       <c r="C53" s="55"/>
       <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
+      <c r="E53" s="54"/>
       <c r="F53" s="55"/>
       <c r="G53" s="54"/>
     </row>
@@ -33888,7 +33896,7 @@
       <c r="B54" s="54"/>
       <c r="C54" s="55"/>
       <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
+      <c r="E54" s="54"/>
       <c r="F54" s="55"/>
       <c r="G54" s="54"/>
     </row>
@@ -33896,7 +33904,7 @@
       <c r="B55" s="54"/>
       <c r="C55" s="55"/>
       <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
+      <c r="E55" s="54"/>
       <c r="F55" s="55"/>
       <c r="G55" s="54"/>
     </row>
@@ -33904,7 +33912,7 @@
       <c r="B56" s="54"/>
       <c r="C56" s="55"/>
       <c r="D56" s="55"/>
-      <c r="E56" s="55"/>
+      <c r="E56" s="54"/>
       <c r="F56" s="55"/>
       <c r="G56" s="54"/>
     </row>
@@ -33912,7 +33920,7 @@
       <c r="B57" s="54"/>
       <c r="C57" s="55"/>
       <c r="D57" s="55"/>
-      <c r="E57" s="55"/>
+      <c r="E57" s="54"/>
       <c r="F57" s="55"/>
       <c r="G57" s="54"/>
     </row>
@@ -33920,7 +33928,7 @@
       <c r="B58" s="54"/>
       <c r="C58" s="55"/>
       <c r="D58" s="55"/>
-      <c r="E58" s="55"/>
+      <c r="E58" s="54"/>
       <c r="F58" s="55"/>
       <c r="G58" s="54"/>
     </row>
@@ -33928,7 +33936,7 @@
       <c r="B59" s="54"/>
       <c r="C59" s="55"/>
       <c r="D59" s="55"/>
-      <c r="E59" s="55"/>
+      <c r="E59" s="54"/>
       <c r="F59" s="55"/>
       <c r="G59" s="54"/>
     </row>
@@ -33936,7 +33944,7 @@
       <c r="B60" s="54"/>
       <c r="C60" s="55"/>
       <c r="D60" s="55"/>
-      <c r="E60" s="55"/>
+      <c r="E60" s="54"/>
       <c r="F60" s="55"/>
       <c r="G60" s="54"/>
     </row>
@@ -33944,7 +33952,7 @@
       <c r="B61" s="54"/>
       <c r="C61" s="55"/>
       <c r="D61" s="55"/>
-      <c r="E61" s="55"/>
+      <c r="E61" s="54"/>
       <c r="F61" s="55"/>
       <c r="G61" s="54"/>
     </row>
@@ -33952,7 +33960,7 @@
       <c r="B62" s="54"/>
       <c r="C62" s="55"/>
       <c r="D62" s="55"/>
-      <c r="E62" s="55"/>
+      <c r="E62" s="54"/>
       <c r="F62" s="55"/>
       <c r="G62" s="54"/>
     </row>
@@ -33960,7 +33968,7 @@
       <c r="B63" s="54"/>
       <c r="C63" s="55"/>
       <c r="D63" s="55"/>
-      <c r="E63" s="55"/>
+      <c r="E63" s="54"/>
       <c r="F63" s="55"/>
       <c r="G63" s="54"/>
     </row>
@@ -33968,7 +33976,7 @@
       <c r="B64" s="54"/>
       <c r="C64" s="55"/>
       <c r="D64" s="55"/>
-      <c r="E64" s="55"/>
+      <c r="E64" s="54"/>
       <c r="F64" s="55"/>
       <c r="G64" s="54"/>
     </row>
@@ -33976,7 +33984,7 @@
       <c r="B65" s="54"/>
       <c r="C65" s="55"/>
       <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
+      <c r="E65" s="54"/>
       <c r="F65" s="55"/>
       <c r="G65" s="54"/>
     </row>
@@ -33984,7 +33992,7 @@
       <c r="B66" s="54"/>
       <c r="C66" s="55"/>
       <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
+      <c r="E66" s="54"/>
       <c r="F66" s="55"/>
       <c r="G66" s="54"/>
     </row>
@@ -33992,7 +34000,7 @@
       <c r="B67" s="54"/>
       <c r="C67" s="55"/>
       <c r="D67" s="55"/>
-      <c r="E67" s="55"/>
+      <c r="E67" s="54"/>
       <c r="F67" s="55"/>
       <c r="G67" s="54"/>
     </row>
@@ -34000,7 +34008,7 @@
       <c r="B68" s="54"/>
       <c r="C68" s="55"/>
       <c r="D68" s="55"/>
-      <c r="E68" s="55"/>
+      <c r="E68" s="54"/>
       <c r="F68" s="55"/>
       <c r="G68" s="54"/>
     </row>
@@ -34008,7 +34016,7 @@
       <c r="B69" s="54"/>
       <c r="C69" s="55"/>
       <c r="D69" s="55"/>
-      <c r="E69" s="55"/>
+      <c r="E69" s="54"/>
       <c r="F69" s="55"/>
       <c r="G69" s="54"/>
     </row>
@@ -34016,7 +34024,7 @@
       <c r="B70" s="54"/>
       <c r="C70" s="55"/>
       <c r="D70" s="55"/>
-      <c r="E70" s="55"/>
+      <c r="E70" s="54"/>
       <c r="F70" s="55"/>
       <c r="G70" s="54"/>
     </row>
@@ -34024,7 +34032,7 @@
       <c r="B71" s="54"/>
       <c r="C71" s="55"/>
       <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
+      <c r="E71" s="54"/>
       <c r="F71" s="55"/>
       <c r="G71" s="54"/>
     </row>
@@ -34032,7 +34040,7 @@
       <c r="B72" s="54"/>
       <c r="C72" s="55"/>
       <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
+      <c r="E72" s="54"/>
       <c r="F72" s="55"/>
       <c r="G72" s="54"/>
     </row>
@@ -34040,7 +34048,7 @@
       <c r="B73" s="54"/>
       <c r="C73" s="55"/>
       <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
+      <c r="E73" s="54"/>
       <c r="F73" s="55"/>
       <c r="G73" s="54"/>
     </row>
@@ -34048,7 +34056,7 @@
       <c r="B74" s="54"/>
       <c r="C74" s="55"/>
       <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
+      <c r="E74" s="54"/>
       <c r="F74" s="55"/>
       <c r="G74" s="54"/>
     </row>
@@ -34056,7 +34064,7 @@
       <c r="B75" s="54"/>
       <c r="C75" s="55"/>
       <c r="D75" s="55"/>
-      <c r="E75" s="55"/>
+      <c r="E75" s="54"/>
       <c r="F75" s="55"/>
       <c r="G75" s="54"/>
     </row>
@@ -34064,7 +34072,7 @@
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
       <c r="D76" s="55"/>
-      <c r="E76" s="55"/>
+      <c r="E76" s="54"/>
       <c r="F76" s="55"/>
       <c r="G76" s="54"/>
     </row>
@@ -34072,7 +34080,7 @@
       <c r="B77" s="54"/>
       <c r="C77" s="55"/>
       <c r="D77" s="55"/>
-      <c r="E77" s="55"/>
+      <c r="E77" s="54"/>
       <c r="F77" s="55"/>
       <c r="G77" s="54"/>
     </row>
@@ -34080,7 +34088,7 @@
       <c r="B78" s="54"/>
       <c r="C78" s="55"/>
       <c r="D78" s="55"/>
-      <c r="E78" s="55"/>
+      <c r="E78" s="54"/>
       <c r="F78" s="55"/>
       <c r="G78" s="54"/>
     </row>
@@ -34088,7 +34096,7 @@
       <c r="B79" s="54"/>
       <c r="C79" s="55"/>
       <c r="D79" s="55"/>
-      <c r="E79" s="55"/>
+      <c r="E79" s="54"/>
       <c r="F79" s="55"/>
       <c r="G79" s="54"/>
     </row>
@@ -34096,7 +34104,7 @@
       <c r="B80" s="54"/>
       <c r="C80" s="55"/>
       <c r="D80" s="55"/>
-      <c r="E80" s="55"/>
+      <c r="E80" s="54"/>
       <c r="F80" s="55"/>
       <c r="G80" s="54"/>
     </row>
@@ -34104,7 +34112,7 @@
       <c r="B81" s="54"/>
       <c r="C81" s="55"/>
       <c r="D81" s="55"/>
-      <c r="E81" s="55"/>
+      <c r="E81" s="54"/>
       <c r="F81" s="55"/>
       <c r="G81" s="54"/>
     </row>
@@ -34112,7 +34120,7 @@
       <c r="B82" s="54"/>
       <c r="C82" s="55"/>
       <c r="D82" s="55"/>
-      <c r="E82" s="55"/>
+      <c r="E82" s="54"/>
       <c r="F82" s="55"/>
       <c r="G82" s="54"/>
     </row>
@@ -34120,7 +34128,7 @@
       <c r="B83" s="54"/>
       <c r="C83" s="55"/>
       <c r="D83" s="55"/>
-      <c r="E83" s="55"/>
+      <c r="E83" s="54"/>
       <c r="F83" s="55"/>
       <c r="G83" s="54"/>
     </row>
@@ -34128,7 +34136,7 @@
       <c r="B84" s="54"/>
       <c r="C84" s="55"/>
       <c r="D84" s="55"/>
-      <c r="E84" s="55"/>
+      <c r="E84" s="54"/>
       <c r="F84" s="55"/>
       <c r="G84" s="54"/>
     </row>
@@ -34136,7 +34144,7 @@
       <c r="B85" s="54"/>
       <c r="C85" s="55"/>
       <c r="D85" s="55"/>
-      <c r="E85" s="55"/>
+      <c r="E85" s="54"/>
       <c r="F85" s="55"/>
       <c r="G85" s="54"/>
     </row>
@@ -34144,7 +34152,7 @@
       <c r="B86" s="54"/>
       <c r="C86" s="55"/>
       <c r="D86" s="55"/>
-      <c r="E86" s="55"/>
+      <c r="E86" s="54"/>
       <c r="F86" s="55"/>
       <c r="G86" s="54"/>
     </row>
@@ -34152,7 +34160,7 @@
       <c r="B87" s="54"/>
       <c r="C87" s="55"/>
       <c r="D87" s="55"/>
-      <c r="E87" s="55"/>
+      <c r="E87" s="54"/>
       <c r="F87" s="55"/>
       <c r="G87" s="54"/>
     </row>
@@ -34160,7 +34168,7 @@
       <c r="B88" s="54"/>
       <c r="C88" s="55"/>
       <c r="D88" s="55"/>
-      <c r="E88" s="55"/>
+      <c r="E88" s="54"/>
       <c r="F88" s="55"/>
       <c r="G88" s="54"/>
     </row>
@@ -34168,7 +34176,7 @@
       <c r="B89" s="54"/>
       <c r="C89" s="55"/>
       <c r="D89" s="55"/>
-      <c r="E89" s="55"/>
+      <c r="E89" s="54"/>
       <c r="F89" s="55"/>
       <c r="G89" s="54"/>
     </row>
@@ -34176,7 +34184,7 @@
       <c r="B90" s="54"/>
       <c r="C90" s="55"/>
       <c r="D90" s="55"/>
-      <c r="E90" s="55"/>
+      <c r="E90" s="54"/>
       <c r="F90" s="55"/>
       <c r="G90" s="54"/>
     </row>
@@ -34184,7 +34192,7 @@
       <c r="B91" s="54"/>
       <c r="C91" s="55"/>
       <c r="D91" s="55"/>
-      <c r="E91" s="55"/>
+      <c r="E91" s="54"/>
       <c r="F91" s="55"/>
       <c r="G91" s="54"/>
     </row>
@@ -34192,7 +34200,7 @@
       <c r="B92" s="54"/>
       <c r="C92" s="55"/>
       <c r="D92" s="55"/>
-      <c r="E92" s="55"/>
+      <c r="E92" s="54"/>
       <c r="F92" s="55"/>
       <c r="G92" s="54"/>
     </row>
@@ -34200,7 +34208,7 @@
       <c r="B93" s="54"/>
       <c r="C93" s="55"/>
       <c r="D93" s="55"/>
-      <c r="E93" s="55"/>
+      <c r="E93" s="54"/>
       <c r="F93" s="55"/>
       <c r="G93" s="54"/>
     </row>
@@ -34208,7 +34216,7 @@
       <c r="B94" s="54"/>
       <c r="C94" s="55"/>
       <c r="D94" s="55"/>
-      <c r="E94" s="55"/>
+      <c r="E94" s="54"/>
       <c r="F94" s="55"/>
       <c r="G94" s="54"/>
     </row>
@@ -34216,7 +34224,7 @@
       <c r="B95" s="54"/>
       <c r="C95" s="55"/>
       <c r="D95" s="55"/>
-      <c r="E95" s="55"/>
+      <c r="E95" s="54"/>
       <c r="F95" s="55"/>
       <c r="G95" s="54"/>
     </row>
@@ -34224,7 +34232,7 @@
       <c r="B96" s="54"/>
       <c r="C96" s="55"/>
       <c r="D96" s="55"/>
-      <c r="E96" s="55"/>
+      <c r="E96" s="54"/>
       <c r="F96" s="55"/>
       <c r="G96" s="54"/>
     </row>
@@ -34232,7 +34240,7 @@
       <c r="B97" s="54"/>
       <c r="C97" s="55"/>
       <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
+      <c r="E97" s="54"/>
       <c r="F97" s="55"/>
       <c r="G97" s="54"/>
     </row>
@@ -34240,7 +34248,7 @@
       <c r="B98" s="54"/>
       <c r="C98" s="55"/>
       <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
+      <c r="E98" s="54"/>
       <c r="F98" s="55"/>
       <c r="G98" s="54"/>
     </row>
@@ -34248,7 +34256,7 @@
       <c r="B99" s="54"/>
       <c r="C99" s="55"/>
       <c r="D99" s="55"/>
-      <c r="E99" s="55"/>
+      <c r="E99" s="54"/>
       <c r="F99" s="55"/>
       <c r="G99" s="54"/>
     </row>
@@ -34256,7 +34264,7 @@
       <c r="B100" s="54"/>
       <c r="C100" s="55"/>
       <c r="D100" s="55"/>
-      <c r="E100" s="55"/>
+      <c r="E100" s="54"/>
       <c r="F100" s="55"/>
       <c r="G100" s="54"/>
     </row>
@@ -34264,7 +34272,7 @@
       <c r="B101" s="54"/>
       <c r="C101" s="55"/>
       <c r="D101" s="55"/>
-      <c r="E101" s="55"/>
+      <c r="E101" s="54"/>
       <c r="F101" s="55"/>
       <c r="G101" s="54"/>
     </row>
@@ -34272,7 +34280,7 @@
       <c r="B102" s="54"/>
       <c r="C102" s="55"/>
       <c r="D102" s="55"/>
-      <c r="E102" s="55"/>
+      <c r="E102" s="54"/>
       <c r="F102" s="55"/>
       <c r="G102" s="54"/>
     </row>
@@ -34280,7 +34288,7 @@
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
       <c r="D103" s="55"/>
-      <c r="E103" s="55"/>
+      <c r="E103" s="54"/>
       <c r="F103" s="55"/>
       <c r="G103" s="54"/>
     </row>
@@ -34288,7 +34296,7 @@
       <c r="B104" s="54"/>
       <c r="C104" s="55"/>
       <c r="D104" s="55"/>
-      <c r="E104" s="55"/>
+      <c r="E104" s="54"/>
       <c r="F104" s="55"/>
       <c r="G104" s="54"/>
     </row>
@@ -34296,7 +34304,7 @@
       <c r="B105" s="54"/>
       <c r="C105" s="55"/>
       <c r="D105" s="55"/>
-      <c r="E105" s="55"/>
+      <c r="E105" s="54"/>
       <c r="F105" s="55"/>
       <c r="G105" s="54"/>
     </row>
@@ -34304,7 +34312,7 @@
       <c r="B106" s="54"/>
       <c r="C106" s="55"/>
       <c r="D106" s="55"/>
-      <c r="E106" s="55"/>
+      <c r="E106" s="54"/>
       <c r="F106" s="55"/>
       <c r="G106" s="54"/>
     </row>
@@ -34312,7 +34320,7 @@
       <c r="B107" s="54"/>
       <c r="C107" s="55"/>
       <c r="D107" s="55"/>
-      <c r="E107" s="55"/>
+      <c r="E107" s="54"/>
       <c r="F107" s="55"/>
       <c r="G107" s="54"/>
     </row>
@@ -34320,7 +34328,7 @@
       <c r="B108" s="54"/>
       <c r="C108" s="55"/>
       <c r="D108" s="55"/>
-      <c r="E108" s="55"/>
+      <c r="E108" s="54"/>
       <c r="F108" s="55"/>
       <c r="G108" s="54"/>
     </row>
@@ -34328,7 +34336,7 @@
       <c r="B109" s="54"/>
       <c r="C109" s="55"/>
       <c r="D109" s="55"/>
-      <c r="E109" s="55"/>
+      <c r="E109" s="54"/>
       <c r="F109" s="55"/>
       <c r="G109" s="54"/>
     </row>
@@ -34336,7 +34344,7 @@
       <c r="B110" s="54"/>
       <c r="C110" s="55"/>
       <c r="D110" s="55"/>
-      <c r="E110" s="55"/>
+      <c r="E110" s="54"/>
       <c r="F110" s="55"/>
       <c r="G110" s="54"/>
     </row>
@@ -34344,7 +34352,7 @@
       <c r="B111" s="54"/>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
-      <c r="E111" s="55"/>
+      <c r="E111" s="54"/>
       <c r="F111" s="55"/>
       <c r="G111" s="54"/>
     </row>
@@ -34352,7 +34360,7 @@
       <c r="B112" s="54"/>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="55"/>
+      <c r="E112" s="54"/>
       <c r="F112" s="55"/>
       <c r="G112" s="54"/>
     </row>
@@ -34360,7 +34368,7 @@
       <c r="B113" s="54"/>
       <c r="C113" s="55"/>
       <c r="D113" s="55"/>
-      <c r="E113" s="55"/>
+      <c r="E113" s="54"/>
       <c r="F113" s="55"/>
       <c r="G113" s="54"/>
     </row>
@@ -34368,7 +34376,7 @@
       <c r="B114" s="54"/>
       <c r="C114" s="55"/>
       <c r="D114" s="55"/>
-      <c r="E114" s="55"/>
+      <c r="E114" s="54"/>
       <c r="F114" s="55"/>
       <c r="G114" s="54"/>
     </row>
@@ -34376,7 +34384,7 @@
       <c r="B115" s="54"/>
       <c r="C115" s="55"/>
       <c r="D115" s="55"/>
-      <c r="E115" s="55"/>
+      <c r="E115" s="54"/>
       <c r="F115" s="55"/>
       <c r="G115" s="54"/>
     </row>
@@ -34384,7 +34392,7 @@
       <c r="B116" s="54"/>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="55"/>
+      <c r="E116" s="54"/>
       <c r="F116" s="55"/>
       <c r="G116" s="54"/>
     </row>
@@ -34392,7 +34400,7 @@
       <c r="B117" s="54"/>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
-      <c r="E117" s="55"/>
+      <c r="E117" s="54"/>
       <c r="F117" s="55"/>
       <c r="G117" s="54"/>
     </row>
@@ -34400,7 +34408,7 @@
       <c r="B118" s="54"/>
       <c r="C118" s="55"/>
       <c r="D118" s="55"/>
-      <c r="E118" s="55"/>
+      <c r="E118" s="54"/>
       <c r="F118" s="55"/>
       <c r="G118" s="54"/>
     </row>
@@ -34408,7 +34416,7 @@
       <c r="B119" s="54"/>
       <c r="C119" s="55"/>
       <c r="D119" s="55"/>
-      <c r="E119" s="55"/>
+      <c r="E119" s="54"/>
       <c r="F119" s="55"/>
       <c r="G119" s="54"/>
     </row>
@@ -34416,7 +34424,7 @@
       <c r="B120" s="54"/>
       <c r="C120" s="55"/>
       <c r="D120" s="55"/>
-      <c r="E120" s="55"/>
+      <c r="E120" s="54"/>
       <c r="F120" s="55"/>
       <c r="G120" s="54"/>
     </row>
@@ -34424,7 +34432,7 @@
       <c r="B121" s="54"/>
       <c r="C121" s="55"/>
       <c r="D121" s="55"/>
-      <c r="E121" s="55"/>
+      <c r="E121" s="54"/>
       <c r="F121" s="55"/>
       <c r="G121" s="54"/>
     </row>
@@ -34432,7 +34440,7 @@
       <c r="B122" s="54"/>
       <c r="C122" s="55"/>
       <c r="D122" s="55"/>
-      <c r="E122" s="55"/>
+      <c r="E122" s="54"/>
       <c r="F122" s="55"/>
       <c r="G122" s="54"/>
     </row>
@@ -34440,7 +34448,7 @@
       <c r="B123" s="54"/>
       <c r="C123" s="55"/>
       <c r="D123" s="55"/>
-      <c r="E123" s="55"/>
+      <c r="E123" s="54"/>
       <c r="F123" s="55"/>
       <c r="G123" s="54"/>
     </row>
@@ -34448,7 +34456,7 @@
       <c r="B124" s="54"/>
       <c r="C124" s="55"/>
       <c r="D124" s="55"/>
-      <c r="E124" s="55"/>
+      <c r="E124" s="54"/>
       <c r="F124" s="55"/>
       <c r="G124" s="54"/>
     </row>
@@ -34456,7 +34464,7 @@
       <c r="B125" s="54"/>
       <c r="C125" s="55"/>
       <c r="D125" s="55"/>
-      <c r="E125" s="55"/>
+      <c r="E125" s="54"/>
       <c r="F125" s="55"/>
       <c r="G125" s="54"/>
     </row>
@@ -34464,7 +34472,7 @@
       <c r="B126" s="54"/>
       <c r="C126" s="55"/>
       <c r="D126" s="55"/>
-      <c r="E126" s="55"/>
+      <c r="E126" s="54"/>
       <c r="F126" s="55"/>
       <c r="G126" s="54"/>
     </row>
@@ -34472,7 +34480,7 @@
       <c r="B127" s="54"/>
       <c r="C127" s="55"/>
       <c r="D127" s="55"/>
-      <c r="E127" s="55"/>
+      <c r="E127" s="54"/>
       <c r="F127" s="55"/>
       <c r="G127" s="54"/>
     </row>
@@ -34480,7 +34488,7 @@
       <c r="B128" s="54"/>
       <c r="C128" s="55"/>
       <c r="D128" s="55"/>
-      <c r="E128" s="55"/>
+      <c r="E128" s="54"/>
       <c r="F128" s="55"/>
       <c r="G128" s="54"/>
     </row>
@@ -34488,7 +34496,7 @@
       <c r="B129" s="54"/>
       <c r="C129" s="55"/>
       <c r="D129" s="55"/>
-      <c r="E129" s="55"/>
+      <c r="E129" s="54"/>
       <c r="F129" s="55"/>
       <c r="G129" s="54"/>
     </row>
@@ -34496,7 +34504,7 @@
       <c r="B130" s="54"/>
       <c r="C130" s="55"/>
       <c r="D130" s="55"/>
-      <c r="E130" s="55"/>
+      <c r="E130" s="54"/>
       <c r="F130" s="55"/>
       <c r="G130" s="54"/>
     </row>
@@ -34504,7 +34512,7 @@
       <c r="B131" s="54"/>
       <c r="C131" s="55"/>
       <c r="D131" s="55"/>
-      <c r="E131" s="55"/>
+      <c r="E131" s="54"/>
       <c r="F131" s="55"/>
       <c r="G131" s="54"/>
     </row>
@@ -34512,7 +34520,7 @@
       <c r="B132" s="54"/>
       <c r="C132" s="55"/>
       <c r="D132" s="55"/>
-      <c r="E132" s="55"/>
+      <c r="E132" s="54"/>
       <c r="F132" s="55"/>
       <c r="G132" s="54"/>
     </row>
@@ -34520,7 +34528,7 @@
       <c r="B133" s="54"/>
       <c r="C133" s="55"/>
       <c r="D133" s="55"/>
-      <c r="E133" s="55"/>
+      <c r="E133" s="54"/>
       <c r="F133" s="55"/>
       <c r="G133" s="54"/>
     </row>
@@ -34528,7 +34536,7 @@
       <c r="B134" s="54"/>
       <c r="C134" s="55"/>
       <c r="D134" s="55"/>
-      <c r="E134" s="55"/>
+      <c r="E134" s="54"/>
       <c r="F134" s="55"/>
       <c r="G134" s="54"/>
     </row>
@@ -34536,7 +34544,7 @@
       <c r="B135" s="54"/>
       <c r="C135" s="55"/>
       <c r="D135" s="55"/>
-      <c r="E135" s="55"/>
+      <c r="E135" s="54"/>
       <c r="F135" s="55"/>
       <c r="G135" s="54"/>
     </row>
@@ -34544,7 +34552,7 @@
       <c r="B136" s="54"/>
       <c r="C136" s="55"/>
       <c r="D136" s="55"/>
-      <c r="E136" s="55"/>
+      <c r="E136" s="54"/>
       <c r="F136" s="55"/>
       <c r="G136" s="54"/>
     </row>
@@ -34552,7 +34560,7 @@
       <c r="B137" s="54"/>
       <c r="C137" s="55"/>
       <c r="D137" s="55"/>
-      <c r="E137" s="55"/>
+      <c r="E137" s="54"/>
       <c r="F137" s="55"/>
       <c r="G137" s="54"/>
     </row>
@@ -34560,7 +34568,7 @@
       <c r="B138" s="54"/>
       <c r="C138" s="55"/>
       <c r="D138" s="55"/>
-      <c r="E138" s="55"/>
+      <c r="E138" s="54"/>
       <c r="F138" s="55"/>
       <c r="G138" s="54"/>
     </row>
@@ -34568,7 +34576,7 @@
       <c r="B139" s="54"/>
       <c r="C139" s="55"/>
       <c r="D139" s="55"/>
-      <c r="E139" s="55"/>
+      <c r="E139" s="54"/>
       <c r="F139" s="55"/>
       <c r="G139" s="54"/>
     </row>
@@ -34576,7 +34584,7 @@
       <c r="B140" s="54"/>
       <c r="C140" s="55"/>
       <c r="D140" s="55"/>
-      <c r="E140" s="55"/>
+      <c r="E140" s="54"/>
       <c r="F140" s="55"/>
       <c r="G140" s="54"/>
     </row>
@@ -34584,7 +34592,7 @@
       <c r="B141" s="54"/>
       <c r="C141" s="55"/>
       <c r="D141" s="55"/>
-      <c r="E141" s="55"/>
+      <c r="E141" s="54"/>
       <c r="F141" s="55"/>
       <c r="G141" s="54"/>
     </row>
@@ -34592,7 +34600,7 @@
       <c r="B142" s="54"/>
       <c r="C142" s="55"/>
       <c r="D142" s="55"/>
-      <c r="E142" s="55"/>
+      <c r="E142" s="54"/>
       <c r="F142" s="55"/>
       <c r="G142" s="54"/>
     </row>
@@ -34600,7 +34608,7 @@
       <c r="B143" s="54"/>
       <c r="C143" s="55"/>
       <c r="D143" s="55"/>
-      <c r="E143" s="55"/>
+      <c r="E143" s="54"/>
       <c r="F143" s="55"/>
       <c r="G143" s="54"/>
     </row>
@@ -34608,7 +34616,7 @@
       <c r="B144" s="54"/>
       <c r="C144" s="55"/>
       <c r="D144" s="55"/>
-      <c r="E144" s="55"/>
+      <c r="E144" s="54"/>
       <c r="F144" s="55"/>
       <c r="G144" s="54"/>
     </row>
@@ -34616,7 +34624,7 @@
       <c r="B145" s="54"/>
       <c r="C145" s="55"/>
       <c r="D145" s="55"/>
-      <c r="E145" s="55"/>
+      <c r="E145" s="54"/>
       <c r="F145" s="55"/>
       <c r="G145" s="54"/>
     </row>
@@ -34624,7 +34632,7 @@
       <c r="B146" s="54"/>
       <c r="C146" s="55"/>
       <c r="D146" s="55"/>
-      <c r="E146" s="55"/>
+      <c r="E146" s="54"/>
       <c r="F146" s="55"/>
       <c r="G146" s="54"/>
     </row>
@@ -34632,7 +34640,7 @@
       <c r="B147" s="54"/>
       <c r="C147" s="55"/>
       <c r="D147" s="55"/>
-      <c r="E147" s="55"/>
+      <c r="E147" s="54"/>
       <c r="F147" s="55"/>
       <c r="G147" s="54"/>
     </row>
@@ -34640,7 +34648,7 @@
       <c r="B148" s="54"/>
       <c r="C148" s="55"/>
       <c r="D148" s="55"/>
-      <c r="E148" s="55"/>
+      <c r="E148" s="54"/>
       <c r="F148" s="55"/>
       <c r="G148" s="54"/>
     </row>
@@ -34648,7 +34656,7 @@
       <c r="B149" s="54"/>
       <c r="C149" s="55"/>
       <c r="D149" s="55"/>
-      <c r="E149" s="55"/>
+      <c r="E149" s="54"/>
       <c r="F149" s="55"/>
       <c r="G149" s="54"/>
     </row>
@@ -34656,7 +34664,7 @@
       <c r="B150" s="54"/>
       <c r="C150" s="55"/>
       <c r="D150" s="55"/>
-      <c r="E150" s="55"/>
+      <c r="E150" s="54"/>
       <c r="F150" s="55"/>
       <c r="G150" s="54"/>
     </row>
@@ -34664,7 +34672,7 @@
       <c r="B151" s="54"/>
       <c r="C151" s="55"/>
       <c r="D151" s="55"/>
-      <c r="E151" s="55"/>
+      <c r="E151" s="54"/>
       <c r="F151" s="55"/>
       <c r="G151" s="54"/>
     </row>
@@ -34672,7 +34680,7 @@
       <c r="B152" s="54"/>
       <c r="C152" s="55"/>
       <c r="D152" s="55"/>
-      <c r="E152" s="55"/>
+      <c r="E152" s="54"/>
       <c r="F152" s="55"/>
       <c r="G152" s="54"/>
     </row>
@@ -34680,7 +34688,7 @@
       <c r="B153" s="54"/>
       <c r="C153" s="55"/>
       <c r="D153" s="55"/>
-      <c r="E153" s="55"/>
+      <c r="E153" s="54"/>
       <c r="F153" s="55"/>
       <c r="G153" s="54"/>
     </row>
@@ -34688,7 +34696,7 @@
       <c r="B154" s="54"/>
       <c r="C154" s="55"/>
       <c r="D154" s="55"/>
-      <c r="E154" s="55"/>
+      <c r="E154" s="54"/>
       <c r="F154" s="55"/>
       <c r="G154" s="54"/>
     </row>
@@ -34696,7 +34704,7 @@
       <c r="B155" s="54"/>
       <c r="C155" s="55"/>
       <c r="D155" s="55"/>
-      <c r="E155" s="55"/>
+      <c r="E155" s="54"/>
       <c r="F155" s="55"/>
       <c r="G155" s="54"/>
     </row>
@@ -34704,7 +34712,7 @@
       <c r="B156" s="54"/>
       <c r="C156" s="55"/>
       <c r="D156" s="55"/>
-      <c r="E156" s="55"/>
+      <c r="E156" s="54"/>
       <c r="F156" s="55"/>
       <c r="G156" s="54"/>
     </row>
@@ -34712,7 +34720,7 @@
       <c r="B157" s="54"/>
       <c r="C157" s="55"/>
       <c r="D157" s="55"/>
-      <c r="E157" s="55"/>
+      <c r="E157" s="54"/>
       <c r="F157" s="55"/>
       <c r="G157" s="54"/>
     </row>
@@ -34720,7 +34728,7 @@
       <c r="B158" s="54"/>
       <c r="C158" s="55"/>
       <c r="D158" s="55"/>
-      <c r="E158" s="55"/>
+      <c r="E158" s="54"/>
       <c r="F158" s="55"/>
       <c r="G158" s="54"/>
     </row>
@@ -34728,7 +34736,7 @@
       <c r="B159" s="54"/>
       <c r="C159" s="55"/>
       <c r="D159" s="55"/>
-      <c r="E159" s="55"/>
+      <c r="E159" s="54"/>
       <c r="F159" s="55"/>
       <c r="G159" s="54"/>
     </row>
@@ -34736,7 +34744,7 @@
       <c r="B160" s="54"/>
       <c r="C160" s="55"/>
       <c r="D160" s="55"/>
-      <c r="E160" s="55"/>
+      <c r="E160" s="54"/>
       <c r="F160" s="55"/>
       <c r="G160" s="54"/>
     </row>
@@ -34744,7 +34752,7 @@
       <c r="B161" s="54"/>
       <c r="C161" s="55"/>
       <c r="D161" s="55"/>
-      <c r="E161" s="55"/>
+      <c r="E161" s="54"/>
       <c r="F161" s="55"/>
       <c r="G161" s="54"/>
     </row>
@@ -34752,7 +34760,7 @@
       <c r="B162" s="54"/>
       <c r="C162" s="55"/>
       <c r="D162" s="55"/>
-      <c r="E162" s="55"/>
+      <c r="E162" s="54"/>
       <c r="F162" s="55"/>
       <c r="G162" s="54"/>
     </row>
@@ -34760,7 +34768,7 @@
       <c r="B163" s="54"/>
       <c r="C163" s="55"/>
       <c r="D163" s="55"/>
-      <c r="E163" s="55"/>
+      <c r="E163" s="54"/>
       <c r="F163" s="55"/>
       <c r="G163" s="54"/>
     </row>
@@ -34768,7 +34776,7 @@
       <c r="B164" s="54"/>
       <c r="C164" s="55"/>
       <c r="D164" s="55"/>
-      <c r="E164" s="55"/>
+      <c r="E164" s="54"/>
       <c r="F164" s="55"/>
       <c r="G164" s="54"/>
     </row>
@@ -34776,7 +34784,7 @@
       <c r="B165" s="54"/>
       <c r="C165" s="55"/>
       <c r="D165" s="55"/>
-      <c r="E165" s="55"/>
+      <c r="E165" s="54"/>
       <c r="F165" s="55"/>
       <c r="G165" s="54"/>
     </row>
@@ -34784,7 +34792,7 @@
       <c r="B166" s="54"/>
       <c r="C166" s="55"/>
       <c r="D166" s="55"/>
-      <c r="E166" s="55"/>
+      <c r="E166" s="54"/>
       <c r="F166" s="55"/>
       <c r="G166" s="54"/>
     </row>
@@ -34792,7 +34800,7 @@
       <c r="B167" s="54"/>
       <c r="C167" s="55"/>
       <c r="D167" s="55"/>
-      <c r="E167" s="55"/>
+      <c r="E167" s="54"/>
       <c r="F167" s="55"/>
       <c r="G167" s="54"/>
     </row>
@@ -34800,7 +34808,7 @@
       <c r="B168" s="54"/>
       <c r="C168" s="55"/>
       <c r="D168" s="55"/>
-      <c r="E168" s="55"/>
+      <c r="E168" s="54"/>
       <c r="F168" s="55"/>
       <c r="G168" s="54"/>
     </row>
@@ -34808,7 +34816,7 @@
       <c r="B169" s="54"/>
       <c r="C169" s="55"/>
       <c r="D169" s="55"/>
-      <c r="E169" s="55"/>
+      <c r="E169" s="54"/>
       <c r="F169" s="55"/>
       <c r="G169" s="54"/>
     </row>
@@ -34816,7 +34824,7 @@
       <c r="B170" s="54"/>
       <c r="C170" s="55"/>
       <c r="D170" s="55"/>
-      <c r="E170" s="55"/>
+      <c r="E170" s="54"/>
       <c r="F170" s="55"/>
       <c r="G170" s="54"/>
     </row>
@@ -34824,7 +34832,7 @@
       <c r="B171" s="54"/>
       <c r="C171" s="55"/>
       <c r="D171" s="55"/>
-      <c r="E171" s="55"/>
+      <c r="E171" s="54"/>
       <c r="F171" s="55"/>
       <c r="G171" s="54"/>
     </row>
@@ -34832,7 +34840,7 @@
       <c r="B172" s="54"/>
       <c r="C172" s="55"/>
       <c r="D172" s="55"/>
-      <c r="E172" s="55"/>
+      <c r="E172" s="54"/>
       <c r="F172" s="55"/>
       <c r="G172" s="54"/>
     </row>
@@ -34840,7 +34848,7 @@
       <c r="B173" s="54"/>
       <c r="C173" s="55"/>
       <c r="D173" s="55"/>
-      <c r="E173" s="55"/>
+      <c r="E173" s="54"/>
       <c r="F173" s="55"/>
       <c r="G173" s="54"/>
     </row>
@@ -34848,7 +34856,7 @@
       <c r="B174" s="54"/>
       <c r="C174" s="55"/>
       <c r="D174" s="55"/>
-      <c r="E174" s="55"/>
+      <c r="E174" s="54"/>
       <c r="F174" s="55"/>
       <c r="G174" s="54"/>
     </row>
@@ -34856,7 +34864,7 @@
       <c r="B175" s="54"/>
       <c r="C175" s="55"/>
       <c r="D175" s="55"/>
-      <c r="E175" s="55"/>
+      <c r="E175" s="54"/>
       <c r="F175" s="55"/>
       <c r="G175" s="54"/>
     </row>
@@ -34864,7 +34872,7 @@
       <c r="B176" s="54"/>
       <c r="C176" s="55"/>
       <c r="D176" s="55"/>
-      <c r="E176" s="55"/>
+      <c r="E176" s="54"/>
       <c r="F176" s="55"/>
       <c r="G176" s="54"/>
     </row>
@@ -34872,7 +34880,7 @@
       <c r="B177" s="54"/>
       <c r="C177" s="55"/>
       <c r="D177" s="55"/>
-      <c r="E177" s="55"/>
+      <c r="E177" s="54"/>
       <c r="F177" s="55"/>
       <c r="G177" s="54"/>
     </row>
@@ -34880,7 +34888,7 @@
       <c r="B178" s="54"/>
       <c r="C178" s="55"/>
       <c r="D178" s="55"/>
-      <c r="E178" s="55"/>
+      <c r="E178" s="54"/>
       <c r="F178" s="55"/>
       <c r="G178" s="54"/>
     </row>
@@ -34888,7 +34896,7 @@
       <c r="B179" s="54"/>
       <c r="C179" s="55"/>
       <c r="D179" s="55"/>
-      <c r="E179" s="55"/>
+      <c r="E179" s="54"/>
       <c r="F179" s="55"/>
       <c r="G179" s="54"/>
     </row>
@@ -34896,7 +34904,7 @@
       <c r="B180" s="54"/>
       <c r="C180" s="55"/>
       <c r="D180" s="55"/>
-      <c r="E180" s="55"/>
+      <c r="E180" s="54"/>
       <c r="F180" s="55"/>
       <c r="G180" s="54"/>
     </row>
@@ -34904,7 +34912,7 @@
       <c r="B181" s="54"/>
       <c r="C181" s="55"/>
       <c r="D181" s="55"/>
-      <c r="E181" s="55"/>
+      <c r="E181" s="54"/>
       <c r="F181" s="55"/>
       <c r="G181" s="54"/>
     </row>
@@ -34912,7 +34920,7 @@
       <c r="B182" s="54"/>
       <c r="C182" s="55"/>
       <c r="D182" s="55"/>
-      <c r="E182" s="55"/>
+      <c r="E182" s="54"/>
       <c r="F182" s="55"/>
       <c r="G182" s="54"/>
     </row>
@@ -34920,7 +34928,7 @@
       <c r="B183" s="54"/>
       <c r="C183" s="55"/>
       <c r="D183" s="55"/>
-      <c r="E183" s="55"/>
+      <c r="E183" s="54"/>
       <c r="F183" s="55"/>
       <c r="G183" s="54"/>
     </row>
@@ -34928,7 +34936,7 @@
       <c r="B184" s="54"/>
       <c r="C184" s="55"/>
       <c r="D184" s="55"/>
-      <c r="E184" s="55"/>
+      <c r="E184" s="54"/>
       <c r="F184" s="55"/>
       <c r="G184" s="54"/>
     </row>
@@ -34936,7 +34944,7 @@
       <c r="B185" s="54"/>
       <c r="C185" s="55"/>
       <c r="D185" s="55"/>
-      <c r="E185" s="55"/>
+      <c r="E185" s="54"/>
       <c r="F185" s="55"/>
       <c r="G185" s="54"/>
     </row>
@@ -34944,7 +34952,7 @@
       <c r="B186" s="54"/>
       <c r="C186" s="55"/>
       <c r="D186" s="55"/>
-      <c r="E186" s="55"/>
+      <c r="E186" s="54"/>
       <c r="F186" s="55"/>
       <c r="G186" s="54"/>
     </row>
@@ -34952,7 +34960,7 @@
       <c r="B187" s="54"/>
       <c r="C187" s="55"/>
       <c r="D187" s="55"/>
-      <c r="E187" s="55"/>
+      <c r="E187" s="54"/>
       <c r="F187" s="55"/>
       <c r="G187" s="54"/>
     </row>
@@ -34960,7 +34968,7 @@
       <c r="B188" s="54"/>
       <c r="C188" s="55"/>
       <c r="D188" s="55"/>
-      <c r="E188" s="55"/>
+      <c r="E188" s="54"/>
       <c r="F188" s="55"/>
       <c r="G188" s="54"/>
     </row>
@@ -34968,7 +34976,7 @@
       <c r="B189" s="54"/>
       <c r="C189" s="55"/>
       <c r="D189" s="55"/>
-      <c r="E189" s="55"/>
+      <c r="E189" s="54"/>
       <c r="F189" s="55"/>
       <c r="G189" s="54"/>
     </row>
@@ -34976,7 +34984,7 @@
       <c r="B190" s="54"/>
       <c r="C190" s="55"/>
       <c r="D190" s="55"/>
-      <c r="E190" s="55"/>
+      <c r="E190" s="54"/>
       <c r="F190" s="55"/>
       <c r="G190" s="54"/>
     </row>
@@ -34984,7 +34992,7 @@
       <c r="B191" s="54"/>
       <c r="C191" s="55"/>
       <c r="D191" s="55"/>
-      <c r="E191" s="55"/>
+      <c r="E191" s="54"/>
       <c r="F191" s="55"/>
       <c r="G191" s="54"/>
     </row>
@@ -34992,7 +35000,7 @@
       <c r="B192" s="54"/>
       <c r="C192" s="55"/>
       <c r="D192" s="55"/>
-      <c r="E192" s="55"/>
+      <c r="E192" s="54"/>
       <c r="F192" s="55"/>
       <c r="G192" s="54"/>
     </row>
@@ -35000,7 +35008,7 @@
       <c r="B193" s="54"/>
       <c r="C193" s="55"/>
       <c r="D193" s="55"/>
-      <c r="E193" s="55"/>
+      <c r="E193" s="54"/>
       <c r="F193" s="55"/>
       <c r="G193" s="54"/>
     </row>
@@ -35008,7 +35016,7 @@
       <c r="B194" s="54"/>
       <c r="C194" s="55"/>
       <c r="D194" s="55"/>
-      <c r="E194" s="55"/>
+      <c r="E194" s="54"/>
       <c r="F194" s="55"/>
       <c r="G194" s="54"/>
     </row>
@@ -35016,7 +35024,7 @@
       <c r="B195" s="54"/>
       <c r="C195" s="55"/>
       <c r="D195" s="55"/>
-      <c r="E195" s="55"/>
+      <c r="E195" s="54"/>
       <c r="F195" s="55"/>
       <c r="G195" s="54"/>
     </row>
@@ -35024,7 +35032,7 @@
       <c r="B196" s="54"/>
       <c r="C196" s="55"/>
       <c r="D196" s="55"/>
-      <c r="E196" s="55"/>
+      <c r="E196" s="54"/>
       <c r="F196" s="55"/>
       <c r="G196" s="54"/>
     </row>
@@ -35032,7 +35040,7 @@
       <c r="B197" s="54"/>
       <c r="C197" s="55"/>
       <c r="D197" s="55"/>
-      <c r="E197" s="55"/>
+      <c r="E197" s="54"/>
       <c r="F197" s="55"/>
       <c r="G197" s="54"/>
     </row>
@@ -35040,7 +35048,7 @@
       <c r="B198" s="54"/>
       <c r="C198" s="55"/>
       <c r="D198" s="55"/>
-      <c r="E198" s="55"/>
+      <c r="E198" s="54"/>
       <c r="F198" s="55"/>
       <c r="G198" s="54"/>
     </row>
@@ -35048,7 +35056,7 @@
       <c r="B199" s="54"/>
       <c r="C199" s="55"/>
       <c r="D199" s="55"/>
-      <c r="E199" s="55"/>
+      <c r="E199" s="54"/>
       <c r="F199" s="55"/>
       <c r="G199" s="54"/>
     </row>
@@ -35056,7 +35064,7 @@
       <c r="B200" s="54"/>
       <c r="C200" s="55"/>
       <c r="D200" s="55"/>
-      <c r="E200" s="55"/>
+      <c r="E200" s="54"/>
       <c r="F200" s="55"/>
       <c r="G200" s="54"/>
     </row>
@@ -35064,7 +35072,7 @@
       <c r="B201" s="54"/>
       <c r="C201" s="55"/>
       <c r="D201" s="55"/>
-      <c r="E201" s="55"/>
+      <c r="E201" s="54"/>
       <c r="F201" s="55"/>
       <c r="G201" s="54"/>
     </row>
@@ -35072,7 +35080,7 @@
       <c r="B202" s="54"/>
       <c r="C202" s="55"/>
       <c r="D202" s="55"/>
-      <c r="E202" s="55"/>
+      <c r="E202" s="54"/>
       <c r="F202" s="55"/>
       <c r="G202" s="54"/>
     </row>
@@ -35080,7 +35088,7 @@
       <c r="B203" s="54"/>
       <c r="C203" s="55"/>
       <c r="D203" s="55"/>
-      <c r="E203" s="55"/>
+      <c r="E203" s="54"/>
       <c r="F203" s="55"/>
       <c r="G203" s="54"/>
     </row>
@@ -35088,7 +35096,7 @@
       <c r="B204" s="54"/>
       <c r="C204" s="55"/>
       <c r="D204" s="55"/>
-      <c r="E204" s="55"/>
+      <c r="E204" s="54"/>
       <c r="F204" s="55"/>
       <c r="G204" s="54"/>
     </row>
@@ -35096,7 +35104,7 @@
       <c r="B205" s="54"/>
       <c r="C205" s="55"/>
       <c r="D205" s="55"/>
-      <c r="E205" s="55"/>
+      <c r="E205" s="54"/>
       <c r="F205" s="55"/>
       <c r="G205" s="54"/>
     </row>
@@ -35104,7 +35112,7 @@
       <c r="B206" s="54"/>
       <c r="C206" s="55"/>
       <c r="D206" s="55"/>
-      <c r="E206" s="55"/>
+      <c r="E206" s="54"/>
       <c r="F206" s="55"/>
       <c r="G206" s="54"/>
     </row>
@@ -35112,7 +35120,7 @@
       <c r="B207" s="54"/>
       <c r="C207" s="55"/>
       <c r="D207" s="55"/>
-      <c r="E207" s="55"/>
+      <c r="E207" s="54"/>
       <c r="F207" s="55"/>
       <c r="G207" s="54"/>
     </row>
@@ -35120,7 +35128,7 @@
       <c r="B208" s="54"/>
       <c r="C208" s="55"/>
       <c r="D208" s="55"/>
-      <c r="E208" s="55"/>
+      <c r="E208" s="54"/>
       <c r="F208" s="55"/>
       <c r="G208" s="54"/>
     </row>
@@ -35128,7 +35136,7 @@
       <c r="B209" s="54"/>
       <c r="C209" s="55"/>
       <c r="D209" s="55"/>
-      <c r="E209" s="55"/>
+      <c r="E209" s="54"/>
       <c r="F209" s="55"/>
       <c r="G209" s="54"/>
     </row>
@@ -35136,7 +35144,7 @@
       <c r="B210" s="54"/>
       <c r="C210" s="55"/>
       <c r="D210" s="55"/>
-      <c r="E210" s="55"/>
+      <c r="E210" s="54"/>
       <c r="F210" s="55"/>
       <c r="G210" s="54"/>
     </row>
@@ -35144,7 +35152,7 @@
       <c r="B211" s="54"/>
       <c r="C211" s="55"/>
       <c r="D211" s="55"/>
-      <c r="E211" s="55"/>
+      <c r="E211" s="54"/>
       <c r="F211" s="55"/>
       <c r="G211" s="54"/>
     </row>
@@ -35152,7 +35160,7 @@
       <c r="B212" s="54"/>
       <c r="C212" s="55"/>
       <c r="D212" s="55"/>
-      <c r="E212" s="55"/>
+      <c r="E212" s="54"/>
       <c r="F212" s="55"/>
       <c r="G212" s="54"/>
     </row>
@@ -35160,7 +35168,7 @@
       <c r="B213" s="54"/>
       <c r="C213" s="55"/>
       <c r="D213" s="55"/>
-      <c r="E213" s="55"/>
+      <c r="E213" s="54"/>
       <c r="F213" s="55"/>
       <c r="G213" s="54"/>
     </row>
@@ -35168,7 +35176,7 @@
       <c r="B214" s="54"/>
       <c r="C214" s="55"/>
       <c r="D214" s="55"/>
-      <c r="E214" s="55"/>
+      <c r="E214" s="54"/>
       <c r="F214" s="55"/>
       <c r="G214" s="54"/>
     </row>
@@ -35176,7 +35184,7 @@
       <c r="B215" s="54"/>
       <c r="C215" s="55"/>
       <c r="D215" s="55"/>
-      <c r="E215" s="55"/>
+      <c r="E215" s="54"/>
       <c r="F215" s="55"/>
       <c r="G215" s="54"/>
     </row>
@@ -35184,7 +35192,7 @@
       <c r="B216" s="54"/>
       <c r="C216" s="55"/>
       <c r="D216" s="55"/>
-      <c r="E216" s="55"/>
+      <c r="E216" s="54"/>
       <c r="F216" s="55"/>
       <c r="G216" s="54"/>
     </row>
@@ -35192,7 +35200,7 @@
       <c r="B217" s="54"/>
       <c r="C217" s="55"/>
       <c r="D217" s="55"/>
-      <c r="E217" s="55"/>
+      <c r="E217" s="54"/>
       <c r="F217" s="55"/>
       <c r="G217" s="54"/>
     </row>
@@ -35200,7 +35208,7 @@
       <c r="B218" s="54"/>
       <c r="C218" s="55"/>
       <c r="D218" s="55"/>
-      <c r="E218" s="55"/>
+      <c r="E218" s="54"/>
       <c r="F218" s="55"/>
       <c r="G218" s="54"/>
     </row>
@@ -35208,7 +35216,7 @@
       <c r="B219" s="54"/>
       <c r="C219" s="55"/>
       <c r="D219" s="55"/>
-      <c r="E219" s="55"/>
+      <c r="E219" s="54"/>
       <c r="F219" s="55"/>
       <c r="G219" s="54"/>
     </row>
@@ -35216,7 +35224,7 @@
       <c r="B220" s="54"/>
       <c r="C220" s="55"/>
       <c r="D220" s="55"/>
-      <c r="E220" s="55"/>
+      <c r="E220" s="54"/>
       <c r="F220" s="55"/>
       <c r="G220" s="54"/>
     </row>
@@ -35224,7 +35232,7 @@
       <c r="B221" s="54"/>
       <c r="C221" s="55"/>
       <c r="D221" s="55"/>
-      <c r="E221" s="55"/>
+      <c r="E221" s="54"/>
       <c r="F221" s="55"/>
       <c r="G221" s="54"/>
     </row>
@@ -35232,7 +35240,7 @@
       <c r="B222" s="54"/>
       <c r="C222" s="55"/>
       <c r="D222" s="55"/>
-      <c r="E222" s="55"/>
+      <c r="E222" s="54"/>
       <c r="F222" s="55"/>
       <c r="G222" s="54"/>
     </row>
@@ -35240,7 +35248,7 @@
       <c r="B223" s="54"/>
       <c r="C223" s="55"/>
       <c r="D223" s="55"/>
-      <c r="E223" s="55"/>
+      <c r="E223" s="54"/>
       <c r="F223" s="55"/>
       <c r="G223" s="54"/>
     </row>
@@ -35248,7 +35256,7 @@
       <c r="B224" s="54"/>
       <c r="C224" s="55"/>
       <c r="D224" s="55"/>
-      <c r="E224" s="55"/>
+      <c r="E224" s="54"/>
       <c r="F224" s="55"/>
       <c r="G224" s="54"/>
     </row>
@@ -35256,7 +35264,7 @@
       <c r="B225" s="54"/>
       <c r="C225" s="55"/>
       <c r="D225" s="55"/>
-      <c r="E225" s="55"/>
+      <c r="E225" s="54"/>
       <c r="F225" s="55"/>
       <c r="G225" s="54"/>
     </row>
@@ -35264,7 +35272,7 @@
       <c r="B226" s="54"/>
       <c r="C226" s="55"/>
       <c r="D226" s="55"/>
-      <c r="E226" s="55"/>
+      <c r="E226" s="54"/>
       <c r="F226" s="55"/>
       <c r="G226" s="54"/>
     </row>
@@ -35272,7 +35280,7 @@
       <c r="B227" s="54"/>
       <c r="C227" s="55"/>
       <c r="D227" s="55"/>
-      <c r="E227" s="55"/>
+      <c r="E227" s="54"/>
       <c r="F227" s="55"/>
       <c r="G227" s="54"/>
     </row>
@@ -35280,7 +35288,7 @@
       <c r="B228" s="54"/>
       <c r="C228" s="55"/>
       <c r="D228" s="55"/>
-      <c r="E228" s="55"/>
+      <c r="E228" s="54"/>
       <c r="F228" s="55"/>
       <c r="G228" s="54"/>
     </row>
@@ -35288,7 +35296,7 @@
       <c r="B229" s="54"/>
       <c r="C229" s="55"/>
       <c r="D229" s="55"/>
-      <c r="E229" s="55"/>
+      <c r="E229" s="54"/>
       <c r="F229" s="55"/>
       <c r="G229" s="54"/>
     </row>
@@ -35296,7 +35304,7 @@
       <c r="B230" s="54"/>
       <c r="C230" s="55"/>
       <c r="D230" s="55"/>
-      <c r="E230" s="55"/>
+      <c r="E230" s="54"/>
       <c r="F230" s="55"/>
       <c r="G230" s="54"/>
     </row>
@@ -35304,7 +35312,7 @@
       <c r="B231" s="54"/>
       <c r="C231" s="55"/>
       <c r="D231" s="55"/>
-      <c r="E231" s="55"/>
+      <c r="E231" s="54"/>
       <c r="F231" s="55"/>
       <c r="G231" s="54"/>
     </row>
@@ -35312,7 +35320,7 @@
       <c r="B232" s="54"/>
       <c r="C232" s="55"/>
       <c r="D232" s="55"/>
-      <c r="E232" s="55"/>
+      <c r="E232" s="54"/>
       <c r="F232" s="55"/>
       <c r="G232" s="54"/>
     </row>
@@ -35320,7 +35328,7 @@
       <c r="B233" s="54"/>
       <c r="C233" s="55"/>
       <c r="D233" s="55"/>
-      <c r="E233" s="55"/>
+      <c r="E233" s="54"/>
       <c r="F233" s="55"/>
       <c r="G233" s="54"/>
     </row>
@@ -35328,7 +35336,7 @@
       <c r="B234" s="54"/>
       <c r="C234" s="55"/>
       <c r="D234" s="55"/>
-      <c r="E234" s="55"/>
+      <c r="E234" s="54"/>
       <c r="F234" s="55"/>
       <c r="G234" s="54"/>
     </row>
@@ -35336,7 +35344,7 @@
       <c r="B235" s="54"/>
       <c r="C235" s="55"/>
       <c r="D235" s="55"/>
-      <c r="E235" s="55"/>
+      <c r="E235" s="54"/>
       <c r="F235" s="55"/>
       <c r="G235" s="54"/>
     </row>
@@ -35344,7 +35352,7 @@
       <c r="B236" s="54"/>
       <c r="C236" s="55"/>
       <c r="D236" s="55"/>
-      <c r="E236" s="55"/>
+      <c r="E236" s="54"/>
       <c r="F236" s="55"/>
       <c r="G236" s="54"/>
     </row>
@@ -35352,7 +35360,7 @@
       <c r="B237" s="54"/>
       <c r="C237" s="55"/>
       <c r="D237" s="55"/>
-      <c r="E237" s="55"/>
+      <c r="E237" s="54"/>
       <c r="F237" s="55"/>
       <c r="G237" s="54"/>
     </row>
@@ -35360,7 +35368,7 @@
       <c r="B238" s="54"/>
       <c r="C238" s="55"/>
       <c r="D238" s="55"/>
-      <c r="E238" s="55"/>
+      <c r="E238" s="54"/>
       <c r="F238" s="55"/>
       <c r="G238" s="54"/>
     </row>
@@ -35368,7 +35376,7 @@
       <c r="B239" s="54"/>
       <c r="C239" s="55"/>
       <c r="D239" s="55"/>
-      <c r="E239" s="55"/>
+      <c r="E239" s="54"/>
       <c r="F239" s="55"/>
       <c r="G239" s="54"/>
     </row>
@@ -35376,7 +35384,7 @@
       <c r="B240" s="54"/>
       <c r="C240" s="55"/>
       <c r="D240" s="55"/>
-      <c r="E240" s="55"/>
+      <c r="E240" s="54"/>
       <c r="F240" s="55"/>
       <c r="G240" s="54"/>
     </row>
@@ -35384,7 +35392,7 @@
       <c r="B241" s="54"/>
       <c r="C241" s="55"/>
       <c r="D241" s="55"/>
-      <c r="E241" s="55"/>
+      <c r="E241" s="54"/>
       <c r="F241" s="55"/>
       <c r="G241" s="54"/>
     </row>
@@ -35392,7 +35400,7 @@
       <c r="B242" s="54"/>
       <c r="C242" s="55"/>
       <c r="D242" s="55"/>
-      <c r="E242" s="55"/>
+      <c r="E242" s="54"/>
       <c r="F242" s="55"/>
       <c r="G242" s="54"/>
     </row>
@@ -35400,7 +35408,7 @@
       <c r="B243" s="54"/>
       <c r="C243" s="55"/>
       <c r="D243" s="55"/>
-      <c r="E243" s="55"/>
+      <c r="E243" s="54"/>
       <c r="F243" s="55"/>
       <c r="G243" s="54"/>
     </row>
@@ -35408,7 +35416,7 @@
       <c r="B244" s="54"/>
       <c r="C244" s="55"/>
       <c r="D244" s="55"/>
-      <c r="E244" s="55"/>
+      <c r="E244" s="54"/>
       <c r="F244" s="55"/>
       <c r="G244" s="54"/>
     </row>
@@ -35416,7 +35424,7 @@
       <c r="B245" s="54"/>
       <c r="C245" s="55"/>
       <c r="D245" s="55"/>
-      <c r="E245" s="55"/>
+      <c r="E245" s="54"/>
       <c r="F245" s="55"/>
       <c r="G245" s="54"/>
     </row>
@@ -35424,7 +35432,7 @@
       <c r="B246" s="54"/>
       <c r="C246" s="55"/>
       <c r="D246" s="55"/>
-      <c r="E246" s="55"/>
+      <c r="E246" s="54"/>
       <c r="F246" s="55"/>
       <c r="G246" s="54"/>
     </row>
@@ -35432,7 +35440,7 @@
       <c r="B247" s="54"/>
       <c r="C247" s="55"/>
       <c r="D247" s="55"/>
-      <c r="E247" s="55"/>
+      <c r="E247" s="54"/>
       <c r="F247" s="55"/>
       <c r="G247" s="54"/>
     </row>
@@ -35440,7 +35448,7 @@
       <c r="B248" s="54"/>
       <c r="C248" s="55"/>
       <c r="D248" s="55"/>
-      <c r="E248" s="55"/>
+      <c r="E248" s="54"/>
       <c r="F248" s="55"/>
       <c r="G248" s="54"/>
     </row>
@@ -35448,7 +35456,7 @@
       <c r="B249" s="54"/>
       <c r="C249" s="55"/>
       <c r="D249" s="55"/>
-      <c r="E249" s="55"/>
+      <c r="E249" s="54"/>
       <c r="F249" s="55"/>
       <c r="G249" s="54"/>
     </row>
@@ -35456,7 +35464,7 @@
       <c r="B250" s="54"/>
       <c r="C250" s="55"/>
       <c r="D250" s="55"/>
-      <c r="E250" s="55"/>
+      <c r="E250" s="54"/>
       <c r="F250" s="55"/>
       <c r="G250" s="54"/>
     </row>
@@ -35464,7 +35472,7 @@
       <c r="B251" s="54"/>
       <c r="C251" s="55"/>
       <c r="D251" s="55"/>
-      <c r="E251" s="55"/>
+      <c r="E251" s="54"/>
       <c r="F251" s="55"/>
       <c r="G251" s="54"/>
     </row>
@@ -35472,7 +35480,7 @@
       <c r="B252" s="54"/>
       <c r="C252" s="55"/>
       <c r="D252" s="55"/>
-      <c r="E252" s="55"/>
+      <c r="E252" s="54"/>
       <c r="F252" s="55"/>
       <c r="G252" s="54"/>
     </row>
@@ -35480,7 +35488,7 @@
       <c r="B253" s="54"/>
       <c r="C253" s="55"/>
       <c r="D253" s="55"/>
-      <c r="E253" s="55"/>
+      <c r="E253" s="54"/>
       <c r="F253" s="55"/>
       <c r="G253" s="54"/>
     </row>
@@ -35488,7 +35496,7 @@
       <c r="B254" s="54"/>
       <c r="C254" s="55"/>
       <c r="D254" s="55"/>
-      <c r="E254" s="55"/>
+      <c r="E254" s="54"/>
       <c r="F254" s="55"/>
       <c r="G254" s="54"/>
     </row>
@@ -35496,7 +35504,7 @@
       <c r="B255" s="54"/>
       <c r="C255" s="55"/>
       <c r="D255" s="55"/>
-      <c r="E255" s="55"/>
+      <c r="E255" s="54"/>
       <c r="F255" s="55"/>
       <c r="G255" s="54"/>
     </row>
@@ -35504,7 +35512,7 @@
       <c r="B256" s="54"/>
       <c r="C256" s="55"/>
       <c r="D256" s="55"/>
-      <c r="E256" s="55"/>
+      <c r="E256" s="54"/>
       <c r="F256" s="55"/>
       <c r="G256" s="54"/>
     </row>
@@ -35512,7 +35520,7 @@
       <c r="B257" s="54"/>
       <c r="C257" s="55"/>
       <c r="D257" s="55"/>
-      <c r="E257" s="55"/>
+      <c r="E257" s="54"/>
       <c r="F257" s="55"/>
       <c r="G257" s="54"/>
     </row>
@@ -35520,7 +35528,7 @@
       <c r="B258" s="54"/>
       <c r="C258" s="55"/>
       <c r="D258" s="55"/>
-      <c r="E258" s="55"/>
+      <c r="E258" s="54"/>
       <c r="F258" s="55"/>
       <c r="G258" s="54"/>
     </row>
@@ -35528,7 +35536,7 @@
       <c r="B259" s="54"/>
       <c r="C259" s="55"/>
       <c r="D259" s="55"/>
-      <c r="E259" s="55"/>
+      <c r="E259" s="54"/>
       <c r="F259" s="55"/>
       <c r="G259" s="54"/>
     </row>
@@ -35536,7 +35544,7 @@
       <c r="B260" s="54"/>
       <c r="C260" s="55"/>
       <c r="D260" s="55"/>
-      <c r="E260" s="55"/>
+      <c r="E260" s="54"/>
       <c r="F260" s="55"/>
       <c r="G260" s="54"/>
     </row>
@@ -35544,7 +35552,7 @@
       <c r="B261" s="54"/>
       <c r="C261" s="55"/>
       <c r="D261" s="55"/>
-      <c r="E261" s="55"/>
+      <c r="E261" s="54"/>
       <c r="F261" s="55"/>
       <c r="G261" s="54"/>
     </row>
@@ -35552,7 +35560,7 @@
       <c r="B262" s="54"/>
       <c r="C262" s="55"/>
       <c r="D262" s="55"/>
-      <c r="E262" s="55"/>
+      <c r="E262" s="54"/>
       <c r="F262" s="55"/>
       <c r="G262" s="54"/>
     </row>
@@ -35560,7 +35568,7 @@
       <c r="B263" s="54"/>
       <c r="C263" s="55"/>
       <c r="D263" s="55"/>
-      <c r="E263" s="55"/>
+      <c r="E263" s="54"/>
       <c r="F263" s="55"/>
       <c r="G263" s="54"/>
     </row>
@@ -35568,7 +35576,7 @@
       <c r="B264" s="54"/>
       <c r="C264" s="55"/>
       <c r="D264" s="55"/>
-      <c r="E264" s="55"/>
+      <c r="E264" s="54"/>
       <c r="F264" s="55"/>
       <c r="G264" s="54"/>
     </row>
@@ -35576,7 +35584,7 @@
       <c r="B265" s="54"/>
       <c r="C265" s="55"/>
       <c r="D265" s="55"/>
-      <c r="E265" s="55"/>
+      <c r="E265" s="54"/>
       <c r="F265" s="55"/>
       <c r="G265" s="54"/>
     </row>
@@ -35584,7 +35592,7 @@
       <c r="B266" s="54"/>
       <c r="C266" s="55"/>
       <c r="D266" s="55"/>
-      <c r="E266" s="55"/>
+      <c r="E266" s="54"/>
       <c r="F266" s="55"/>
       <c r="G266" s="54"/>
     </row>
@@ -35592,7 +35600,7 @@
       <c r="B267" s="54"/>
       <c r="C267" s="55"/>
       <c r="D267" s="55"/>
-      <c r="E267" s="55"/>
+      <c r="E267" s="54"/>
       <c r="F267" s="55"/>
       <c r="G267" s="54"/>
     </row>
@@ -35600,7 +35608,7 @@
       <c r="B268" s="54"/>
       <c r="C268" s="55"/>
       <c r="D268" s="55"/>
-      <c r="E268" s="55"/>
+      <c r="E268" s="54"/>
       <c r="F268" s="55"/>
       <c r="G268" s="54"/>
     </row>
@@ -35608,7 +35616,7 @@
       <c r="B269" s="54"/>
       <c r="C269" s="55"/>
       <c r="D269" s="55"/>
-      <c r="E269" s="55"/>
+      <c r="E269" s="54"/>
       <c r="F269" s="55"/>
       <c r="G269" s="54"/>
     </row>
@@ -35616,7 +35624,7 @@
       <c r="B270" s="54"/>
       <c r="C270" s="55"/>
       <c r="D270" s="55"/>
-      <c r="E270" s="55"/>
+      <c r="E270" s="54"/>
       <c r="F270" s="55"/>
       <c r="G270" s="54"/>
     </row>
@@ -35624,7 +35632,7 @@
       <c r="B271" s="54"/>
       <c r="C271" s="55"/>
       <c r="D271" s="55"/>
-      <c r="E271" s="55"/>
+      <c r="E271" s="54"/>
       <c r="F271" s="55"/>
       <c r="G271" s="54"/>
     </row>
@@ -35632,7 +35640,7 @@
       <c r="B272" s="54"/>
       <c r="C272" s="55"/>
       <c r="D272" s="55"/>
-      <c r="E272" s="55"/>
+      <c r="E272" s="54"/>
       <c r="F272" s="55"/>
       <c r="G272" s="54"/>
     </row>
@@ -35640,7 +35648,7 @@
       <c r="B273" s="54"/>
       <c r="C273" s="55"/>
       <c r="D273" s="55"/>
-      <c r="E273" s="55"/>
+      <c r="E273" s="54"/>
       <c r="F273" s="55"/>
       <c r="G273" s="54"/>
     </row>
@@ -35648,7 +35656,7 @@
       <c r="B274" s="54"/>
       <c r="C274" s="55"/>
       <c r="D274" s="55"/>
-      <c r="E274" s="55"/>
+      <c r="E274" s="54"/>
       <c r="F274" s="55"/>
       <c r="G274" s="54"/>
     </row>
@@ -35656,7 +35664,7 @@
       <c r="B275" s="54"/>
       <c r="C275" s="55"/>
       <c r="D275" s="55"/>
-      <c r="E275" s="55"/>
+      <c r="E275" s="54"/>
       <c r="F275" s="55"/>
       <c r="G275" s="54"/>
     </row>
@@ -35664,7 +35672,7 @@
       <c r="B276" s="54"/>
       <c r="C276" s="55"/>
       <c r="D276" s="55"/>
-      <c r="E276" s="55"/>
+      <c r="E276" s="54"/>
       <c r="F276" s="55"/>
       <c r="G276" s="54"/>
     </row>
@@ -35672,7 +35680,7 @@
       <c r="B277" s="54"/>
       <c r="C277" s="55"/>
       <c r="D277" s="55"/>
-      <c r="E277" s="55"/>
+      <c r="E277" s="54"/>
       <c r="F277" s="55"/>
       <c r="G277" s="54"/>
     </row>
@@ -35680,7 +35688,7 @@
       <c r="B278" s="54"/>
       <c r="C278" s="55"/>
       <c r="D278" s="55"/>
-      <c r="E278" s="55"/>
+      <c r="E278" s="54"/>
       <c r="F278" s="55"/>
       <c r="G278" s="54"/>
     </row>
@@ -35688,7 +35696,7 @@
       <c r="B279" s="54"/>
       <c r="C279" s="55"/>
       <c r="D279" s="55"/>
-      <c r="E279" s="55"/>
+      <c r="E279" s="54"/>
       <c r="F279" s="55"/>
       <c r="G279" s="54"/>
     </row>
@@ -35696,7 +35704,7 @@
       <c r="B280" s="54"/>
       <c r="C280" s="55"/>
       <c r="D280" s="55"/>
-      <c r="E280" s="55"/>
+      <c r="E280" s="54"/>
       <c r="F280" s="55"/>
       <c r="G280" s="54"/>
     </row>
@@ -35704,7 +35712,7 @@
       <c r="B281" s="54"/>
       <c r="C281" s="55"/>
       <c r="D281" s="55"/>
-      <c r="E281" s="55"/>
+      <c r="E281" s="54"/>
       <c r="F281" s="55"/>
       <c r="G281" s="54"/>
     </row>
@@ -35712,7 +35720,7 @@
       <c r="B282" s="54"/>
       <c r="C282" s="55"/>
       <c r="D282" s="55"/>
-      <c r="E282" s="55"/>
+      <c r="E282" s="54"/>
       <c r="F282" s="55"/>
       <c r="G282" s="54"/>
     </row>
@@ -35720,7 +35728,7 @@
       <c r="B283" s="54"/>
       <c r="C283" s="55"/>
       <c r="D283" s="55"/>
-      <c r="E283" s="55"/>
+      <c r="E283" s="54"/>
       <c r="F283" s="55"/>
       <c r="G283" s="54"/>
     </row>
@@ -35728,7 +35736,7 @@
       <c r="B284" s="54"/>
       <c r="C284" s="55"/>
       <c r="D284" s="55"/>
-      <c r="E284" s="55"/>
+      <c r="E284" s="54"/>
       <c r="F284" s="55"/>
       <c r="G284" s="54"/>
     </row>
@@ -35736,7 +35744,7 @@
       <c r="B285" s="54"/>
       <c r="C285" s="55"/>
       <c r="D285" s="55"/>
-      <c r="E285" s="55"/>
+      <c r="E285" s="54"/>
       <c r="F285" s="55"/>
       <c r="G285" s="54"/>
     </row>
@@ -35744,7 +35752,7 @@
       <c r="B286" s="54"/>
       <c r="C286" s="55"/>
       <c r="D286" s="55"/>
-      <c r="E286" s="55"/>
+      <c r="E286" s="54"/>
       <c r="F286" s="55"/>
       <c r="G286" s="54"/>
     </row>
@@ -35752,7 +35760,7 @@
       <c r="B287" s="54"/>
       <c r="C287" s="55"/>
       <c r="D287" s="55"/>
-      <c r="E287" s="55"/>
+      <c r="E287" s="54"/>
       <c r="F287" s="55"/>
       <c r="G287" s="54"/>
     </row>
@@ -35760,7 +35768,7 @@
       <c r="B288" s="54"/>
       <c r="C288" s="55"/>
       <c r="D288" s="55"/>
-      <c r="E288" s="55"/>
+      <c r="E288" s="54"/>
       <c r="F288" s="55"/>
       <c r="G288" s="54"/>
     </row>
@@ -35768,7 +35776,7 @@
       <c r="B289" s="54"/>
       <c r="C289" s="55"/>
       <c r="D289" s="55"/>
-      <c r="E289" s="55"/>
+      <c r="E289" s="54"/>
       <c r="F289" s="55"/>
       <c r="G289" s="54"/>
     </row>
@@ -35776,7 +35784,7 @@
       <c r="B290" s="54"/>
       <c r="C290" s="55"/>
       <c r="D290" s="55"/>
-      <c r="E290" s="55"/>
+      <c r="E290" s="54"/>
       <c r="F290" s="55"/>
       <c r="G290" s="54"/>
     </row>
@@ -35784,7 +35792,7 @@
       <c r="B291" s="54"/>
       <c r="C291" s="55"/>
       <c r="D291" s="55"/>
-      <c r="E291" s="55"/>
+      <c r="E291" s="54"/>
       <c r="F291" s="55"/>
       <c r="G291" s="54"/>
     </row>
@@ -35792,7 +35800,7 @@
       <c r="B292" s="54"/>
       <c r="C292" s="55"/>
       <c r="D292" s="55"/>
-      <c r="E292" s="55"/>
+      <c r="E292" s="54"/>
       <c r="F292" s="55"/>
       <c r="G292" s="54"/>
     </row>
@@ -35800,7 +35808,7 @@
       <c r="B293" s="54"/>
       <c r="C293" s="55"/>
       <c r="D293" s="55"/>
-      <c r="E293" s="55"/>
+      <c r="E293" s="54"/>
       <c r="F293" s="55"/>
       <c r="G293" s="54"/>
     </row>
@@ -35808,7 +35816,7 @@
       <c r="B294" s="54"/>
       <c r="C294" s="55"/>
       <c r="D294" s="55"/>
-      <c r="E294" s="55"/>
+      <c r="E294" s="54"/>
       <c r="F294" s="55"/>
       <c r="G294" s="54"/>
     </row>
@@ -35816,7 +35824,7 @@
       <c r="B295" s="54"/>
       <c r="C295" s="55"/>
       <c r="D295" s="55"/>
-      <c r="E295" s="55"/>
+      <c r="E295" s="54"/>
       <c r="F295" s="55"/>
       <c r="G295" s="54"/>
     </row>
@@ -35824,7 +35832,7 @@
       <c r="B296" s="54"/>
       <c r="C296" s="55"/>
       <c r="D296" s="55"/>
-      <c r="E296" s="55"/>
+      <c r="E296" s="54"/>
       <c r="F296" s="55"/>
       <c r="G296" s="54"/>
     </row>
@@ -35832,7 +35840,7 @@
       <c r="B297" s="54"/>
       <c r="C297" s="55"/>
       <c r="D297" s="55"/>
-      <c r="E297" s="55"/>
+      <c r="E297" s="54"/>
       <c r="F297" s="55"/>
       <c r="G297" s="54"/>
     </row>
@@ -35840,7 +35848,7 @@
       <c r="B298" s="54"/>
       <c r="C298" s="55"/>
       <c r="D298" s="55"/>
-      <c r="E298" s="55"/>
+      <c r="E298" s="54"/>
       <c r="F298" s="55"/>
       <c r="G298" s="54"/>
     </row>
@@ -35848,7 +35856,7 @@
       <c r="B299" s="54"/>
       <c r="C299" s="55"/>
       <c r="D299" s="55"/>
-      <c r="E299" s="55"/>
+      <c r="E299" s="54"/>
       <c r="F299" s="55"/>
       <c r="G299" s="54"/>
     </row>
@@ -35856,7 +35864,7 @@
       <c r="B300" s="54"/>
       <c r="C300" s="55"/>
       <c r="D300" s="55"/>
-      <c r="E300" s="55"/>
+      <c r="E300" s="54"/>
       <c r="F300" s="55"/>
       <c r="G300" s="54"/>
     </row>
@@ -35864,7 +35872,7 @@
       <c r="B301" s="54"/>
       <c r="C301" s="55"/>
       <c r="D301" s="55"/>
-      <c r="E301" s="55"/>
+      <c r="E301" s="54"/>
       <c r="F301" s="55"/>
       <c r="G301" s="54"/>
     </row>
@@ -35872,7 +35880,7 @@
       <c r="B302" s="54"/>
       <c r="C302" s="55"/>
       <c r="D302" s="55"/>
-      <c r="E302" s="55"/>
+      <c r="E302" s="54"/>
       <c r="F302" s="55"/>
       <c r="G302" s="54"/>
     </row>
@@ -35880,7 +35888,7 @@
       <c r="B303" s="54"/>
       <c r="C303" s="55"/>
       <c r="D303" s="55"/>
-      <c r="E303" s="55"/>
+      <c r="E303" s="54"/>
       <c r="F303" s="55"/>
       <c r="G303" s="54"/>
     </row>
@@ -35888,7 +35896,7 @@
       <c r="B304" s="54"/>
       <c r="C304" s="55"/>
       <c r="D304" s="55"/>
-      <c r="E304" s="55"/>
+      <c r="E304" s="54"/>
       <c r="F304" s="55"/>
       <c r="G304" s="54"/>
     </row>
@@ -35896,7 +35904,7 @@
       <c r="B305" s="54"/>
       <c r="C305" s="55"/>
       <c r="D305" s="55"/>
-      <c r="E305" s="55"/>
+      <c r="E305" s="54"/>
       <c r="F305" s="55"/>
       <c r="G305" s="54"/>
     </row>
@@ -35904,7 +35912,7 @@
       <c r="B306" s="54"/>
       <c r="C306" s="55"/>
       <c r="D306" s="55"/>
-      <c r="E306" s="55"/>
+      <c r="E306" s="54"/>
       <c r="F306" s="55"/>
       <c r="G306" s="54"/>
     </row>
@@ -35912,7 +35920,7 @@
       <c r="B307" s="54"/>
       <c r="C307" s="55"/>
       <c r="D307" s="55"/>
-      <c r="E307" s="55"/>
+      <c r="E307" s="54"/>
       <c r="F307" s="55"/>
       <c r="G307" s="54"/>
     </row>
@@ -35920,7 +35928,7 @@
       <c r="B308" s="54"/>
       <c r="C308" s="55"/>
       <c r="D308" s="55"/>
-      <c r="E308" s="55"/>
+      <c r="E308" s="54"/>
       <c r="F308" s="55"/>
       <c r="G308" s="54"/>
     </row>
@@ -35928,7 +35936,7 @@
       <c r="B309" s="54"/>
       <c r="C309" s="55"/>
       <c r="D309" s="55"/>
-      <c r="E309" s="55"/>
+      <c r="E309" s="54"/>
       <c r="F309" s="55"/>
       <c r="G309" s="54"/>
     </row>
@@ -35936,7 +35944,7 @@
       <c r="B310" s="54"/>
       <c r="C310" s="55"/>
       <c r="D310" s="55"/>
-      <c r="E310" s="55"/>
+      <c r="E310" s="54"/>
       <c r="F310" s="55"/>
       <c r="G310" s="54"/>
     </row>
@@ -35944,7 +35952,7 @@
       <c r="B311" s="54"/>
       <c r="C311" s="55"/>
       <c r="D311" s="55"/>
-      <c r="E311" s="55"/>
+      <c r="E311" s="54"/>
       <c r="F311" s="55"/>
       <c r="G311" s="54"/>
     </row>
@@ -35952,7 +35960,7 @@
       <c r="B312" s="54"/>
       <c r="C312" s="55"/>
       <c r="D312" s="55"/>
-      <c r="E312" s="55"/>
+      <c r="E312" s="54"/>
       <c r="F312" s="55"/>
       <c r="G312" s="54"/>
     </row>
@@ -35960,7 +35968,7 @@
       <c r="B313" s="54"/>
       <c r="C313" s="55"/>
       <c r="D313" s="55"/>
-      <c r="E313" s="55"/>
+      <c r="E313" s="54"/>
       <c r="F313" s="55"/>
       <c r="G313" s="54"/>
     </row>
@@ -35968,7 +35976,7 @@
       <c r="B314" s="54"/>
       <c r="C314" s="55"/>
       <c r="D314" s="55"/>
-      <c r="E314" s="55"/>
+      <c r="E314" s="54"/>
       <c r="F314" s="55"/>
       <c r="G314" s="54"/>
     </row>
@@ -35976,7 +35984,7 @@
       <c r="B315" s="54"/>
       <c r="C315" s="55"/>
       <c r="D315" s="55"/>
-      <c r="E315" s="55"/>
+      <c r="E315" s="54"/>
       <c r="F315" s="55"/>
       <c r="G315" s="54"/>
     </row>
@@ -35984,7 +35992,7 @@
       <c r="B316" s="54"/>
       <c r="C316" s="55"/>
       <c r="D316" s="55"/>
-      <c r="E316" s="55"/>
+      <c r="E316" s="54"/>
       <c r="F316" s="55"/>
       <c r="G316" s="54"/>
     </row>
@@ -35992,7 +36000,7 @@
       <c r="B317" s="54"/>
       <c r="C317" s="55"/>
       <c r="D317" s="55"/>
-      <c r="E317" s="55"/>
+      <c r="E317" s="54"/>
       <c r="F317" s="55"/>
       <c r="G317" s="54"/>
     </row>
@@ -36000,7 +36008,7 @@
       <c r="B318" s="54"/>
       <c r="C318" s="55"/>
       <c r="D318" s="55"/>
-      <c r="E318" s="55"/>
+      <c r="E318" s="54"/>
       <c r="F318" s="55"/>
       <c r="G318" s="54"/>
     </row>
@@ -36008,7 +36016,7 @@
       <c r="B319" s="54"/>
       <c r="C319" s="55"/>
       <c r="D319" s="55"/>
-      <c r="E319" s="55"/>
+      <c r="E319" s="54"/>
       <c r="F319" s="55"/>
       <c r="G319" s="54"/>
     </row>
@@ -36016,7 +36024,7 @@
       <c r="B320" s="54"/>
       <c r="C320" s="55"/>
       <c r="D320" s="55"/>
-      <c r="E320" s="55"/>
+      <c r="E320" s="54"/>
       <c r="F320" s="55"/>
       <c r="G320" s="54"/>
     </row>
@@ -36024,7 +36032,7 @@
       <c r="B321" s="54"/>
       <c r="C321" s="55"/>
       <c r="D321" s="55"/>
-      <c r="E321" s="55"/>
+      <c r="E321" s="54"/>
       <c r="F321" s="55"/>
       <c r="G321" s="54"/>
     </row>
@@ -36032,7 +36040,7 @@
       <c r="B322" s="54"/>
       <c r="C322" s="55"/>
       <c r="D322" s="55"/>
-      <c r="E322" s="55"/>
+      <c r="E322" s="54"/>
       <c r="F322" s="55"/>
       <c r="G322" s="54"/>
     </row>
@@ -36040,7 +36048,7 @@
       <c r="B323" s="54"/>
       <c r="C323" s="55"/>
       <c r="D323" s="55"/>
-      <c r="E323" s="55"/>
+      <c r="E323" s="54"/>
       <c r="F323" s="55"/>
       <c r="G323" s="54"/>
     </row>
@@ -36048,7 +36056,7 @@
       <c r="B324" s="54"/>
       <c r="C324" s="55"/>
       <c r="D324" s="55"/>
-      <c r="E324" s="55"/>
+      <c r="E324" s="54"/>
       <c r="F324" s="55"/>
       <c r="G324" s="54"/>
     </row>
@@ -36056,7 +36064,7 @@
       <c r="B325" s="54"/>
       <c r="C325" s="55"/>
       <c r="D325" s="55"/>
-      <c r="E325" s="55"/>
+      <c r="E325" s="54"/>
       <c r="F325" s="55"/>
       <c r="G325" s="54"/>
     </row>
@@ -36064,7 +36072,7 @@
       <c r="B326" s="54"/>
       <c r="C326" s="55"/>
       <c r="D326" s="55"/>
-      <c r="E326" s="55"/>
+      <c r="E326" s="54"/>
       <c r="F326" s="55"/>
       <c r="G326" s="54"/>
     </row>
@@ -36072,7 +36080,7 @@
       <c r="B327" s="54"/>
       <c r="C327" s="55"/>
       <c r="D327" s="55"/>
-      <c r="E327" s="55"/>
+      <c r="E327" s="54"/>
       <c r="F327" s="55"/>
       <c r="G327" s="54"/>
     </row>
@@ -36080,7 +36088,7 @@
       <c r="B328" s="54"/>
       <c r="C328" s="55"/>
       <c r="D328" s="55"/>
-      <c r="E328" s="55"/>
+      <c r="E328" s="54"/>
       <c r="F328" s="55"/>
       <c r="G328" s="54"/>
     </row>
@@ -36088,7 +36096,7 @@
       <c r="B329" s="54"/>
       <c r="C329" s="55"/>
       <c r="D329" s="55"/>
-      <c r="E329" s="55"/>
+      <c r="E329" s="54"/>
       <c r="F329" s="55"/>
       <c r="G329" s="54"/>
     </row>
@@ -36096,7 +36104,7 @@
       <c r="B330" s="54"/>
       <c r="C330" s="55"/>
       <c r="D330" s="55"/>
-      <c r="E330" s="55"/>
+      <c r="E330" s="54"/>
       <c r="F330" s="55"/>
       <c r="G330" s="54"/>
     </row>
@@ -36104,7 +36112,7 @@
       <c r="B331" s="54"/>
       <c r="C331" s="55"/>
       <c r="D331" s="55"/>
-      <c r="E331" s="55"/>
+      <c r="E331" s="54"/>
       <c r="F331" s="55"/>
       <c r="G331" s="54"/>
     </row>
@@ -36112,7 +36120,7 @@
       <c r="B332" s="54"/>
       <c r="C332" s="55"/>
       <c r="D332" s="55"/>
-      <c r="E332" s="55"/>
+      <c r="E332" s="54"/>
       <c r="F332" s="55"/>
       <c r="G332" s="54"/>
     </row>
@@ -36120,7 +36128,7 @@
       <c r="B333" s="54"/>
       <c r="C333" s="55"/>
       <c r="D333" s="55"/>
-      <c r="E333" s="55"/>
+      <c r="E333" s="54"/>
       <c r="F333" s="55"/>
       <c r="G333" s="54"/>
     </row>
@@ -36128,7 +36136,7 @@
       <c r="B334" s="54"/>
       <c r="C334" s="55"/>
       <c r="D334" s="55"/>
-      <c r="E334" s="55"/>
+      <c r="E334" s="54"/>
       <c r="F334" s="55"/>
       <c r="G334" s="54"/>
     </row>
@@ -36136,7 +36144,7 @@
       <c r="B335" s="54"/>
       <c r="C335" s="55"/>
       <c r="D335" s="55"/>
-      <c r="E335" s="55"/>
+      <c r="E335" s="54"/>
       <c r="F335" s="55"/>
       <c r="G335" s="54"/>
     </row>
@@ -36144,7 +36152,7 @@
       <c r="B336" s="54"/>
       <c r="C336" s="55"/>
       <c r="D336" s="55"/>
-      <c r="E336" s="55"/>
+      <c r="E336" s="54"/>
       <c r="F336" s="55"/>
       <c r="G336" s="54"/>
     </row>
@@ -36152,7 +36160,7 @@
       <c r="B337" s="54"/>
       <c r="C337" s="55"/>
       <c r="D337" s="55"/>
-      <c r="E337" s="55"/>
+      <c r="E337" s="54"/>
       <c r="F337" s="55"/>
       <c r="G337" s="54"/>
     </row>
@@ -36160,7 +36168,7 @@
       <c r="B338" s="54"/>
       <c r="C338" s="55"/>
       <c r="D338" s="55"/>
-      <c r="E338" s="55"/>
+      <c r="E338" s="54"/>
       <c r="F338" s="55"/>
       <c r="G338" s="54"/>
     </row>
@@ -36168,7 +36176,7 @@
       <c r="B339" s="54"/>
       <c r="C339" s="55"/>
       <c r="D339" s="55"/>
-      <c r="E339" s="55"/>
+      <c r="E339" s="54"/>
       <c r="F339" s="55"/>
       <c r="G339" s="54"/>
     </row>
@@ -36176,7 +36184,7 @@
       <c r="B340" s="54"/>
       <c r="C340" s="55"/>
       <c r="D340" s="55"/>
-      <c r="E340" s="55"/>
+      <c r="E340" s="54"/>
       <c r="F340" s="55"/>
       <c r="G340" s="54"/>
     </row>
@@ -36184,7 +36192,7 @@
       <c r="B341" s="54"/>
       <c r="C341" s="55"/>
       <c r="D341" s="55"/>
-      <c r="E341" s="55"/>
+      <c r="E341" s="54"/>
       <c r="F341" s="55"/>
       <c r="G341" s="54"/>
     </row>
@@ -36192,7 +36200,7 @@
       <c r="B342" s="54"/>
       <c r="C342" s="55"/>
       <c r="D342" s="55"/>
-      <c r="E342" s="55"/>
+      <c r="E342" s="54"/>
       <c r="F342" s="55"/>
       <c r="G342" s="54"/>
     </row>
@@ -36200,7 +36208,7 @@
       <c r="B343" s="54"/>
       <c r="C343" s="55"/>
       <c r="D343" s="55"/>
-      <c r="E343" s="55"/>
+      <c r="E343" s="54"/>
       <c r="F343" s="55"/>
       <c r="G343" s="54"/>
     </row>
@@ -36208,7 +36216,7 @@
       <c r="B344" s="54"/>
       <c r="C344" s="55"/>
       <c r="D344" s="55"/>
-      <c r="E344" s="55"/>
+      <c r="E344" s="54"/>
       <c r="F344" s="55"/>
       <c r="G344" s="54"/>
     </row>
@@ -36216,7 +36224,7 @@
       <c r="B345" s="54"/>
       <c r="C345" s="55"/>
       <c r="D345" s="55"/>
-      <c r="E345" s="55"/>
+      <c r="E345" s="54"/>
       <c r="F345" s="55"/>
       <c r="G345" s="54"/>
     </row>
@@ -36224,7 +36232,7 @@
       <c r="B346" s="54"/>
       <c r="C346" s="55"/>
       <c r="D346" s="55"/>
-      <c r="E346" s="55"/>
+      <c r="E346" s="54"/>
       <c r="F346" s="55"/>
       <c r="G346" s="54"/>
     </row>
@@ -36232,7 +36240,7 @@
       <c r="B347" s="54"/>
       <c r="C347" s="55"/>
       <c r="D347" s="55"/>
-      <c r="E347" s="55"/>
+      <c r="E347" s="54"/>
       <c r="F347" s="55"/>
       <c r="G347" s="54"/>
     </row>
@@ -36240,7 +36248,7 @@
       <c r="B348" s="54"/>
       <c r="C348" s="55"/>
       <c r="D348" s="55"/>
-      <c r="E348" s="55"/>
+      <c r="E348" s="54"/>
       <c r="F348" s="55"/>
       <c r="G348" s="54"/>
     </row>
@@ -36248,7 +36256,7 @@
       <c r="B349" s="54"/>
       <c r="C349" s="55"/>
       <c r="D349" s="55"/>
-      <c r="E349" s="55"/>
+      <c r="E349" s="54"/>
       <c r="F349" s="55"/>
       <c r="G349" s="54"/>
     </row>
@@ -36256,7 +36264,7 @@
       <c r="B350" s="54"/>
       <c r="C350" s="55"/>
       <c r="D350" s="55"/>
-      <c r="E350" s="55"/>
+      <c r="E350" s="54"/>
       <c r="F350" s="55"/>
       <c r="G350" s="54"/>
     </row>
@@ -36264,7 +36272,7 @@
       <c r="B351" s="54"/>
       <c r="C351" s="55"/>
       <c r="D351" s="55"/>
-      <c r="E351" s="55"/>
+      <c r="E351" s="54"/>
       <c r="F351" s="55"/>
       <c r="G351" s="54"/>
     </row>
@@ -36272,7 +36280,7 @@
       <c r="B352" s="54"/>
       <c r="C352" s="55"/>
       <c r="D352" s="55"/>
-      <c r="E352" s="55"/>
+      <c r="E352" s="54"/>
       <c r="F352" s="55"/>
       <c r="G352" s="54"/>
     </row>
@@ -36280,7 +36288,7 @@
       <c r="B353" s="54"/>
       <c r="C353" s="55"/>
       <c r="D353" s="55"/>
-      <c r="E353" s="55"/>
+      <c r="E353" s="54"/>
       <c r="F353" s="55"/>
       <c r="G353" s="54"/>
     </row>
@@ -36288,7 +36296,7 @@
       <c r="B354" s="54"/>
       <c r="C354" s="55"/>
       <c r="D354" s="55"/>
-      <c r="E354" s="55"/>
+      <c r="E354" s="54"/>
       <c r="F354" s="55"/>
       <c r="G354" s="54"/>
     </row>
@@ -36296,7 +36304,7 @@
       <c r="B355" s="54"/>
       <c r="C355" s="55"/>
       <c r="D355" s="55"/>
-      <c r="E355" s="55"/>
+      <c r="E355" s="54"/>
       <c r="F355" s="55"/>
       <c r="G355" s="54"/>
     </row>
@@ -36304,7 +36312,7 @@
       <c r="B356" s="54"/>
       <c r="C356" s="55"/>
       <c r="D356" s="55"/>
-      <c r="E356" s="55"/>
+      <c r="E356" s="54"/>
       <c r="F356" s="55"/>
       <c r="G356" s="54"/>
     </row>
@@ -36312,7 +36320,7 @@
       <c r="B357" s="54"/>
       <c r="C357" s="55"/>
       <c r="D357" s="55"/>
-      <c r="E357" s="55"/>
+      <c r="E357" s="54"/>
       <c r="F357" s="55"/>
       <c r="G357" s="54"/>
     </row>
@@ -36320,7 +36328,7 @@
       <c r="B358" s="54"/>
       <c r="C358" s="55"/>
       <c r="D358" s="55"/>
-      <c r="E358" s="55"/>
+      <c r="E358" s="54"/>
       <c r="F358" s="55"/>
       <c r="G358" s="54"/>
     </row>
@@ -36328,7 +36336,7 @@
       <c r="B359" s="54"/>
       <c r="C359" s="55"/>
       <c r="D359" s="55"/>
-      <c r="E359" s="55"/>
+      <c r="E359" s="54"/>
       <c r="F359" s="55"/>
       <c r="G359" s="54"/>
     </row>
@@ -36336,7 +36344,7 @@
       <c r="B360" s="54"/>
       <c r="C360" s="55"/>
       <c r="D360" s="55"/>
-      <c r="E360" s="55"/>
+      <c r="E360" s="54"/>
       <c r="F360" s="55"/>
       <c r="G360" s="54"/>
     </row>
@@ -36344,7 +36352,7 @@
       <c r="B361" s="54"/>
       <c r="C361" s="55"/>
       <c r="D361" s="55"/>
-      <c r="E361" s="55"/>
+      <c r="E361" s="54"/>
       <c r="F361" s="55"/>
       <c r="G361" s="54"/>
     </row>
@@ -36352,7 +36360,7 @@
       <c r="B362" s="54"/>
       <c r="C362" s="55"/>
       <c r="D362" s="55"/>
-      <c r="E362" s="55"/>
+      <c r="E362" s="54"/>
       <c r="F362" s="55"/>
       <c r="G362" s="54"/>
     </row>
@@ -36360,7 +36368,7 @@
       <c r="B363" s="54"/>
       <c r="C363" s="55"/>
       <c r="D363" s="55"/>
-      <c r="E363" s="55"/>
+      <c r="E363" s="54"/>
       <c r="F363" s="55"/>
       <c r="G363" s="54"/>
     </row>
@@ -36368,7 +36376,7 @@
       <c r="B364" s="54"/>
       <c r="C364" s="55"/>
       <c r="D364" s="55"/>
-      <c r="E364" s="55"/>
+      <c r="E364" s="54"/>
       <c r="F364" s="55"/>
       <c r="G364" s="54"/>
     </row>
@@ -36376,7 +36384,7 @@
       <c r="B365" s="54"/>
       <c r="C365" s="55"/>
       <c r="D365" s="55"/>
-      <c r="E365" s="55"/>
+      <c r="E365" s="54"/>
       <c r="F365" s="55"/>
       <c r="G365" s="54"/>
     </row>
@@ -36384,7 +36392,7 @@
       <c r="B366" s="54"/>
       <c r="C366" s="55"/>
       <c r="D366" s="55"/>
-      <c r="E366" s="55"/>
+      <c r="E366" s="54"/>
       <c r="F366" s="55"/>
       <c r="G366" s="54"/>
     </row>
@@ -36392,7 +36400,7 @@
       <c r="B367" s="54"/>
       <c r="C367" s="55"/>
       <c r="D367" s="55"/>
-      <c r="E367" s="55"/>
+      <c r="E367" s="54"/>
       <c r="F367" s="55"/>
       <c r="G367" s="54"/>
     </row>
@@ -36400,7 +36408,7 @@
       <c r="B368" s="54"/>
       <c r="C368" s="55"/>
       <c r="D368" s="55"/>
-      <c r="E368" s="55"/>
+      <c r="E368" s="54"/>
       <c r="F368" s="55"/>
       <c r="G368" s="54"/>
     </row>
@@ -36408,7 +36416,7 @@
       <c r="B369" s="54"/>
       <c r="C369" s="55"/>
       <c r="D369" s="55"/>
-      <c r="E369" s="55"/>
+      <c r="E369" s="54"/>
       <c r="F369" s="55"/>
       <c r="G369" s="54"/>
     </row>
@@ -36416,7 +36424,7 @@
       <c r="B370" s="54"/>
       <c r="C370" s="55"/>
       <c r="D370" s="55"/>
-      <c r="E370" s="55"/>
+      <c r="E370" s="54"/>
       <c r="F370" s="55"/>
       <c r="G370" s="54"/>
     </row>
@@ -36424,7 +36432,7 @@
       <c r="B371" s="54"/>
       <c r="C371" s="55"/>
       <c r="D371" s="55"/>
-      <c r="E371" s="55"/>
+      <c r="E371" s="54"/>
       <c r="F371" s="55"/>
       <c r="G371" s="54"/>
     </row>
@@ -36432,7 +36440,7 @@
       <c r="B372" s="54"/>
       <c r="C372" s="55"/>
       <c r="D372" s="55"/>
-      <c r="E372" s="55"/>
+      <c r="E372" s="54"/>
       <c r="F372" s="55"/>
       <c r="G372" s="54"/>
     </row>
@@ -36440,7 +36448,7 @@
       <c r="B373" s="54"/>
       <c r="C373" s="55"/>
       <c r="D373" s="55"/>
-      <c r="E373" s="55"/>
+      <c r="E373" s="54"/>
       <c r="F373" s="55"/>
       <c r="G373" s="54"/>
     </row>
@@ -36448,7 +36456,7 @@
       <c r="B374" s="54"/>
       <c r="C374" s="55"/>
       <c r="D374" s="55"/>
-      <c r="E374" s="55"/>
+      <c r="E374" s="54"/>
       <c r="F374" s="55"/>
       <c r="G374" s="54"/>
     </row>
@@ -36456,7 +36464,7 @@
       <c r="B375" s="54"/>
       <c r="C375" s="55"/>
       <c r="D375" s="55"/>
-      <c r="E375" s="55"/>
+      <c r="E375" s="54"/>
       <c r="F375" s="55"/>
       <c r="G375" s="54"/>
     </row>
@@ -36464,7 +36472,7 @@
       <c r="B376" s="54"/>
       <c r="C376" s="55"/>
       <c r="D376" s="55"/>
-      <c r="E376" s="55"/>
+      <c r="E376" s="54"/>
       <c r="F376" s="55"/>
       <c r="G376" s="54"/>
     </row>
@@ -36472,7 +36480,7 @@
       <c r="B377" s="54"/>
       <c r="C377" s="55"/>
       <c r="D377" s="55"/>
-      <c r="E377" s="55"/>
+      <c r="E377" s="54"/>
       <c r="F377" s="55"/>
       <c r="G377" s="54"/>
     </row>
@@ -36480,7 +36488,7 @@
       <c r="B378" s="54"/>
       <c r="C378" s="55"/>
       <c r="D378" s="55"/>
-      <c r="E378" s="55"/>
+      <c r="E378" s="54"/>
       <c r="F378" s="55"/>
       <c r="G378" s="54"/>
     </row>
@@ -36488,7 +36496,7 @@
       <c r="B379" s="54"/>
       <c r="C379" s="55"/>
       <c r="D379" s="55"/>
-      <c r="E379" s="55"/>
+      <c r="E379" s="54"/>
       <c r="F379" s="55"/>
       <c r="G379" s="54"/>
     </row>
@@ -36496,7 +36504,7 @@
       <c r="B380" s="54"/>
       <c r="C380" s="55"/>
       <c r="D380" s="55"/>
-      <c r="E380" s="55"/>
+      <c r="E380" s="54"/>
       <c r="F380" s="55"/>
       <c r="G380" s="54"/>
     </row>
@@ -36504,7 +36512,7 @@
       <c r="B381" s="54"/>
       <c r="C381" s="55"/>
       <c r="D381" s="55"/>
-      <c r="E381" s="55"/>
+      <c r="E381" s="54"/>
       <c r="F381" s="55"/>
       <c r="G381" s="54"/>
     </row>
@@ -36512,7 +36520,7 @@
       <c r="B382" s="54"/>
       <c r="C382" s="55"/>
       <c r="D382" s="55"/>
-      <c r="E382" s="55"/>
+      <c r="E382" s="54"/>
       <c r="F382" s="55"/>
       <c r="G382" s="54"/>
     </row>
@@ -36520,7 +36528,7 @@
       <c r="B383" s="54"/>
       <c r="C383" s="55"/>
       <c r="D383" s="55"/>
-      <c r="E383" s="55"/>
+      <c r="E383" s="54"/>
       <c r="F383" s="55"/>
       <c r="G383" s="54"/>
     </row>
@@ -36528,7 +36536,7 @@
       <c r="B384" s="54"/>
       <c r="C384" s="55"/>
       <c r="D384" s="55"/>
-      <c r="E384" s="55"/>
+      <c r="E384" s="54"/>
       <c r="F384" s="55"/>
       <c r="G384" s="54"/>
     </row>
@@ -36536,7 +36544,7 @@
       <c r="B385" s="54"/>
       <c r="C385" s="55"/>
       <c r="D385" s="55"/>
-      <c r="E385" s="55"/>
+      <c r="E385" s="54"/>
       <c r="F385" s="55"/>
       <c r="G385" s="54"/>
     </row>
@@ -36544,7 +36552,7 @@
       <c r="B386" s="54"/>
       <c r="C386" s="55"/>
       <c r="D386" s="55"/>
-      <c r="E386" s="55"/>
+      <c r="E386" s="54"/>
       <c r="F386" s="55"/>
       <c r="G386" s="54"/>
     </row>
@@ -36552,7 +36560,7 @@
       <c r="B387" s="54"/>
       <c r="C387" s="55"/>
       <c r="D387" s="55"/>
-      <c r="E387" s="55"/>
+      <c r="E387" s="54"/>
       <c r="F387" s="55"/>
       <c r="G387" s="54"/>
     </row>
@@ -36560,7 +36568,7 @@
       <c r="B388" s="54"/>
       <c r="C388" s="55"/>
       <c r="D388" s="55"/>
-      <c r="E388" s="55"/>
+      <c r="E388" s="54"/>
       <c r="F388" s="55"/>
       <c r="G388" s="54"/>
     </row>
@@ -36568,7 +36576,7 @@
       <c r="B389" s="54"/>
       <c r="C389" s="55"/>
       <c r="D389" s="55"/>
-      <c r="E389" s="55"/>
+      <c r="E389" s="54"/>
       <c r="F389" s="55"/>
       <c r="G389" s="54"/>
     </row>
@@ -36576,7 +36584,7 @@
       <c r="B390" s="54"/>
       <c r="C390" s="55"/>
       <c r="D390" s="55"/>
-      <c r="E390" s="55"/>
+      <c r="E390" s="54"/>
       <c r="F390" s="55"/>
       <c r="G390" s="54"/>
     </row>
@@ -36584,7 +36592,7 @@
       <c r="B391" s="54"/>
       <c r="C391" s="55"/>
       <c r="D391" s="55"/>
-      <c r="E391" s="55"/>
+      <c r="E391" s="54"/>
       <c r="F391" s="55"/>
       <c r="G391" s="54"/>
     </row>
@@ -36592,7 +36600,7 @@
       <c r="B392" s="54"/>
       <c r="C392" s="55"/>
       <c r="D392" s="55"/>
-      <c r="E392" s="55"/>
+      <c r="E392" s="54"/>
       <c r="F392" s="55"/>
       <c r="G392" s="54"/>
     </row>
@@ -36600,7 +36608,7 @@
       <c r="B393" s="54"/>
       <c r="C393" s="55"/>
       <c r="D393" s="55"/>
-      <c r="E393" s="55"/>
+      <c r="E393" s="54"/>
       <c r="F393" s="55"/>
       <c r="G393" s="54"/>
     </row>
@@ -36608,7 +36616,7 @@
       <c r="B394" s="54"/>
       <c r="C394" s="55"/>
       <c r="D394" s="55"/>
-      <c r="E394" s="55"/>
+      <c r="E394" s="54"/>
       <c r="F394" s="55"/>
       <c r="G394" s="54"/>
     </row>
@@ -36616,7 +36624,7 @@
       <c r="B395" s="54"/>
       <c r="C395" s="55"/>
       <c r="D395" s="55"/>
-      <c r="E395" s="55"/>
+      <c r="E395" s="54"/>
       <c r="F395" s="55"/>
       <c r="G395" s="54"/>
     </row>
@@ -36624,7 +36632,7 @@
       <c r="B396" s="54"/>
       <c r="C396" s="55"/>
       <c r="D396" s="55"/>
-      <c r="E396" s="55"/>
+      <c r="E396" s="54"/>
       <c r="F396" s="55"/>
       <c r="G396" s="54"/>
     </row>
@@ -36632,7 +36640,7 @@
       <c r="B397" s="54"/>
       <c r="C397" s="55"/>
       <c r="D397" s="55"/>
-      <c r="E397" s="55"/>
+      <c r="E397" s="54"/>
       <c r="F397" s="55"/>
       <c r="G397" s="54"/>
     </row>
@@ -36640,7 +36648,7 @@
       <c r="B398" s="54"/>
       <c r="C398" s="55"/>
       <c r="D398" s="55"/>
-      <c r="E398" s="55"/>
+      <c r="E398" s="54"/>
       <c r="F398" s="55"/>
       <c r="G398" s="54"/>
     </row>
@@ -36648,7 +36656,7 @@
       <c r="B399" s="54"/>
       <c r="C399" s="55"/>
       <c r="D399" s="55"/>
-      <c r="E399" s="55"/>
+      <c r="E399" s="54"/>
       <c r="F399" s="55"/>
       <c r="G399" s="54"/>
     </row>
@@ -36656,7 +36664,7 @@
       <c r="B400" s="54"/>
       <c r="C400" s="55"/>
       <c r="D400" s="55"/>
-      <c r="E400" s="55"/>
+      <c r="E400" s="54"/>
       <c r="F400" s="55"/>
       <c r="G400" s="54"/>
     </row>
@@ -36664,7 +36672,7 @@
       <c r="B401" s="54"/>
       <c r="C401" s="55"/>
       <c r="D401" s="55"/>
-      <c r="E401" s="55"/>
+      <c r="E401" s="54"/>
       <c r="F401" s="55"/>
       <c r="G401" s="54"/>
     </row>
@@ -36672,7 +36680,7 @@
       <c r="B402" s="54"/>
       <c r="C402" s="55"/>
       <c r="D402" s="55"/>
-      <c r="E402" s="55"/>
+      <c r="E402" s="54"/>
       <c r="F402" s="55"/>
       <c r="G402" s="54"/>
     </row>
@@ -36680,7 +36688,7 @@
       <c r="B403" s="54"/>
       <c r="C403" s="55"/>
       <c r="D403" s="55"/>
-      <c r="E403" s="55"/>
+      <c r="E403" s="54"/>
       <c r="F403" s="55"/>
       <c r="G403" s="54"/>
     </row>
@@ -36688,7 +36696,7 @@
       <c r="B404" s="54"/>
       <c r="C404" s="55"/>
       <c r="D404" s="55"/>
-      <c r="E404" s="55"/>
+      <c r="E404" s="54"/>
       <c r="F404" s="55"/>
       <c r="G404" s="54"/>
     </row>
@@ -36696,7 +36704,7 @@
       <c r="B405" s="54"/>
       <c r="C405" s="55"/>
       <c r="D405" s="55"/>
-      <c r="E405" s="55"/>
+      <c r="E405" s="54"/>
       <c r="F405" s="55"/>
       <c r="G405" s="54"/>
     </row>
@@ -36704,7 +36712,7 @@
       <c r="B406" s="54"/>
       <c r="C406" s="55"/>
       <c r="D406" s="55"/>
-      <c r="E406" s="55"/>
+      <c r="E406" s="54"/>
       <c r="F406" s="55"/>
       <c r="G406" s="54"/>
     </row>
@@ -36712,7 +36720,7 @@
       <c r="B407" s="54"/>
       <c r="C407" s="55"/>
       <c r="D407" s="55"/>
-      <c r="E407" s="55"/>
+      <c r="E407" s="54"/>
       <c r="F407" s="55"/>
       <c r="G407" s="54"/>
     </row>
@@ -36720,7 +36728,7 @@
       <c r="B408" s="54"/>
       <c r="C408" s="55"/>
       <c r="D408" s="55"/>
-      <c r="E408" s="55"/>
+      <c r="E408" s="54"/>
       <c r="F408" s="55"/>
       <c r="G408" s="54"/>
     </row>
@@ -36728,7 +36736,7 @@
       <c r="B409" s="54"/>
       <c r="C409" s="55"/>
       <c r="D409" s="55"/>
-      <c r="E409" s="55"/>
+      <c r="E409" s="54"/>
       <c r="F409" s="55"/>
       <c r="G409" s="54"/>
     </row>
@@ -36736,7 +36744,7 @@
       <c r="B410" s="54"/>
       <c r="C410" s="55"/>
       <c r="D410" s="55"/>
-      <c r="E410" s="55"/>
+      <c r="E410" s="54"/>
       <c r="F410" s="55"/>
       <c r="G410" s="54"/>
     </row>
@@ -36744,7 +36752,7 @@
       <c r="B411" s="54"/>
       <c r="C411" s="55"/>
       <c r="D411" s="55"/>
-      <c r="E411" s="55"/>
+      <c r="E411" s="54"/>
       <c r="F411" s="55"/>
       <c r="G411" s="54"/>
     </row>
@@ -36752,7 +36760,7 @@
       <c r="B412" s="54"/>
       <c r="C412" s="55"/>
       <c r="D412" s="55"/>
-      <c r="E412" s="55"/>
+      <c r="E412" s="54"/>
       <c r="F412" s="55"/>
       <c r="G412" s="54"/>
     </row>
@@ -36760,7 +36768,7 @@
       <c r="B413" s="54"/>
       <c r="C413" s="55"/>
       <c r="D413" s="55"/>
-      <c r="E413" s="55"/>
+      <c r="E413" s="54"/>
       <c r="F413" s="55"/>
       <c r="G413" s="54"/>
     </row>
@@ -36768,7 +36776,7 @@
       <c r="B414" s="54"/>
       <c r="C414" s="55"/>
       <c r="D414" s="55"/>
-      <c r="E414" s="55"/>
+      <c r="E414" s="54"/>
       <c r="F414" s="55"/>
       <c r="G414" s="54"/>
     </row>
@@ -36776,7 +36784,7 @@
       <c r="B415" s="54"/>
       <c r="C415" s="55"/>
       <c r="D415" s="55"/>
-      <c r="E415" s="55"/>
+      <c r="E415" s="54"/>
       <c r="F415" s="55"/>
       <c r="G415" s="54"/>
     </row>
@@ -36784,7 +36792,7 @@
       <c r="B416" s="54"/>
       <c r="C416" s="55"/>
       <c r="D416" s="55"/>
-      <c r="E416" s="55"/>
+      <c r="E416" s="54"/>
       <c r="F416" s="55"/>
       <c r="G416" s="54"/>
     </row>
@@ -36792,7 +36800,7 @@
       <c r="B417" s="54"/>
       <c r="C417" s="55"/>
       <c r="D417" s="55"/>
-      <c r="E417" s="55"/>
+      <c r="E417" s="54"/>
       <c r="F417" s="55"/>
       <c r="G417" s="54"/>
     </row>
@@ -36800,7 +36808,7 @@
       <c r="B418" s="54"/>
       <c r="C418" s="55"/>
       <c r="D418" s="55"/>
-      <c r="E418" s="55"/>
+      <c r="E418" s="54"/>
       <c r="F418" s="55"/>
       <c r="G418" s="54"/>
     </row>
@@ -36808,7 +36816,7 @@
       <c r="B419" s="54"/>
       <c r="C419" s="55"/>
       <c r="D419" s="55"/>
-      <c r="E419" s="55"/>
+      <c r="E419" s="54"/>
       <c r="F419" s="55"/>
       <c r="G419" s="54"/>
     </row>
@@ -36816,7 +36824,7 @@
       <c r="B420" s="54"/>
       <c r="C420" s="55"/>
       <c r="D420" s="55"/>
-      <c r="E420" s="55"/>
+      <c r="E420" s="54"/>
       <c r="F420" s="55"/>
       <c r="G420" s="54"/>
     </row>
@@ -36824,7 +36832,7 @@
       <c r="B421" s="54"/>
       <c r="C421" s="55"/>
       <c r="D421" s="55"/>
-      <c r="E421" s="55"/>
+      <c r="E421" s="54"/>
       <c r="F421" s="55"/>
       <c r="G421" s="54"/>
     </row>
@@ -36832,7 +36840,7 @@
       <c r="B422" s="54"/>
       <c r="C422" s="55"/>
       <c r="D422" s="55"/>
-      <c r="E422" s="55"/>
+      <c r="E422" s="54"/>
       <c r="F422" s="55"/>
       <c r="G422" s="54"/>
     </row>
@@ -36840,7 +36848,7 @@
       <c r="B423" s="54"/>
       <c r="C423" s="55"/>
       <c r="D423" s="55"/>
-      <c r="E423" s="55"/>
+      <c r="E423" s="54"/>
       <c r="F423" s="55"/>
       <c r="G423" s="54"/>
     </row>
@@ -36848,7 +36856,7 @@
       <c r="B424" s="54"/>
       <c r="C424" s="55"/>
       <c r="D424" s="55"/>
-      <c r="E424" s="55"/>
+      <c r="E424" s="54"/>
       <c r="F424" s="55"/>
       <c r="G424" s="54"/>
     </row>
@@ -36856,7 +36864,7 @@
       <c r="B425" s="54"/>
       <c r="C425" s="55"/>
       <c r="D425" s="55"/>
-      <c r="E425" s="55"/>
+      <c r="E425" s="54"/>
       <c r="F425" s="55"/>
       <c r="G425" s="54"/>
     </row>
@@ -36864,7 +36872,7 @@
       <c r="B426" s="54"/>
       <c r="C426" s="55"/>
       <c r="D426" s="55"/>
-      <c r="E426" s="55"/>
+      <c r="E426" s="54"/>
       <c r="F426" s="55"/>
       <c r="G426" s="54"/>
     </row>
@@ -36872,7 +36880,7 @@
       <c r="B427" s="54"/>
       <c r="C427" s="55"/>
       <c r="D427" s="55"/>
-      <c r="E427" s="55"/>
+      <c r="E427" s="54"/>
       <c r="F427" s="55"/>
       <c r="G427" s="54"/>
     </row>
@@ -36880,7 +36888,7 @@
       <c r="B428" s="54"/>
       <c r="C428" s="55"/>
       <c r="D428" s="55"/>
-      <c r="E428" s="55"/>
+      <c r="E428" s="54"/>
       <c r="F428" s="55"/>
       <c r="G428" s="54"/>
     </row>
@@ -36888,7 +36896,7 @@
       <c r="B429" s="54"/>
       <c r="C429" s="55"/>
       <c r="D429" s="55"/>
-      <c r="E429" s="55"/>
+      <c r="E429" s="54"/>
       <c r="F429" s="55"/>
       <c r="G429" s="54"/>
     </row>
@@ -36896,7 +36904,7 @@
       <c r="B430" s="54"/>
       <c r="C430" s="55"/>
       <c r="D430" s="55"/>
-      <c r="E430" s="55"/>
+      <c r="E430" s="54"/>
       <c r="F430" s="55"/>
       <c r="G430" s="54"/>
     </row>
@@ -36904,7 +36912,7 @@
       <c r="B431" s="54"/>
       <c r="C431" s="55"/>
       <c r="D431" s="55"/>
-      <c r="E431" s="55"/>
+      <c r="E431" s="54"/>
       <c r="F431" s="55"/>
       <c r="G431" s="54"/>
     </row>
@@ -36912,7 +36920,7 @@
       <c r="B432" s="54"/>
       <c r="C432" s="55"/>
       <c r="D432" s="55"/>
-      <c r="E432" s="55"/>
+      <c r="E432" s="54"/>
       <c r="F432" s="55"/>
       <c r="G432" s="54"/>
     </row>
@@ -36920,7 +36928,7 @@
       <c r="B433" s="54"/>
       <c r="C433" s="55"/>
       <c r="D433" s="55"/>
-      <c r="E433" s="55"/>
+      <c r="E433" s="54"/>
       <c r="F433" s="55"/>
       <c r="G433" s="54"/>
     </row>
@@ -36928,7 +36936,7 @@
       <c r="B434" s="54"/>
       <c r="C434" s="55"/>
       <c r="D434" s="55"/>
-      <c r="E434" s="55"/>
+      <c r="E434" s="54"/>
       <c r="F434" s="55"/>
       <c r="G434" s="54"/>
     </row>
@@ -36936,7 +36944,7 @@
       <c r="B435" s="54"/>
       <c r="C435" s="55"/>
       <c r="D435" s="55"/>
-      <c r="E435" s="55"/>
+      <c r="E435" s="54"/>
       <c r="F435" s="55"/>
       <c r="G435" s="54"/>
     </row>
@@ -36944,7 +36952,7 @@
       <c r="B436" s="54"/>
       <c r="C436" s="55"/>
       <c r="D436" s="55"/>
-      <c r="E436" s="55"/>
+      <c r="E436" s="54"/>
       <c r="F436" s="55"/>
       <c r="G436" s="54"/>
     </row>
@@ -36952,7 +36960,7 @@
       <c r="B437" s="54"/>
       <c r="C437" s="55"/>
       <c r="D437" s="55"/>
-      <c r="E437" s="55"/>
+      <c r="E437" s="54"/>
       <c r="F437" s="55"/>
       <c r="G437" s="54"/>
     </row>
@@ -36960,7 +36968,7 @@
       <c r="B438" s="54"/>
       <c r="C438" s="55"/>
       <c r="D438" s="55"/>
-      <c r="E438" s="55"/>
+      <c r="E438" s="54"/>
       <c r="F438" s="55"/>
       <c r="G438" s="54"/>
     </row>
@@ -36968,7 +36976,7 @@
       <c r="B439" s="54"/>
       <c r="C439" s="55"/>
       <c r="D439" s="55"/>
-      <c r="E439" s="55"/>
+      <c r="E439" s="54"/>
       <c r="F439" s="55"/>
       <c r="G439" s="54"/>
     </row>
@@ -36976,7 +36984,7 @@
       <c r="B440" s="54"/>
       <c r="C440" s="55"/>
       <c r="D440" s="55"/>
-      <c r="E440" s="55"/>
+      <c r="E440" s="54"/>
       <c r="F440" s="55"/>
       <c r="G440" s="54"/>
     </row>
@@ -36984,7 +36992,7 @@
       <c r="B441" s="54"/>
       <c r="C441" s="55"/>
       <c r="D441" s="55"/>
-      <c r="E441" s="55"/>
+      <c r="E441" s="54"/>
       <c r="F441" s="55"/>
       <c r="G441" s="54"/>
     </row>
@@ -36992,7 +37000,7 @@
       <c r="B442" s="54"/>
       <c r="C442" s="55"/>
       <c r="D442" s="55"/>
-      <c r="E442" s="55"/>
+      <c r="E442" s="54"/>
       <c r="F442" s="55"/>
       <c r="G442" s="54"/>
     </row>
@@ -37000,7 +37008,7 @@
       <c r="B443" s="54"/>
       <c r="C443" s="55"/>
       <c r="D443" s="55"/>
-      <c r="E443" s="55"/>
+      <c r="E443" s="54"/>
       <c r="F443" s="55"/>
       <c r="G443" s="54"/>
     </row>
@@ -37008,7 +37016,7 @@
       <c r="B444" s="54"/>
       <c r="C444" s="55"/>
       <c r="D444" s="55"/>
-      <c r="E444" s="55"/>
+      <c r="E444" s="54"/>
       <c r="F444" s="55"/>
       <c r="G444" s="54"/>
     </row>
@@ -37016,7 +37024,7 @@
       <c r="B445" s="54"/>
       <c r="C445" s="55"/>
       <c r="D445" s="55"/>
-      <c r="E445" s="55"/>
+      <c r="E445" s="54"/>
       <c r="F445" s="55"/>
       <c r="G445" s="54"/>
     </row>
@@ -37024,7 +37032,7 @@
       <c r="B446" s="54"/>
       <c r="C446" s="55"/>
       <c r="D446" s="55"/>
-      <c r="E446" s="55"/>
+      <c r="E446" s="54"/>
       <c r="F446" s="55"/>
       <c r="G446" s="54"/>
     </row>
@@ -37032,7 +37040,7 @@
       <c r="B447" s="54"/>
       <c r="C447" s="55"/>
       <c r="D447" s="55"/>
-      <c r="E447" s="55"/>
+      <c r="E447" s="54"/>
       <c r="F447" s="55"/>
       <c r="G447" s="54"/>
     </row>
@@ -37040,7 +37048,7 @@
       <c r="B448" s="54"/>
       <c r="C448" s="55"/>
       <c r="D448" s="55"/>
-      <c r="E448" s="55"/>
+      <c r="E448" s="54"/>
       <c r="F448" s="55"/>
       <c r="G448" s="54"/>
     </row>
@@ -37048,7 +37056,7 @@
       <c r="B449" s="54"/>
       <c r="C449" s="55"/>
       <c r="D449" s="55"/>
-      <c r="E449" s="55"/>
+      <c r="E449" s="54"/>
       <c r="F449" s="55"/>
       <c r="G449" s="54"/>
     </row>
@@ -37056,7 +37064,7 @@
       <c r="B450" s="54"/>
       <c r="C450" s="55"/>
       <c r="D450" s="55"/>
-      <c r="E450" s="55"/>
+      <c r="E450" s="54"/>
       <c r="F450" s="55"/>
       <c r="G450" s="54"/>
     </row>
@@ -37064,7 +37072,7 @@
       <c r="B451" s="54"/>
       <c r="C451" s="55"/>
       <c r="D451" s="55"/>
-      <c r="E451" s="55"/>
+      <c r="E451" s="54"/>
       <c r="F451" s="55"/>
       <c r="G451" s="54"/>
     </row>
@@ -37072,7 +37080,7 @@
       <c r="B452" s="54"/>
       <c r="C452" s="55"/>
       <c r="D452" s="55"/>
-      <c r="E452" s="55"/>
+      <c r="E452" s="54"/>
       <c r="F452" s="55"/>
       <c r="G452" s="54"/>
     </row>
@@ -37080,7 +37088,7 @@
       <c r="B453" s="54"/>
       <c r="C453" s="55"/>
       <c r="D453" s="55"/>
-      <c r="E453" s="55"/>
+      <c r="E453" s="54"/>
       <c r="F453" s="55"/>
       <c r="G453" s="54"/>
     </row>
@@ -37088,7 +37096,7 @@
       <c r="B454" s="54"/>
       <c r="C454" s="55"/>
       <c r="D454" s="55"/>
-      <c r="E454" s="55"/>
+      <c r="E454" s="54"/>
       <c r="F454" s="55"/>
       <c r="G454" s="54"/>
     </row>
@@ -37096,7 +37104,7 @@
       <c r="B455" s="54"/>
       <c r="C455" s="55"/>
       <c r="D455" s="55"/>
-      <c r="E455" s="55"/>
+      <c r="E455" s="54"/>
       <c r="F455" s="55"/>
       <c r="G455" s="54"/>
     </row>
@@ -37104,7 +37112,7 @@
       <c r="B456" s="54"/>
       <c r="C456" s="55"/>
       <c r="D456" s="55"/>
-      <c r="E456" s="55"/>
+      <c r="E456" s="54"/>
       <c r="F456" s="55"/>
       <c r="G456" s="54"/>
     </row>
@@ -37112,7 +37120,7 @@
       <c r="B457" s="54"/>
       <c r="C457" s="55"/>
       <c r="D457" s="55"/>
-      <c r="E457" s="55"/>
+      <c r="E457" s="54"/>
       <c r="F457" s="55"/>
       <c r="G457" s="54"/>
     </row>
@@ -37120,7 +37128,7 @@
       <c r="B458" s="54"/>
       <c r="C458" s="55"/>
       <c r="D458" s="55"/>
-      <c r="E458" s="55"/>
+      <c r="E458" s="54"/>
       <c r="F458" s="55"/>
       <c r="G458" s="54"/>
     </row>
@@ -37128,7 +37136,7 @@
       <c r="B459" s="54"/>
       <c r="C459" s="55"/>
       <c r="D459" s="55"/>
-      <c r="E459" s="55"/>
+      <c r="E459" s="54"/>
       <c r="F459" s="55"/>
       <c r="G459" s="54"/>
     </row>
@@ -37136,7 +37144,7 @@
       <c r="B460" s="54"/>
       <c r="C460" s="55"/>
       <c r="D460" s="55"/>
-      <c r="E460" s="55"/>
+      <c r="E460" s="54"/>
       <c r="F460" s="55"/>
       <c r="G460" s="54"/>
     </row>
@@ -37144,7 +37152,7 @@
       <c r="B461" s="54"/>
       <c r="C461" s="55"/>
       <c r="D461" s="55"/>
-      <c r="E461" s="55"/>
+      <c r="E461" s="54"/>
       <c r="F461" s="55"/>
       <c r="G461" s="54"/>
     </row>
@@ -37152,7 +37160,7 @@
       <c r="B462" s="54"/>
       <c r="C462" s="55"/>
       <c r="D462" s="55"/>
-      <c r="E462" s="55"/>
+      <c r="E462" s="54"/>
       <c r="F462" s="55"/>
       <c r="G462" s="54"/>
     </row>
@@ -37160,7 +37168,7 @@
       <c r="B463" s="54"/>
       <c r="C463" s="55"/>
       <c r="D463" s="55"/>
-      <c r="E463" s="55"/>
+      <c r="E463" s="54"/>
       <c r="F463" s="55"/>
       <c r="G463" s="54"/>
     </row>
@@ -37168,7 +37176,7 @@
       <c r="B464" s="54"/>
       <c r="C464" s="55"/>
       <c r="D464" s="55"/>
-      <c r="E464" s="55"/>
+      <c r="E464" s="54"/>
       <c r="F464" s="55"/>
       <c r="G464" s="54"/>
     </row>
@@ -37176,7 +37184,7 @@
       <c r="B465" s="54"/>
       <c r="C465" s="55"/>
       <c r="D465" s="55"/>
-      <c r="E465" s="55"/>
+      <c r="E465" s="54"/>
       <c r="F465" s="55"/>
       <c r="G465" s="54"/>
     </row>
@@ -37184,7 +37192,7 @@
       <c r="B466" s="54"/>
       <c r="C466" s="55"/>
       <c r="D466" s="55"/>
-      <c r="E466" s="55"/>
+      <c r="E466" s="54"/>
       <c r="F466" s="55"/>
       <c r="G466" s="54"/>
     </row>
@@ -37192,7 +37200,7 @@
       <c r="B467" s="54"/>
       <c r="C467" s="55"/>
       <c r="D467" s="55"/>
-      <c r="E467" s="55"/>
+      <c r="E467" s="54"/>
       <c r="F467" s="55"/>
       <c r="G467" s="54"/>
     </row>
@@ -37200,7 +37208,7 @@
       <c r="B468" s="54"/>
       <c r="C468" s="55"/>
       <c r="D468" s="55"/>
-      <c r="E468" s="55"/>
+      <c r="E468" s="54"/>
       <c r="F468" s="55"/>
       <c r="G468" s="54"/>
     </row>
@@ -37208,7 +37216,7 @@
       <c r="B469" s="54"/>
       <c r="C469" s="55"/>
       <c r="D469" s="55"/>
-      <c r="E469" s="55"/>
+      <c r="E469" s="54"/>
       <c r="F469" s="55"/>
       <c r="G469" s="54"/>
     </row>
@@ -37216,7 +37224,7 @@
       <c r="B470" s="54"/>
       <c r="C470" s="55"/>
       <c r="D470" s="55"/>
-      <c r="E470" s="55"/>
+      <c r="E470" s="54"/>
       <c r="F470" s="55"/>
       <c r="G470" s="54"/>
     </row>
@@ -37224,7 +37232,7 @@
       <c r="B471" s="54"/>
       <c r="C471" s="55"/>
       <c r="D471" s="55"/>
-      <c r="E471" s="55"/>
+      <c r="E471" s="54"/>
       <c r="F471" s="55"/>
       <c r="G471" s="54"/>
     </row>
@@ -37232,7 +37240,7 @@
       <c r="B472" s="54"/>
       <c r="C472" s="55"/>
       <c r="D472" s="55"/>
-      <c r="E472" s="55"/>
+      <c r="E472" s="54"/>
       <c r="F472" s="55"/>
       <c r="G472" s="54"/>
     </row>
@@ -37240,7 +37248,7 @@
       <c r="B473" s="54"/>
       <c r="C473" s="55"/>
       <c r="D473" s="55"/>
-      <c r="E473" s="55"/>
+      <c r="E473" s="54"/>
       <c r="F473" s="55"/>
       <c r="G473" s="54"/>
     </row>
@@ -37248,7 +37256,7 @@
       <c r="B474" s="54"/>
       <c r="C474" s="55"/>
       <c r="D474" s="55"/>
-      <c r="E474" s="55"/>
+      <c r="E474" s="54"/>
       <c r="F474" s="55"/>
       <c r="G474" s="54"/>
     </row>
@@ -37256,7 +37264,7 @@
       <c r="B475" s="54"/>
       <c r="C475" s="55"/>
       <c r="D475" s="55"/>
-      <c r="E475" s="55"/>
+      <c r="E475" s="54"/>
       <c r="F475" s="55"/>
       <c r="G475" s="54"/>
     </row>
@@ -37264,7 +37272,7 @@
       <c r="B476" s="54"/>
       <c r="C476" s="55"/>
       <c r="D476" s="55"/>
-      <c r="E476" s="55"/>
+      <c r="E476" s="54"/>
       <c r="F476" s="55"/>
       <c r="G476" s="54"/>
     </row>
@@ -37272,7 +37280,7 @@
       <c r="B477" s="54"/>
       <c r="C477" s="55"/>
       <c r="D477" s="55"/>
-      <c r="E477" s="55"/>
+      <c r="E477" s="54"/>
       <c r="F477" s="55"/>
       <c r="G477" s="54"/>
     </row>
@@ -37280,7 +37288,7 @@
       <c r="B478" s="54"/>
       <c r="C478" s="55"/>
       <c r="D478" s="55"/>
-      <c r="E478" s="55"/>
+      <c r="E478" s="54"/>
       <c r="F478" s="55"/>
       <c r="G478" s="54"/>
     </row>
@@ -37288,7 +37296,7 @@
       <c r="B479" s="54"/>
       <c r="C479" s="55"/>
       <c r="D479" s="55"/>
-      <c r="E479" s="55"/>
+      <c r="E479" s="54"/>
       <c r="F479" s="55"/>
       <c r="G479" s="54"/>
     </row>
@@ -37296,7 +37304,7 @@
       <c r="B480" s="54"/>
       <c r="C480" s="55"/>
       <c r="D480" s="55"/>
-      <c r="E480" s="55"/>
+      <c r="E480" s="54"/>
       <c r="F480" s="55"/>
       <c r="G480" s="54"/>
     </row>
@@ -37304,7 +37312,7 @@
       <c r="B481" s="54"/>
       <c r="C481" s="55"/>
       <c r="D481" s="55"/>
-      <c r="E481" s="55"/>
+      <c r="E481" s="54"/>
       <c r="F481" s="55"/>
       <c r="G481" s="54"/>
     </row>
@@ -37312,7 +37320,7 @@
       <c r="B482" s="54"/>
       <c r="C482" s="55"/>
       <c r="D482" s="55"/>
-      <c r="E482" s="55"/>
+      <c r="E482" s="54"/>
       <c r="F482" s="55"/>
       <c r="G482" s="54"/>
     </row>
@@ -37320,7 +37328,7 @@
       <c r="B483" s="54"/>
       <c r="C483" s="55"/>
       <c r="D483" s="55"/>
-      <c r="E483" s="55"/>
+      <c r="E483" s="54"/>
       <c r="F483" s="55"/>
       <c r="G483" s="54"/>
     </row>
@@ -37328,7 +37336,7 @@
       <c r="B484" s="54"/>
       <c r="C484" s="55"/>
       <c r="D484" s="55"/>
-      <c r="E484" s="55"/>
+      <c r="E484" s="54"/>
       <c r="F484" s="55"/>
       <c r="G484" s="54"/>
     </row>
@@ -37336,7 +37344,7 @@
       <c r="B485" s="54"/>
       <c r="C485" s="55"/>
       <c r="D485" s="55"/>
-      <c r="E485" s="55"/>
+      <c r="E485" s="54"/>
       <c r="F485" s="55"/>
       <c r="G485" s="54"/>
     </row>
@@ -37344,7 +37352,7 @@
       <c r="B486" s="54"/>
       <c r="C486" s="55"/>
       <c r="D486" s="55"/>
-      <c r="E486" s="55"/>
+      <c r="E486" s="54"/>
       <c r="F486" s="55"/>
       <c r="G486" s="54"/>
     </row>
@@ -37352,7 +37360,7 @@
       <c r="B487" s="54"/>
       <c r="C487" s="55"/>
       <c r="D487" s="55"/>
-      <c r="E487" s="55"/>
+      <c r="E487" s="54"/>
       <c r="F487" s="55"/>
       <c r="G487" s="54"/>
     </row>
@@ -37360,7 +37368,7 @@
       <c r="B488" s="54"/>
       <c r="C488" s="55"/>
       <c r="D488" s="55"/>
-      <c r="E488" s="55"/>
+      <c r="E488" s="54"/>
       <c r="F488" s="55"/>
       <c r="G488" s="54"/>
     </row>
@@ -37368,7 +37376,7 @@
       <c r="B489" s="54"/>
       <c r="C489" s="55"/>
       <c r="D489" s="55"/>
-      <c r="E489" s="55"/>
+      <c r="E489" s="54"/>
       <c r="F489" s="55"/>
       <c r="G489" s="54"/>
     </row>
@@ -37376,7 +37384,7 @@
       <c r="B490" s="54"/>
       <c r="C490" s="55"/>
       <c r="D490" s="55"/>
-      <c r="E490" s="55"/>
+      <c r="E490" s="54"/>
       <c r="F490" s="55"/>
       <c r="G490" s="54"/>
     </row>
@@ -37384,7 +37392,7 @@
       <c r="B491" s="54"/>
       <c r="C491" s="55"/>
       <c r="D491" s="55"/>
-      <c r="E491" s="55"/>
+      <c r="E491" s="54"/>
       <c r="F491" s="55"/>
       <c r="G491" s="54"/>
     </row>
@@ -37392,7 +37400,7 @@
       <c r="B492" s="54"/>
       <c r="C492" s="55"/>
       <c r="D492" s="55"/>
-      <c r="E492" s="55"/>
+      <c r="E492" s="54"/>
       <c r="F492" s="55"/>
       <c r="G492" s="54"/>
     </row>
@@ -37400,7 +37408,7 @@
       <c r="B493" s="54"/>
       <c r="C493" s="55"/>
       <c r="D493" s="55"/>
-      <c r="E493" s="55"/>
+      <c r="E493" s="54"/>
       <c r="F493" s="55"/>
       <c r="G493" s="54"/>
     </row>
@@ -37408,7 +37416,7 @@
       <c r="B494" s="54"/>
       <c r="C494" s="55"/>
       <c r="D494" s="55"/>
-      <c r="E494" s="55"/>
+      <c r="E494" s="54"/>
       <c r="F494" s="55"/>
       <c r="G494" s="54"/>
     </row>
@@ -37416,7 +37424,7 @@
       <c r="B495" s="54"/>
       <c r="C495" s="55"/>
       <c r="D495" s="55"/>
-      <c r="E495" s="55"/>
+      <c r="E495" s="54"/>
       <c r="F495" s="55"/>
       <c r="G495" s="54"/>
     </row>
@@ -37424,7 +37432,7 @@
       <c r="B496" s="54"/>
       <c r="C496" s="55"/>
       <c r="D496" s="55"/>
-      <c r="E496" s="55"/>
+      <c r="E496" s="54"/>
       <c r="F496" s="55"/>
       <c r="G496" s="54"/>
     </row>
@@ -37432,7 +37440,7 @@
       <c r="B497" s="54"/>
       <c r="C497" s="55"/>
       <c r="D497" s="55"/>
-      <c r="E497" s="55"/>
+      <c r="E497" s="54"/>
       <c r="F497" s="55"/>
       <c r="G497" s="54"/>
     </row>
@@ -37440,7 +37448,7 @@
       <c r="B498" s="54"/>
       <c r="C498" s="55"/>
       <c r="D498" s="55"/>
-      <c r="E498" s="55"/>
+      <c r="E498" s="54"/>
       <c r="F498" s="55"/>
       <c r="G498" s="54"/>
     </row>
@@ -37448,7 +37456,7 @@
       <c r="B499" s="54"/>
       <c r="C499" s="55"/>
       <c r="D499" s="55"/>
-      <c r="E499" s="55"/>
+      <c r="E499" s="54"/>
       <c r="F499" s="55"/>
       <c r="G499" s="54"/>
     </row>
@@ -37456,7 +37464,7 @@
       <c r="B500" s="54"/>
       <c r="C500" s="55"/>
       <c r="D500" s="55"/>
-      <c r="E500" s="55"/>
+      <c r="E500" s="54"/>
       <c r="F500" s="55"/>
       <c r="G500" s="54"/>
     </row>
@@ -37464,7 +37472,7 @@
       <c r="B501" s="54"/>
       <c r="C501" s="55"/>
       <c r="D501" s="55"/>
-      <c r="E501" s="55"/>
+      <c r="E501" s="54"/>
       <c r="F501" s="55"/>
       <c r="G501" s="54"/>
     </row>
@@ -37472,7 +37480,7 @@
       <c r="B502" s="54"/>
       <c r="C502" s="55"/>
       <c r="D502" s="55"/>
-      <c r="E502" s="55"/>
+      <c r="E502" s="54"/>
       <c r="F502" s="55"/>
       <c r="G502" s="54"/>
     </row>
@@ -37480,7 +37488,7 @@
       <c r="B503" s="54"/>
       <c r="C503" s="55"/>
       <c r="D503" s="55"/>
-      <c r="E503" s="55"/>
+      <c r="E503" s="54"/>
       <c r="F503" s="55"/>
       <c r="G503" s="54"/>
     </row>
@@ -37488,7 +37496,7 @@
       <c r="B504" s="54"/>
       <c r="C504" s="55"/>
       <c r="D504" s="55"/>
-      <c r="E504" s="55"/>
+      <c r="E504" s="54"/>
       <c r="F504" s="55"/>
       <c r="G504" s="54"/>
     </row>
@@ -37496,7 +37504,7 @@
       <c r="B505" s="54"/>
       <c r="C505" s="55"/>
       <c r="D505" s="55"/>
-      <c r="E505" s="55"/>
+      <c r="E505" s="54"/>
       <c r="F505" s="55"/>
       <c r="G505" s="54"/>
     </row>
@@ -37504,7 +37512,7 @@
       <c r="B506" s="54"/>
       <c r="C506" s="55"/>
       <c r="D506" s="55"/>
-      <c r="E506" s="55"/>
+      <c r="E506" s="54"/>
       <c r="F506" s="55"/>
       <c r="G506" s="54"/>
     </row>
@@ -37512,7 +37520,7 @@
       <c r="B507" s="54"/>
       <c r="C507" s="55"/>
       <c r="D507" s="55"/>
-      <c r="E507" s="55"/>
+      <c r="E507" s="54"/>
       <c r="F507" s="55"/>
       <c r="G507" s="54"/>
     </row>
@@ -37520,7 +37528,7 @@
       <c r="B508" s="54"/>
       <c r="C508" s="55"/>
       <c r="D508" s="55"/>
-      <c r="E508" s="55"/>
+      <c r="E508" s="54"/>
       <c r="F508" s="55"/>
       <c r="G508" s="54"/>
     </row>
@@ -37528,7 +37536,7 @@
       <c r="B509" s="54"/>
       <c r="C509" s="55"/>
       <c r="D509" s="55"/>
-      <c r="E509" s="55"/>
+      <c r="E509" s="54"/>
       <c r="F509" s="55"/>
       <c r="G509" s="54"/>
     </row>
@@ -37536,7 +37544,7 @@
       <c r="B510" s="54"/>
       <c r="C510" s="55"/>
       <c r="D510" s="55"/>
-      <c r="E510" s="55"/>
+      <c r="E510" s="54"/>
       <c r="F510" s="55"/>
       <c r="G510" s="54"/>
     </row>
@@ -37544,7 +37552,7 @@
       <c r="B511" s="54"/>
       <c r="C511" s="55"/>
       <c r="D511" s="55"/>
-      <c r="E511" s="55"/>
+      <c r="E511" s="54"/>
       <c r="F511" s="55"/>
       <c r="G511" s="54"/>
     </row>
@@ -37552,7 +37560,7 @@
       <c r="B512" s="54"/>
       <c r="C512" s="55"/>
       <c r="D512" s="55"/>
-      <c r="E512" s="55"/>
+      <c r="E512" s="54"/>
       <c r="F512" s="55"/>
       <c r="G512" s="54"/>
     </row>
@@ -37560,7 +37568,7 @@
       <c r="B513" s="54"/>
       <c r="C513" s="55"/>
       <c r="D513" s="55"/>
-      <c r="E513" s="55"/>
+      <c r="E513" s="54"/>
       <c r="F513" s="55"/>
       <c r="G513" s="54"/>
     </row>
@@ -37568,7 +37576,7 @@
       <c r="B514" s="54"/>
       <c r="C514" s="55"/>
       <c r="D514" s="55"/>
-      <c r="E514" s="55"/>
+      <c r="E514" s="54"/>
       <c r="F514" s="55"/>
       <c r="G514" s="54"/>
     </row>
@@ -37576,7 +37584,7 @@
       <c r="B515" s="54"/>
       <c r="C515" s="55"/>
       <c r="D515" s="55"/>
-      <c r="E515" s="55"/>
+      <c r="E515" s="54"/>
       <c r="F515" s="55"/>
       <c r="G515" s="54"/>
     </row>
@@ -37584,7 +37592,7 @@
       <c r="B516" s="54"/>
       <c r="C516" s="55"/>
       <c r="D516" s="55"/>
-      <c r="E516" s="55"/>
+      <c r="E516" s="54"/>
       <c r="F516" s="55"/>
       <c r="G516" s="54"/>
     </row>
@@ -37592,7 +37600,7 @@
       <c r="B517" s="54"/>
       <c r="C517" s="55"/>
       <c r="D517" s="55"/>
-      <c r="E517" s="55"/>
+      <c r="E517" s="54"/>
       <c r="F517" s="55"/>
       <c r="G517" s="54"/>
     </row>
@@ -37600,7 +37608,7 @@
       <c r="B518" s="54"/>
       <c r="C518" s="55"/>
       <c r="D518" s="55"/>
-      <c r="E518" s="55"/>
+      <c r="E518" s="54"/>
       <c r="F518" s="55"/>
       <c r="G518" s="54"/>
     </row>
@@ -37608,7 +37616,7 @@
       <c r="B519" s="54"/>
       <c r="C519" s="55"/>
       <c r="D519" s="55"/>
-      <c r="E519" s="55"/>
+      <c r="E519" s="54"/>
       <c r="F519" s="55"/>
       <c r="G519" s="54"/>
     </row>
@@ -37616,7 +37624,7 @@
       <c r="B520" s="54"/>
       <c r="C520" s="55"/>
       <c r="D520" s="55"/>
-      <c r="E520" s="55"/>
+      <c r="E520" s="54"/>
       <c r="F520" s="55"/>
       <c r="G520" s="54"/>
     </row>
@@ -37624,7 +37632,7 @@
       <c r="B521" s="54"/>
       <c r="C521" s="55"/>
       <c r="D521" s="55"/>
-      <c r="E521" s="55"/>
+      <c r="E521" s="54"/>
       <c r="F521" s="55"/>
       <c r="G521" s="54"/>
     </row>
@@ -37632,7 +37640,7 @@
       <c r="B522" s="54"/>
       <c r="C522" s="55"/>
       <c r="D522" s="55"/>
-      <c r="E522" s="55"/>
+      <c r="E522" s="54"/>
       <c r="F522" s="55"/>
       <c r="G522" s="54"/>
     </row>
@@ -37640,7 +37648,7 @@
       <c r="B523" s="54"/>
       <c r="C523" s="55"/>
       <c r="D523" s="55"/>
-      <c r="E523" s="55"/>
+      <c r="E523" s="54"/>
       <c r="F523" s="55"/>
       <c r="G523" s="54"/>
     </row>
@@ -37648,7 +37656,7 @@
       <c r="B524" s="54"/>
       <c r="C524" s="55"/>
       <c r="D524" s="55"/>
-      <c r="E524" s="55"/>
+      <c r="E524" s="54"/>
       <c r="F524" s="55"/>
       <c r="G524" s="54"/>
     </row>
@@ -37656,7 +37664,7 @@
       <c r="B525" s="54"/>
       <c r="C525" s="55"/>
       <c r="D525" s="55"/>
-      <c r="E525" s="55"/>
+      <c r="E525" s="54"/>
       <c r="F525" s="55"/>
       <c r="G525" s="54"/>
     </row>
@@ -37664,7 +37672,7 @@
       <c r="B526" s="54"/>
       <c r="C526" s="55"/>
       <c r="D526" s="55"/>
-      <c r="E526" s="55"/>
+      <c r="E526" s="54"/>
       <c r="F526" s="55"/>
       <c r="G526" s="54"/>
     </row>
@@ -37672,7 +37680,7 @@
       <c r="B527" s="54"/>
       <c r="C527" s="55"/>
       <c r="D527" s="55"/>
-      <c r="E527" s="55"/>
+      <c r="E527" s="54"/>
       <c r="F527" s="55"/>
       <c r="G527" s="54"/>
     </row>
@@ -37680,7 +37688,7 @@
       <c r="B528" s="54"/>
       <c r="C528" s="55"/>
       <c r="D528" s="55"/>
-      <c r="E528" s="55"/>
+      <c r="E528" s="54"/>
       <c r="F528" s="55"/>
       <c r="G528" s="54"/>
     </row>
@@ -37688,7 +37696,7 @@
       <c r="B529" s="54"/>
       <c r="C529" s="55"/>
       <c r="D529" s="55"/>
-      <c r="E529" s="55"/>
+      <c r="E529" s="54"/>
       <c r="F529" s="55"/>
       <c r="G529" s="54"/>
     </row>
@@ -37696,7 +37704,7 @@
       <c r="B530" s="54"/>
       <c r="C530" s="55"/>
       <c r="D530" s="55"/>
-      <c r="E530" s="55"/>
+      <c r="E530" s="54"/>
       <c r="F530" s="55"/>
       <c r="G530" s="54"/>
     </row>
@@ -37704,7 +37712,7 @@
       <c r="B531" s="54"/>
       <c r="C531" s="55"/>
       <c r="D531" s="55"/>
-      <c r="E531" s="55"/>
+      <c r="E531" s="54"/>
       <c r="F531" s="55"/>
       <c r="G531" s="54"/>
     </row>
@@ -37712,7 +37720,7 @@
       <c r="B532" s="54"/>
       <c r="C532" s="55"/>
       <c r="D532" s="55"/>
-      <c r="E532" s="55"/>
+      <c r="E532" s="54"/>
       <c r="F532" s="55"/>
       <c r="G532" s="54"/>
     </row>
@@ -37720,7 +37728,7 @@
       <c r="B533" s="54"/>
       <c r="C533" s="55"/>
       <c r="D533" s="55"/>
-      <c r="E533" s="55"/>
+      <c r="E533" s="54"/>
       <c r="F533" s="55"/>
       <c r="G533" s="54"/>
     </row>
@@ -37728,7 +37736,7 @@
       <c r="B534" s="54"/>
       <c r="C534" s="55"/>
       <c r="D534" s="55"/>
-      <c r="E534" s="55"/>
+      <c r="E534" s="54"/>
       <c r="F534" s="55"/>
       <c r="G534" s="54"/>
     </row>
@@ -37736,7 +37744,7 @@
       <c r="B535" s="54"/>
       <c r="C535" s="55"/>
       <c r="D535" s="55"/>
-      <c r="E535" s="55"/>
+      <c r="E535" s="54"/>
       <c r="F535" s="55"/>
       <c r="G535" s="54"/>
     </row>
@@ -37744,7 +37752,7 @@
       <c r="B536" s="54"/>
       <c r="C536" s="55"/>
       <c r="D536" s="55"/>
-      <c r="E536" s="55"/>
+      <c r="E536" s="54"/>
       <c r="F536" s="55"/>
       <c r="G536" s="54"/>
     </row>
@@ -37752,7 +37760,7 @@
       <c r="B537" s="54"/>
       <c r="C537" s="55"/>
       <c r="D537" s="55"/>
-      <c r="E537" s="55"/>
+      <c r="E537" s="54"/>
       <c r="F537" s="55"/>
       <c r="G537" s="54"/>
     </row>
@@ -37760,7 +37768,7 @@
       <c r="B538" s="54"/>
       <c r="C538" s="55"/>
       <c r="D538" s="55"/>
-      <c r="E538" s="55"/>
+      <c r="E538" s="54"/>
       <c r="F538" s="55"/>
       <c r="G538" s="54"/>
     </row>
@@ -37768,7 +37776,7 @@
       <c r="B539" s="54"/>
       <c r="C539" s="55"/>
       <c r="D539" s="55"/>
-      <c r="E539" s="55"/>
+      <c r="E539" s="54"/>
       <c r="F539" s="55"/>
       <c r="G539" s="54"/>
     </row>
@@ -37776,7 +37784,7 @@
       <c r="B540" s="54"/>
       <c r="C540" s="55"/>
       <c r="D540" s="55"/>
-      <c r="E540" s="55"/>
+      <c r="E540" s="54"/>
       <c r="F540" s="55"/>
       <c r="G540" s="54"/>
     </row>
@@ -37784,7 +37792,7 @@
       <c r="B541" s="54"/>
       <c r="C541" s="55"/>
       <c r="D541" s="55"/>
-      <c r="E541" s="55"/>
+      <c r="E541" s="54"/>
       <c r="F541" s="55"/>
       <c r="G541" s="54"/>
     </row>
@@ -37792,7 +37800,7 @@
       <c r="B542" s="54"/>
       <c r="C542" s="55"/>
       <c r="D542" s="55"/>
-      <c r="E542" s="55"/>
+      <c r="E542" s="54"/>
       <c r="F542" s="55"/>
       <c r="G542" s="54"/>
     </row>
@@ -37800,7 +37808,7 @@
       <c r="B543" s="54"/>
       <c r="C543" s="55"/>
       <c r="D543" s="55"/>
-      <c r="E543" s="55"/>
+      <c r="E543" s="54"/>
       <c r="F543" s="55"/>
       <c r="G543" s="54"/>
     </row>
@@ -37808,7 +37816,7 @@
       <c r="B544" s="54"/>
       <c r="C544" s="55"/>
       <c r="D544" s="55"/>
-      <c r="E544" s="55"/>
+      <c r="E544" s="54"/>
       <c r="F544" s="55"/>
       <c r="G544" s="54"/>
     </row>
@@ -37816,7 +37824,7 @@
       <c r="B545" s="54"/>
       <c r="C545" s="55"/>
       <c r="D545" s="55"/>
-      <c r="E545" s="55"/>
+      <c r="E545" s="54"/>
       <c r="F545" s="55"/>
       <c r="G545" s="54"/>
     </row>
@@ -37824,7 +37832,7 @@
       <c r="B546" s="54"/>
       <c r="C546" s="55"/>
       <c r="D546" s="55"/>
-      <c r="E546" s="55"/>
+      <c r="E546" s="54"/>
       <c r="F546" s="55"/>
       <c r="G546" s="54"/>
     </row>
@@ -37832,7 +37840,7 @@
       <c r="B547" s="54"/>
       <c r="C547" s="55"/>
       <c r="D547" s="55"/>
-      <c r="E547" s="55"/>
+      <c r="E547" s="54"/>
       <c r="F547" s="55"/>
       <c r="G547" s="54"/>
     </row>
@@ -37840,7 +37848,7 @@
       <c r="B548" s="54"/>
       <c r="C548" s="55"/>
       <c r="D548" s="55"/>
-      <c r="E548" s="55"/>
+      <c r="E548" s="54"/>
       <c r="F548" s="55"/>
       <c r="G548" s="54"/>
     </row>
@@ -37848,7 +37856,7 @@
       <c r="B549" s="54"/>
       <c r="C549" s="55"/>
       <c r="D549" s="55"/>
-      <c r="E549" s="55"/>
+      <c r="E549" s="54"/>
       <c r="F549" s="55"/>
       <c r="G549" s="54"/>
     </row>
@@ -37856,7 +37864,7 @@
       <c r="B550" s="54"/>
       <c r="C550" s="55"/>
       <c r="D550" s="55"/>
-      <c r="E550" s="55"/>
+      <c r="E550" s="54"/>
       <c r="F550" s="55"/>
       <c r="G550" s="54"/>
     </row>
@@ -37864,7 +37872,7 @@
       <c r="B551" s="54"/>
       <c r="C551" s="55"/>
       <c r="D551" s="55"/>
-      <c r="E551" s="55"/>
+      <c r="E551" s="54"/>
       <c r="F551" s="55"/>
       <c r="G551" s="54"/>
     </row>
@@ -37872,7 +37880,7 @@
       <c r="B552" s="54"/>
       <c r="C552" s="55"/>
       <c r="D552" s="55"/>
-      <c r="E552" s="55"/>
+      <c r="E552" s="54"/>
       <c r="F552" s="55"/>
       <c r="G552" s="54"/>
     </row>
@@ -37880,7 +37888,7 @@
       <c r="B553" s="54"/>
       <c r="C553" s="55"/>
       <c r="D553" s="55"/>
-      <c r="E553" s="55"/>
+      <c r="E553" s="54"/>
       <c r="F553" s="55"/>
       <c r="G553" s="54"/>
     </row>
@@ -37888,7 +37896,7 @@
       <c r="B554" s="54"/>
       <c r="C554" s="55"/>
       <c r="D554" s="55"/>
-      <c r="E554" s="55"/>
+      <c r="E554" s="54"/>
       <c r="F554" s="55"/>
       <c r="G554" s="54"/>
     </row>
@@ -37896,7 +37904,7 @@
       <c r="B555" s="54"/>
       <c r="C555" s="55"/>
       <c r="D555" s="55"/>
-      <c r="E555" s="55"/>
+      <c r="E555" s="54"/>
       <c r="F555" s="55"/>
       <c r="G555" s="54"/>
     </row>
@@ -37904,7 +37912,7 @@
       <c r="B556" s="54"/>
       <c r="C556" s="55"/>
       <c r="D556" s="55"/>
-      <c r="E556" s="55"/>
+      <c r="E556" s="54"/>
       <c r="F556" s="55"/>
       <c r="G556" s="54"/>
     </row>
@@ -37912,7 +37920,7 @@
       <c r="B557" s="54"/>
       <c r="C557" s="55"/>
       <c r="D557" s="55"/>
-      <c r="E557" s="55"/>
+      <c r="E557" s="54"/>
       <c r="F557" s="55"/>
       <c r="G557" s="54"/>
     </row>
@@ -37920,7 +37928,7 @@
       <c r="B558" s="54"/>
       <c r="C558" s="55"/>
       <c r="D558" s="55"/>
-      <c r="E558" s="55"/>
+      <c r="E558" s="54"/>
       <c r="F558" s="55"/>
       <c r="G558" s="54"/>
     </row>
@@ -37928,7 +37936,7 @@
       <c r="B559" s="54"/>
       <c r="C559" s="55"/>
       <c r="D559" s="55"/>
-      <c r="E559" s="55"/>
+      <c r="E559" s="54"/>
       <c r="F559" s="55"/>
       <c r="G559" s="54"/>
     </row>
@@ -37936,7 +37944,7 @@
       <c r="B560" s="54"/>
       <c r="C560" s="55"/>
       <c r="D560" s="55"/>
-      <c r="E560" s="55"/>
+      <c r="E560" s="54"/>
       <c r="F560" s="55"/>
       <c r="G560" s="54"/>
     </row>
@@ -37944,7 +37952,7 @@
       <c r="B561" s="54"/>
       <c r="C561" s="55"/>
       <c r="D561" s="55"/>
-      <c r="E561" s="55"/>
+      <c r="E561" s="54"/>
       <c r="F561" s="55"/>
       <c r="G561" s="54"/>
     </row>
@@ -37952,7 +37960,7 @@
       <c r="B562" s="54"/>
       <c r="C562" s="55"/>
       <c r="D562" s="55"/>
-      <c r="E562" s="55"/>
+      <c r="E562" s="54"/>
       <c r="F562" s="55"/>
       <c r="G562" s="54"/>
     </row>
@@ -37960,7 +37968,7 @@
       <c r="B563" s="54"/>
       <c r="C563" s="55"/>
       <c r="D563" s="55"/>
-      <c r="E563" s="55"/>
+      <c r="E563" s="54"/>
       <c r="F563" s="55"/>
       <c r="G563" s="54"/>
     </row>
@@ -37968,7 +37976,7 @@
       <c r="B564" s="54"/>
       <c r="C564" s="55"/>
       <c r="D564" s="55"/>
-      <c r="E564" s="55"/>
+      <c r="E564" s="54"/>
       <c r="F564" s="55"/>
       <c r="G564" s="54"/>
     </row>
@@ -37976,7 +37984,7 @@
       <c r="B565" s="54"/>
       <c r="C565" s="55"/>
       <c r="D565" s="55"/>
-      <c r="E565" s="55"/>
+      <c r="E565" s="54"/>
       <c r="F565" s="55"/>
       <c r="G565" s="54"/>
     </row>
@@ -37984,7 +37992,7 @@
       <c r="B566" s="54"/>
       <c r="C566" s="55"/>
       <c r="D566" s="55"/>
-      <c r="E566" s="55"/>
+      <c r="E566" s="54"/>
       <c r="F566" s="55"/>
       <c r="G566" s="54"/>
     </row>
@@ -37992,7 +38000,7 @@
       <c r="B567" s="54"/>
       <c r="C567" s="55"/>
       <c r="D567" s="55"/>
-      <c r="E567" s="55"/>
+      <c r="E567" s="54"/>
       <c r="F567" s="55"/>
       <c r="G567" s="54"/>
     </row>
@@ -38000,7 +38008,7 @@
       <c r="B568" s="54"/>
       <c r="C568" s="55"/>
       <c r="D568" s="55"/>
-      <c r="E568" s="55"/>
+      <c r="E568" s="54"/>
       <c r="F568" s="55"/>
       <c r="G568" s="54"/>
     </row>
@@ -38008,7 +38016,7 @@
       <c r="B569" s="54"/>
       <c r="C569" s="55"/>
       <c r="D569" s="55"/>
-      <c r="E569" s="55"/>
+      <c r="E569" s="54"/>
       <c r="F569" s="55"/>
       <c r="G569" s="54"/>
     </row>
@@ -38016,7 +38024,7 @@
       <c r="B570" s="54"/>
       <c r="C570" s="55"/>
       <c r="D570" s="55"/>
-      <c r="E570" s="55"/>
+      <c r="E570" s="54"/>
       <c r="F570" s="55"/>
       <c r="G570" s="54"/>
     </row>
@@ -38024,7 +38032,7 @@
       <c r="B571" s="54"/>
       <c r="C571" s="55"/>
       <c r="D571" s="55"/>
-      <c r="E571" s="55"/>
+      <c r="E571" s="54"/>
       <c r="F571" s="55"/>
       <c r="G571" s="54"/>
     </row>
@@ -38032,7 +38040,7 @@
       <c r="B572" s="54"/>
       <c r="C572" s="55"/>
       <c r="D572" s="55"/>
-      <c r="E572" s="55"/>
+      <c r="E572" s="54"/>
       <c r="F572" s="55"/>
       <c r="G572" s="54"/>
     </row>
@@ -38040,7 +38048,7 @@
       <c r="B573" s="54"/>
       <c r="C573" s="55"/>
       <c r="D573" s="55"/>
-      <c r="E573" s="55"/>
+      <c r="E573" s="54"/>
       <c r="F573" s="55"/>
       <c r="G573" s="54"/>
     </row>
@@ -38048,7 +38056,7 @@
       <c r="B574" s="54"/>
       <c r="C574" s="55"/>
       <c r="D574" s="55"/>
-      <c r="E574" s="55"/>
+      <c r="E574" s="54"/>
       <c r="F574" s="55"/>
       <c r="G574" s="54"/>
     </row>
@@ -38056,7 +38064,7 @@
       <c r="B575" s="54"/>
       <c r="C575" s="55"/>
       <c r="D575" s="55"/>
-      <c r="E575" s="55"/>
+      <c r="E575" s="54"/>
       <c r="F575" s="55"/>
       <c r="G575" s="54"/>
     </row>
@@ -38064,7 +38072,7 @@
       <c r="B576" s="54"/>
       <c r="C576" s="55"/>
       <c r="D576" s="55"/>
-      <c r="E576" s="55"/>
+      <c r="E576" s="54"/>
       <c r="F576" s="55"/>
       <c r="G576" s="54"/>
     </row>
@@ -38072,7 +38080,7 @@
       <c r="B577" s="54"/>
       <c r="C577" s="55"/>
       <c r="D577" s="55"/>
-      <c r="E577" s="55"/>
+      <c r="E577" s="54"/>
       <c r="F577" s="55"/>
       <c r="G577" s="54"/>
     </row>
@@ -38080,7 +38088,7 @@
       <c r="B578" s="54"/>
       <c r="C578" s="55"/>
       <c r="D578" s="55"/>
-      <c r="E578" s="55"/>
+      <c r="E578" s="54"/>
       <c r="F578" s="55"/>
       <c r="G578" s="54"/>
     </row>
@@ -38088,7 +38096,7 @@
       <c r="B579" s="54"/>
       <c r="C579" s="55"/>
       <c r="D579" s="55"/>
-      <c r="E579" s="55"/>
+      <c r="E579" s="54"/>
       <c r="F579" s="55"/>
       <c r="G579" s="54"/>
     </row>
@@ -38096,7 +38104,7 @@
       <c r="B580" s="54"/>
       <c r="C580" s="55"/>
       <c r="D580" s="55"/>
-      <c r="E580" s="55"/>
+      <c r="E580" s="54"/>
       <c r="F580" s="55"/>
       <c r="G580" s="54"/>
     </row>
@@ -38104,7 +38112,7 @@
       <c r="B581" s="54"/>
       <c r="C581" s="55"/>
       <c r="D581" s="55"/>
-      <c r="E581" s="55"/>
+      <c r="E581" s="54"/>
       <c r="F581" s="55"/>
       <c r="G581" s="54"/>
     </row>
@@ -38112,7 +38120,7 @@
       <c r="B582" s="54"/>
       <c r="C582" s="55"/>
       <c r="D582" s="55"/>
-      <c r="E582" s="55"/>
+      <c r="E582" s="54"/>
       <c r="F582" s="55"/>
       <c r="G582" s="54"/>
     </row>
@@ -38120,7 +38128,7 @@
       <c r="B583" s="54"/>
       <c r="C583" s="55"/>
       <c r="D583" s="55"/>
-      <c r="E583" s="55"/>
+      <c r="E583" s="54"/>
       <c r="F583" s="55"/>
       <c r="G583" s="54"/>
     </row>
@@ -38128,7 +38136,7 @@
       <c r="B584" s="54"/>
       <c r="C584" s="55"/>
       <c r="D584" s="55"/>
-      <c r="E584" s="55"/>
+      <c r="E584" s="54"/>
       <c r="F584" s="55"/>
       <c r="G584" s="54"/>
     </row>
@@ -38136,7 +38144,7 @@
       <c r="B585" s="54"/>
       <c r="C585" s="55"/>
       <c r="D585" s="55"/>
-      <c r="E585" s="55"/>
+      <c r="E585" s="54"/>
       <c r="F585" s="55"/>
       <c r="G585" s="54"/>
     </row>
@@ -38144,7 +38152,7 @@
       <c r="B586" s="54"/>
       <c r="C586" s="55"/>
       <c r="D586" s="55"/>
-      <c r="E586" s="55"/>
+      <c r="E586" s="54"/>
       <c r="F586" s="55"/>
       <c r="G586" s="54"/>
     </row>
@@ -38152,7 +38160,7 @@
       <c r="B587" s="54"/>
       <c r="C587" s="55"/>
       <c r="D587" s="55"/>
-      <c r="E587" s="55"/>
+      <c r="E587" s="54"/>
       <c r="F587" s="55"/>
       <c r="G587" s="54"/>
     </row>
@@ -38160,7 +38168,7 @@
       <c r="B588" s="54"/>
       <c r="C588" s="55"/>
       <c r="D588" s="55"/>
-      <c r="E588" s="55"/>
+      <c r="E588" s="54"/>
       <c r="F588" s="55"/>
       <c r="G588" s="54"/>
     </row>
@@ -38168,7 +38176,7 @@
       <c r="B589" s="54"/>
       <c r="C589" s="55"/>
       <c r="D589" s="55"/>
-      <c r="E589" s="55"/>
+      <c r="E589" s="54"/>
       <c r="F589" s="55"/>
       <c r="G589" s="54"/>
     </row>
@@ -38176,7 +38184,7 @@
       <c r="B590" s="54"/>
       <c r="C590" s="55"/>
       <c r="D590" s="55"/>
-      <c r="E590" s="55"/>
+      <c r="E590" s="54"/>
       <c r="F590" s="55"/>
       <c r="G590" s="54"/>
     </row>
@@ -38184,7 +38192,7 @@
       <c r="B591" s="54"/>
       <c r="C591" s="55"/>
       <c r="D591" s="55"/>
-      <c r="E591" s="55"/>
+      <c r="E591" s="54"/>
       <c r="F591" s="55"/>
       <c r="G591" s="54"/>
     </row>
@@ -38192,7 +38200,7 @@
       <c r="B592" s="54"/>
       <c r="C592" s="55"/>
       <c r="D592" s="55"/>
-      <c r="E592" s="55"/>
+      <c r="E592" s="54"/>
       <c r="F592" s="55"/>
       <c r="G592" s="54"/>
     </row>
@@ -38200,7 +38208,7 @@
       <c r="B593" s="54"/>
       <c r="C593" s="55"/>
       <c r="D593" s="55"/>
-      <c r="E593" s="55"/>
+      <c r="E593" s="54"/>
       <c r="F593" s="55"/>
       <c r="G593" s="54"/>
     </row>
@@ -38208,7 +38216,7 @@
       <c r="B594" s="54"/>
       <c r="C594" s="55"/>
       <c r="D594" s="55"/>
-      <c r="E594" s="55"/>
+      <c r="E594" s="54"/>
       <c r="F594" s="55"/>
       <c r="G594" s="54"/>
     </row>
@@ -38216,7 +38224,7 @@
       <c r="B595" s="54"/>
       <c r="C595" s="55"/>
       <c r="D595" s="55"/>
-      <c r="E595" s="55"/>
+      <c r="E595" s="54"/>
       <c r="F595" s="55"/>
       <c r="G595" s="54"/>
     </row>
@@ -38224,7 +38232,7 @@
       <c r="B596" s="54"/>
       <c r="C596" s="55"/>
       <c r="D596" s="55"/>
-      <c r="E596" s="55"/>
+      <c r="E596" s="54"/>
       <c r="F596" s="55"/>
       <c r="G596" s="54"/>
     </row>
@@ -38232,7 +38240,7 @@
       <c r="B597" s="54"/>
       <c r="C597" s="55"/>
       <c r="D597" s="55"/>
-      <c r="E597" s="55"/>
+      <c r="E597" s="54"/>
       <c r="F597" s="55"/>
       <c r="G597" s="54"/>
     </row>
@@ -38240,7 +38248,7 @@
       <c r="B598" s="54"/>
       <c r="C598" s="55"/>
       <c r="D598" s="55"/>
-      <c r="E598" s="55"/>
+      <c r="E598" s="54"/>
       <c r="F598" s="55"/>
       <c r="G598" s="54"/>
     </row>
@@ -38248,7 +38256,7 @@
       <c r="B599" s="54"/>
       <c r="C599" s="55"/>
       <c r="D599" s="55"/>
-      <c r="E599" s="55"/>
+      <c r="E599" s="54"/>
       <c r="F599" s="55"/>
       <c r="G599" s="54"/>
     </row>
@@ -38256,7 +38264,7 @@
       <c r="B600" s="54"/>
       <c r="C600" s="55"/>
       <c r="D600" s="55"/>
-      <c r="E600" s="55"/>
+      <c r="E600" s="54"/>
       <c r="F600" s="55"/>
       <c r="G600" s="54"/>
     </row>
@@ -38264,7 +38272,7 @@
       <c r="B601" s="54"/>
       <c r="C601" s="55"/>
       <c r="D601" s="55"/>
-      <c r="E601" s="55"/>
+      <c r="E601" s="54"/>
       <c r="F601" s="55"/>
       <c r="G601" s="54"/>
     </row>
@@ -38272,7 +38280,7 @@
       <c r="B602" s="54"/>
       <c r="C602" s="55"/>
       <c r="D602" s="55"/>
-      <c r="E602" s="55"/>
+      <c r="E602" s="54"/>
       <c r="F602" s="55"/>
       <c r="G602" s="54"/>
     </row>
@@ -38280,7 +38288,7 @@
       <c r="B603" s="54"/>
       <c r="C603" s="55"/>
       <c r="D603" s="55"/>
-      <c r="E603" s="55"/>
+      <c r="E603" s="54"/>
       <c r="F603" s="55"/>
       <c r="G603" s="54"/>
     </row>
@@ -38288,7 +38296,7 @@
       <c r="B604" s="54"/>
       <c r="C604" s="55"/>
       <c r="D604" s="55"/>
-      <c r="E604" s="55"/>
+      <c r="E604" s="54"/>
       <c r="F604" s="55"/>
       <c r="G604" s="54"/>
     </row>
@@ -38296,7 +38304,7 @@
       <c r="B605" s="54"/>
       <c r="C605" s="55"/>
       <c r="D605" s="55"/>
-      <c r="E605" s="55"/>
+      <c r="E605" s="54"/>
       <c r="F605" s="55"/>
       <c r="G605" s="54"/>
     </row>
@@ -38304,7 +38312,7 @@
       <c r="B606" s="54"/>
       <c r="C606" s="55"/>
       <c r="D606" s="55"/>
-      <c r="E606" s="55"/>
+      <c r="E606" s="54"/>
       <c r="F606" s="55"/>
       <c r="G606" s="54"/>
     </row>
@@ -38312,7 +38320,7 @@
       <c r="B607" s="54"/>
       <c r="C607" s="55"/>
       <c r="D607" s="55"/>
-      <c r="E607" s="55"/>
+      <c r="E607" s="54"/>
       <c r="F607" s="55"/>
       <c r="G607" s="54"/>
     </row>
@@ -38320,7 +38328,7 @@
       <c r="B608" s="54"/>
       <c r="C608" s="55"/>
       <c r="D608" s="55"/>
-      <c r="E608" s="55"/>
+      <c r="E608" s="54"/>
       <c r="F608" s="55"/>
       <c r="G608" s="54"/>
     </row>
@@ -38328,7 +38336,7 @@
       <c r="B609" s="54"/>
       <c r="C609" s="55"/>
       <c r="D609" s="55"/>
-      <c r="E609" s="55"/>
+      <c r="E609" s="54"/>
       <c r="F609" s="55"/>
       <c r="G609" s="54"/>
     </row>
@@ -38336,7 +38344,7 @@
       <c r="B610" s="54"/>
       <c r="C610" s="55"/>
       <c r="D610" s="55"/>
-      <c r="E610" s="55"/>
+      <c r="E610" s="54"/>
       <c r="F610" s="55"/>
       <c r="G610" s="54"/>
     </row>
@@ -38344,7 +38352,7 @@
       <c r="B611" s="54"/>
       <c r="C611" s="55"/>
       <c r="D611" s="55"/>
-      <c r="E611" s="55"/>
+      <c r="E611" s="54"/>
       <c r="F611" s="55"/>
       <c r="G611" s="54"/>
     </row>
@@ -38352,7 +38360,7 @@
       <c r="B612" s="54"/>
       <c r="C612" s="55"/>
       <c r="D612" s="55"/>
-      <c r="E612" s="55"/>
+      <c r="E612" s="54"/>
       <c r="F612" s="55"/>
       <c r="G612" s="54"/>
     </row>
@@ -38360,7 +38368,7 @@
       <c r="B613" s="54"/>
       <c r="C613" s="55"/>
       <c r="D613" s="55"/>
-      <c r="E613" s="55"/>
+      <c r="E613" s="54"/>
       <c r="F613" s="55"/>
       <c r="G613" s="54"/>
     </row>
@@ -38368,7 +38376,7 @@
       <c r="B614" s="54"/>
       <c r="C614" s="55"/>
       <c r="D614" s="55"/>
-      <c r="E614" s="55"/>
+      <c r="E614" s="54"/>
       <c r="F614" s="55"/>
       <c r="G614" s="54"/>
     </row>
@@ -38376,7 +38384,7 @@
       <c r="B615" s="54"/>
       <c r="C615" s="55"/>
       <c r="D615" s="55"/>
-      <c r="E615" s="55"/>
+      <c r="E615" s="54"/>
       <c r="F615" s="55"/>
       <c r="G615" s="54"/>
     </row>
@@ -38384,7 +38392,7 @@
       <c r="B616" s="54"/>
       <c r="C616" s="55"/>
       <c r="D616" s="55"/>
-      <c r="E616" s="55"/>
+      <c r="E616" s="54"/>
       <c r="F616" s="55"/>
       <c r="G616" s="54"/>
     </row>
@@ -38392,7 +38400,7 @@
       <c r="B617" s="54"/>
       <c r="C617" s="55"/>
       <c r="D617" s="55"/>
-      <c r="E617" s="55"/>
+      <c r="E617" s="54"/>
       <c r="F617" s="55"/>
       <c r="G617" s="54"/>
     </row>
@@ -38400,7 +38408,7 @@
       <c r="B618" s="54"/>
       <c r="C618" s="55"/>
       <c r="D618" s="55"/>
-      <c r="E618" s="55"/>
+      <c r="E618" s="54"/>
       <c r="F618" s="55"/>
       <c r="G618" s="54"/>
     </row>
@@ -38408,7 +38416,7 @@
       <c r="B619" s="54"/>
       <c r="C619" s="55"/>
       <c r="D619" s="55"/>
-      <c r="E619" s="55"/>
+      <c r="E619" s="54"/>
       <c r="F619" s="55"/>
       <c r="G619" s="54"/>
     </row>
@@ -38416,7 +38424,7 @@
       <c r="B620" s="54"/>
       <c r="C620" s="55"/>
       <c r="D620" s="55"/>
-      <c r="E620" s="55"/>
+      <c r="E620" s="54"/>
       <c r="F620" s="55"/>
       <c r="G620" s="54"/>
     </row>
@@ -38424,7 +38432,7 @@
       <c r="B621" s="54"/>
       <c r="C621" s="55"/>
       <c r="D621" s="55"/>
-      <c r="E621" s="55"/>
+      <c r="E621" s="54"/>
       <c r="F621" s="55"/>
       <c r="G621" s="54"/>
     </row>
@@ -38432,7 +38440,7 @@
       <c r="B622" s="54"/>
       <c r="C622" s="55"/>
       <c r="D622" s="55"/>
-      <c r="E622" s="55"/>
+      <c r="E622" s="54"/>
       <c r="F622" s="55"/>
       <c r="G622" s="54"/>
     </row>
@@ -38440,7 +38448,7 @@
       <c r="B623" s="54"/>
       <c r="C623" s="55"/>
       <c r="D623" s="55"/>
-      <c r="E623" s="55"/>
+      <c r="E623" s="54"/>
       <c r="F623" s="55"/>
       <c r="G623" s="54"/>
     </row>
@@ -38448,7 +38456,7 @@
       <c r="B624" s="54"/>
       <c r="C624" s="55"/>
       <c r="D624" s="55"/>
-      <c r="E624" s="55"/>
+      <c r="E624" s="54"/>
       <c r="F624" s="55"/>
       <c r="G624" s="54"/>
     </row>
@@ -38456,7 +38464,7 @@
       <c r="B625" s="54"/>
       <c r="C625" s="55"/>
       <c r="D625" s="55"/>
-      <c r="E625" s="55"/>
+      <c r="E625" s="54"/>
       <c r="F625" s="55"/>
       <c r="G625" s="54"/>
     </row>
@@ -38464,7 +38472,7 @@
       <c r="B626" s="54"/>
       <c r="C626" s="55"/>
       <c r="D626" s="55"/>
-      <c r="E626" s="55"/>
+      <c r="E626" s="54"/>
       <c r="F626" s="55"/>
       <c r="G626" s="54"/>
     </row>
@@ -38472,7 +38480,7 @@
       <c r="B627" s="54"/>
       <c r="C627" s="55"/>
       <c r="D627" s="55"/>
-      <c r="E627" s="55"/>
+      <c r="E627" s="54"/>
       <c r="F627" s="55"/>
       <c r="G627" s="54"/>
     </row>
@@ -38480,7 +38488,7 @@
       <c r="B628" s="54"/>
       <c r="C628" s="55"/>
       <c r="D628" s="55"/>
-      <c r="E628" s="55"/>
+      <c r="E628" s="54"/>
       <c r="F628" s="55"/>
       <c r="G628" s="54"/>
     </row>
@@ -38488,7 +38496,7 @@
       <c r="B629" s="54"/>
       <c r="C629" s="55"/>
       <c r="D629" s="55"/>
-      <c r="E629" s="55"/>
+      <c r="E629" s="54"/>
       <c r="F629" s="55"/>
       <c r="G629" s="54"/>
     </row>
@@ -38496,7 +38504,7 @@
       <c r="B630" s="54"/>
       <c r="C630" s="55"/>
       <c r="D630" s="55"/>
-      <c r="E630" s="55"/>
+      <c r="E630" s="54"/>
       <c r="F630" s="55"/>
       <c r="G630" s="54"/>
     </row>
@@ -38504,7 +38512,7 @@
       <c r="B631" s="54"/>
       <c r="C631" s="55"/>
       <c r="D631" s="55"/>
-      <c r="E631" s="55"/>
+      <c r="E631" s="54"/>
       <c r="F631" s="55"/>
       <c r="G631" s="54"/>
     </row>
@@ -38512,7 +38520,7 @@
       <c r="B632" s="54"/>
       <c r="C632" s="55"/>
       <c r="D632" s="55"/>
-      <c r="E632" s="55"/>
+      <c r="E632" s="54"/>
       <c r="F632" s="55"/>
       <c r="G632" s="54"/>
     </row>
@@ -38520,7 +38528,7 @@
       <c r="B633" s="54"/>
       <c r="C633" s="55"/>
       <c r="D633" s="55"/>
-      <c r="E633" s="55"/>
+      <c r="E633" s="54"/>
       <c r="F633" s="55"/>
       <c r="G633" s="54"/>
     </row>
@@ -38528,7 +38536,7 @@
       <c r="B634" s="54"/>
       <c r="C634" s="55"/>
       <c r="D634" s="55"/>
-      <c r="E634" s="55"/>
+      <c r="E634" s="54"/>
       <c r="F634" s="55"/>
       <c r="G634" s="54"/>
     </row>
@@ -38536,7 +38544,7 @@
       <c r="B635" s="54"/>
       <c r="C635" s="55"/>
       <c r="D635" s="55"/>
-      <c r="E635" s="55"/>
+      <c r="E635" s="54"/>
       <c r="F635" s="55"/>
       <c r="G635" s="54"/>
     </row>
@@ -38544,7 +38552,7 @@
       <c r="B636" s="54"/>
       <c r="C636" s="55"/>
       <c r="D636" s="55"/>
-      <c r="E636" s="55"/>
+      <c r="E636" s="54"/>
       <c r="F636" s="55"/>
       <c r="G636" s="54"/>
     </row>
@@ -38552,7 +38560,7 @@
       <c r="B637" s="54"/>
       <c r="C637" s="55"/>
       <c r="D637" s="55"/>
-      <c r="E637" s="55"/>
+      <c r="E637" s="54"/>
       <c r="F637" s="55"/>
       <c r="G637" s="54"/>
     </row>
@@ -38560,7 +38568,7 @@
       <c r="B638" s="54"/>
       <c r="C638" s="55"/>
       <c r="D638" s="55"/>
-      <c r="E638" s="55"/>
+      <c r="E638" s="54"/>
       <c r="F638" s="55"/>
       <c r="G638" s="54"/>
     </row>
@@ -38568,7 +38576,7 @@
       <c r="B639" s="54"/>
       <c r="C639" s="55"/>
       <c r="D639" s="55"/>
-      <c r="E639" s="55"/>
+      <c r="E639" s="54"/>
       <c r="F639" s="55"/>
       <c r="G639" s="54"/>
     </row>
@@ -38576,7 +38584,7 @@
       <c r="B640" s="54"/>
       <c r="C640" s="55"/>
       <c r="D640" s="55"/>
-      <c r="E640" s="55"/>
+      <c r="E640" s="54"/>
       <c r="F640" s="55"/>
       <c r="G640" s="54"/>
     </row>
@@ -38584,7 +38592,7 @@
       <c r="B641" s="54"/>
       <c r="C641" s="55"/>
       <c r="D641" s="55"/>
-      <c r="E641" s="55"/>
+      <c r="E641" s="54"/>
       <c r="F641" s="55"/>
       <c r="G641" s="54"/>
     </row>
@@ -38592,7 +38600,7 @@
       <c r="B642" s="54"/>
       <c r="C642" s="55"/>
       <c r="D642" s="55"/>
-      <c r="E642" s="55"/>
+      <c r="E642" s="54"/>
       <c r="F642" s="55"/>
       <c r="G642" s="54"/>
     </row>
@@ -38600,7 +38608,7 @@
       <c r="B643" s="54"/>
       <c r="C643" s="55"/>
       <c r="D643" s="55"/>
-      <c r="E643" s="55"/>
+      <c r="E643" s="54"/>
       <c r="F643" s="55"/>
       <c r="G643" s="54"/>
     </row>
@@ -38608,7 +38616,7 @@
       <c r="B644" s="54"/>
       <c r="C644" s="55"/>
       <c r="D644" s="55"/>
-      <c r="E644" s="55"/>
+      <c r="E644" s="54"/>
       <c r="F644" s="55"/>
       <c r="G644" s="54"/>
     </row>
@@ -38616,7 +38624,7 @@
       <c r="B645" s="54"/>
       <c r="C645" s="55"/>
       <c r="D645" s="55"/>
-      <c r="E645" s="55"/>
+      <c r="E645" s="54"/>
       <c r="F645" s="55"/>
       <c r="G645" s="54"/>
     </row>
@@ -38624,7 +38632,7 @@
       <c r="B646" s="54"/>
       <c r="C646" s="55"/>
       <c r="D646" s="55"/>
-      <c r="E646" s="55"/>
+      <c r="E646" s="54"/>
       <c r="F646" s="55"/>
       <c r="G646" s="54"/>
     </row>
@@ -38632,7 +38640,7 @@
       <c r="B647" s="54"/>
       <c r="C647" s="55"/>
       <c r="D647" s="55"/>
-      <c r="E647" s="55"/>
+      <c r="E647" s="54"/>
       <c r="F647" s="55"/>
       <c r="G647" s="54"/>
     </row>
@@ -38640,7 +38648,7 @@
       <c r="B648" s="54"/>
       <c r="C648" s="55"/>
       <c r="D648" s="55"/>
-      <c r="E648" s="55"/>
+      <c r="E648" s="54"/>
       <c r="F648" s="55"/>
       <c r="G648" s="54"/>
     </row>
@@ -38648,7 +38656,7 @@
       <c r="B649" s="54"/>
       <c r="C649" s="55"/>
       <c r="D649" s="55"/>
-      <c r="E649" s="55"/>
+      <c r="E649" s="54"/>
       <c r="F649" s="55"/>
       <c r="G649" s="54"/>
     </row>
@@ -38656,7 +38664,7 @@
       <c r="B650" s="54"/>
       <c r="C650" s="55"/>
       <c r="D650" s="55"/>
-      <c r="E650" s="55"/>
+      <c r="E650" s="54"/>
       <c r="F650" s="55"/>
       <c r="G650" s="54"/>
     </row>
@@ -38664,7 +38672,7 @@
       <c r="B651" s="54"/>
       <c r="C651" s="55"/>
       <c r="D651" s="55"/>
-      <c r="E651" s="55"/>
+      <c r="E651" s="54"/>
       <c r="F651" s="55"/>
       <c r="G651" s="54"/>
     </row>
@@ -38672,7 +38680,7 @@
       <c r="B652" s="54"/>
       <c r="C652" s="55"/>
       <c r="D652" s="55"/>
-      <c r="E652" s="55"/>
+      <c r="E652" s="54"/>
       <c r="F652" s="55"/>
       <c r="G652" s="54"/>
     </row>
@@ -38680,7 +38688,7 @@
       <c r="B653" s="54"/>
       <c r="C653" s="55"/>
       <c r="D653" s="55"/>
-      <c r="E653" s="55"/>
+      <c r="E653" s="54"/>
       <c r="F653" s="55"/>
       <c r="G653" s="54"/>
     </row>
@@ -38688,7 +38696,7 @@
       <c r="B654" s="54"/>
       <c r="C654" s="55"/>
       <c r="D654" s="55"/>
-      <c r="E654" s="55"/>
+      <c r="E654" s="54"/>
       <c r="F654" s="55"/>
       <c r="G654" s="54"/>
     </row>
@@ -38696,7 +38704,7 @@
       <c r="B655" s="54"/>
       <c r="C655" s="55"/>
       <c r="D655" s="55"/>
-      <c r="E655" s="55"/>
+      <c r="E655" s="54"/>
       <c r="F655" s="55"/>
       <c r="G655" s="54"/>
     </row>
@@ -38704,7 +38712,7 @@
       <c r="B656" s="54"/>
       <c r="C656" s="55"/>
       <c r="D656" s="55"/>
-      <c r="E656" s="55"/>
+      <c r="E656" s="54"/>
       <c r="F656" s="55"/>
       <c r="G656" s="54"/>
     </row>
@@ -38712,7 +38720,7 @@
       <c r="B657" s="54"/>
       <c r="C657" s="55"/>
       <c r="D657" s="55"/>
-      <c r="E657" s="55"/>
+      <c r="E657" s="54"/>
       <c r="F657" s="55"/>
       <c r="G657" s="54"/>
     </row>
@@ -38720,7 +38728,7 @@
       <c r="B658" s="54"/>
       <c r="C658" s="55"/>
       <c r="D658" s="55"/>
-      <c r="E658" s="55"/>
+      <c r="E658" s="54"/>
       <c r="F658" s="55"/>
       <c r="G658" s="54"/>
     </row>
@@ -38728,7 +38736,7 @@
       <c r="B659" s="54"/>
       <c r="C659" s="55"/>
       <c r="D659" s="55"/>
-      <c r="E659" s="55"/>
+      <c r="E659" s="54"/>
       <c r="F659" s="55"/>
       <c r="G659" s="54"/>
     </row>
@@ -38736,7 +38744,7 @@
       <c r="B660" s="54"/>
       <c r="C660" s="55"/>
       <c r="D660" s="55"/>
-      <c r="E660" s="55"/>
+      <c r="E660" s="54"/>
       <c r="F660" s="55"/>
       <c r="G660" s="54"/>
     </row>
@@ -38744,7 +38752,7 @@
       <c r="B661" s="54"/>
       <c r="C661" s="55"/>
       <c r="D661" s="55"/>
-      <c r="E661" s="55"/>
+      <c r="E661" s="54"/>
       <c r="F661" s="55"/>
       <c r="G661" s="54"/>
     </row>
@@ -38752,7 +38760,7 @@
       <c r="B662" s="54"/>
       <c r="C662" s="55"/>
       <c r="D662" s="55"/>
-      <c r="E662" s="55"/>
+      <c r="E662" s="54"/>
       <c r="F662" s="55"/>
       <c r="G662" s="54"/>
     </row>
@@ -38760,7 +38768,7 @@
       <c r="B663" s="54"/>
       <c r="C663" s="55"/>
       <c r="D663" s="55"/>
-      <c r="E663" s="55"/>
+      <c r="E663" s="54"/>
       <c r="F663" s="55"/>
       <c r="G663" s="54"/>
     </row>
@@ -38768,7 +38776,7 @@
       <c r="B664" s="54"/>
       <c r="C664" s="55"/>
       <c r="D664" s="55"/>
-      <c r="E664" s="55"/>
+      <c r="E664" s="54"/>
       <c r="F664" s="55"/>
       <c r="G664" s="54"/>
     </row>
@@ -38776,7 +38784,7 @@
       <c r="B665" s="54"/>
       <c r="C665" s="55"/>
       <c r="D665" s="55"/>
-      <c r="E665" s="55"/>
+      <c r="E665" s="54"/>
       <c r="F665" s="55"/>
       <c r="G665" s="54"/>
     </row>
@@ -38784,7 +38792,7 @@
       <c r="B666" s="54"/>
       <c r="C666" s="55"/>
       <c r="D666" s="55"/>
-      <c r="E666" s="55"/>
+      <c r="E666" s="54"/>
       <c r="F666" s="55"/>
       <c r="G666" s="54"/>
     </row>
@@ -38792,7 +38800,7 @@
       <c r="B667" s="54"/>
       <c r="C667" s="55"/>
       <c r="D667" s="55"/>
-      <c r="E667" s="55"/>
+      <c r="E667" s="54"/>
       <c r="F667" s="55"/>
       <c r="G667" s="54"/>
     </row>
@@ -38800,7 +38808,7 @@
       <c r="B668" s="54"/>
       <c r="C668" s="55"/>
       <c r="D668" s="55"/>
-      <c r="E668" s="55"/>
+      <c r="E668" s="54"/>
       <c r="F668" s="55"/>
       <c r="G668" s="54"/>
     </row>
@@ -38808,7 +38816,7 @@
       <c r="B669" s="54"/>
       <c r="C669" s="55"/>
       <c r="D669" s="55"/>
-      <c r="E669" s="55"/>
+      <c r="E669" s="54"/>
       <c r="F669" s="55"/>
       <c r="G669" s="54"/>
     </row>
@@ -38816,7 +38824,7 @@
       <c r="B670" s="54"/>
       <c r="C670" s="55"/>
       <c r="D670" s="55"/>
-      <c r="E670" s="55"/>
+      <c r="E670" s="54"/>
       <c r="F670" s="55"/>
       <c r="G670" s="54"/>
     </row>
@@ -38824,7 +38832,7 @@
       <c r="B671" s="54"/>
       <c r="C671" s="55"/>
       <c r="D671" s="55"/>
-      <c r="E671" s="55"/>
+      <c r="E671" s="54"/>
       <c r="F671" s="55"/>
       <c r="G671" s="54"/>
     </row>
@@ -38832,7 +38840,7 @@
       <c r="B672" s="54"/>
       <c r="C672" s="55"/>
       <c r="D672" s="55"/>
-      <c r="E672" s="55"/>
+      <c r="E672" s="54"/>
       <c r="F672" s="55"/>
       <c r="G672" s="54"/>
     </row>
@@ -38840,7 +38848,7 @@
       <c r="B673" s="54"/>
       <c r="C673" s="55"/>
       <c r="D673" s="55"/>
-      <c r="E673" s="55"/>
+      <c r="E673" s="54"/>
       <c r="F673" s="55"/>
       <c r="G673" s="54"/>
     </row>
@@ -38848,7 +38856,7 @@
       <c r="B674" s="54"/>
       <c r="C674" s="55"/>
       <c r="D674" s="55"/>
-      <c r="E674" s="55"/>
+      <c r="E674" s="54"/>
       <c r="F674" s="55"/>
       <c r="G674" s="54"/>
     </row>
@@ -38856,7 +38864,7 @@
       <c r="B675" s="54"/>
       <c r="C675" s="55"/>
       <c r="D675" s="55"/>
-      <c r="E675" s="55"/>
+      <c r="E675" s="54"/>
       <c r="F675" s="55"/>
       <c r="G675" s="54"/>
     </row>
@@ -38864,7 +38872,7 @@
       <c r="B676" s="54"/>
       <c r="C676" s="55"/>
       <c r="D676" s="55"/>
-      <c r="E676" s="55"/>
+      <c r="E676" s="54"/>
       <c r="F676" s="55"/>
       <c r="G676" s="54"/>
     </row>
@@ -38872,7 +38880,7 @@
       <c r="B677" s="54"/>
       <c r="C677" s="55"/>
       <c r="D677" s="55"/>
-      <c r="E677" s="55"/>
+      <c r="E677" s="54"/>
       <c r="F677" s="55"/>
       <c r="G677" s="54"/>
     </row>
@@ -38880,7 +38888,7 @@
       <c r="B678" s="54"/>
       <c r="C678" s="55"/>
       <c r="D678" s="55"/>
-      <c r="E678" s="55"/>
+      <c r="E678" s="54"/>
       <c r="F678" s="55"/>
       <c r="G678" s="54"/>
     </row>
@@ -38888,7 +38896,7 @@
       <c r="B679" s="54"/>
       <c r="C679" s="55"/>
       <c r="D679" s="55"/>
-      <c r="E679" s="55"/>
+      <c r="E679" s="54"/>
       <c r="F679" s="55"/>
       <c r="G679" s="54"/>
     </row>
@@ -38896,7 +38904,7 @@
       <c r="B680" s="54"/>
       <c r="C680" s="55"/>
       <c r="D680" s="55"/>
-      <c r="E680" s="55"/>
+      <c r="E680" s="54"/>
       <c r="F680" s="55"/>
       <c r="G680" s="54"/>
     </row>
@@ -38904,7 +38912,7 @@
       <c r="B681" s="54"/>
       <c r="C681" s="55"/>
       <c r="D681" s="55"/>
-      <c r="E681" s="55"/>
+      <c r="E681" s="54"/>
       <c r="F681" s="55"/>
       <c r="G681" s="54"/>
     </row>
@@ -38912,7 +38920,7 @@
       <c r="B682" s="54"/>
       <c r="C682" s="55"/>
       <c r="D682" s="55"/>
-      <c r="E682" s="55"/>
+      <c r="E682" s="54"/>
       <c r="F682" s="55"/>
       <c r="G682" s="54"/>
     </row>
@@ -38920,7 +38928,7 @@
       <c r="B683" s="54"/>
       <c r="C683" s="55"/>
       <c r="D683" s="55"/>
-      <c r="E683" s="55"/>
+      <c r="E683" s="54"/>
       <c r="F683" s="55"/>
       <c r="G683" s="54"/>
     </row>
@@ -38928,7 +38936,7 @@
       <c r="B684" s="54"/>
       <c r="C684" s="55"/>
       <c r="D684" s="55"/>
-      <c r="E684" s="55"/>
+      <c r="E684" s="54"/>
       <c r="F684" s="55"/>
       <c r="G684" s="54"/>
     </row>
@@ -38936,7 +38944,7 @@
       <c r="B685" s="54"/>
       <c r="C685" s="55"/>
       <c r="D685" s="55"/>
-      <c r="E685" s="55"/>
+      <c r="E685" s="54"/>
       <c r="F685" s="55"/>
       <c r="G685" s="54"/>
     </row>
@@ -38944,7 +38952,7 @@
       <c r="B686" s="54"/>
       <c r="C686" s="55"/>
       <c r="D686" s="55"/>
-      <c r="E686" s="55"/>
+      <c r="E686" s="54"/>
       <c r="F686" s="55"/>
       <c r="G686" s="54"/>
     </row>
@@ -38952,7 +38960,7 @@
       <c r="B687" s="54"/>
       <c r="C687" s="55"/>
       <c r="D687" s="55"/>
-      <c r="E687" s="55"/>
+      <c r="E687" s="54"/>
       <c r="F687" s="55"/>
       <c r="G687" s="54"/>
     </row>
@@ -38960,7 +38968,7 @@
       <c r="B688" s="54"/>
       <c r="C688" s="55"/>
       <c r="D688" s="55"/>
-      <c r="E688" s="55"/>
+      <c r="E688" s="54"/>
       <c r="F688" s="55"/>
       <c r="G688" s="54"/>
     </row>
@@ -38968,7 +38976,7 @@
       <c r="B689" s="54"/>
       <c r="C689" s="55"/>
       <c r="D689" s="55"/>
-      <c r="E689" s="55"/>
+      <c r="E689" s="54"/>
       <c r="F689" s="55"/>
       <c r="G689" s="54"/>
     </row>
@@ -38976,7 +38984,7 @@
       <c r="B690" s="54"/>
       <c r="C690" s="55"/>
       <c r="D690" s="55"/>
-      <c r="E690" s="55"/>
+      <c r="E690" s="54"/>
       <c r="F690" s="55"/>
       <c r="G690" s="54"/>
     </row>
@@ -38984,7 +38992,7 @@
       <c r="B691" s="54"/>
       <c r="C691" s="55"/>
       <c r="D691" s="55"/>
-      <c r="E691" s="55"/>
+      <c r="E691" s="54"/>
       <c r="F691" s="55"/>
       <c r="G691" s="54"/>
     </row>
@@ -38992,7 +39000,7 @@
       <c r="B692" s="54"/>
       <c r="C692" s="55"/>
       <c r="D692" s="55"/>
-      <c r="E692" s="55"/>
+      <c r="E692" s="54"/>
       <c r="F692" s="55"/>
       <c r="G692" s="54"/>
     </row>
@@ -39000,7 +39008,7 @@
       <c r="B693" s="54"/>
       <c r="C693" s="55"/>
       <c r="D693" s="55"/>
-      <c r="E693" s="55"/>
+      <c r="E693" s="54"/>
       <c r="F693" s="55"/>
       <c r="G693" s="54"/>
     </row>
@@ -39008,7 +39016,7 @@
       <c r="B694" s="54"/>
       <c r="C694" s="55"/>
       <c r="D694" s="55"/>
-      <c r="E694" s="55"/>
+      <c r="E694" s="54"/>
       <c r="F694" s="55"/>
       <c r="G694" s="54"/>
     </row>
@@ -39016,7 +39024,7 @@
       <c r="B695" s="54"/>
       <c r="C695" s="55"/>
       <c r="D695" s="55"/>
-      <c r="E695" s="55"/>
+      <c r="E695" s="54"/>
       <c r="F695" s="55"/>
       <c r="G695" s="54"/>
     </row>
@@ -39024,7 +39032,7 @@
       <c r="B696" s="54"/>
       <c r="C696" s="55"/>
       <c r="D696" s="55"/>
-      <c r="E696" s="55"/>
+      <c r="E696" s="54"/>
       <c r="F696" s="55"/>
       <c r="G696" s="54"/>
     </row>
@@ -39032,7 +39040,7 @@
       <c r="B697" s="54"/>
       <c r="C697" s="55"/>
       <c r="D697" s="55"/>
-      <c r="E697" s="55"/>
+      <c r="E697" s="54"/>
       <c r="F697" s="55"/>
       <c r="G697" s="54"/>
     </row>
@@ -39040,7 +39048,7 @@
       <c r="B698" s="54"/>
       <c r="C698" s="55"/>
       <c r="D698" s="55"/>
-      <c r="E698" s="55"/>
+      <c r="E698" s="54"/>
       <c r="F698" s="55"/>
       <c r="G698" s="54"/>
     </row>
@@ -39048,7 +39056,7 @@
       <c r="B699" s="54"/>
       <c r="C699" s="55"/>
       <c r="D699" s="55"/>
-      <c r="E699" s="55"/>
+      <c r="E699" s="54"/>
       <c r="F699" s="55"/>
       <c r="G699" s="54"/>
     </row>
@@ -39056,7 +39064,7 @@
       <c r="B700" s="54"/>
       <c r="C700" s="55"/>
       <c r="D700" s="55"/>
-      <c r="E700" s="55"/>
+      <c r="E700" s="54"/>
       <c r="F700" s="55"/>
       <c r="G700" s="54"/>
     </row>
@@ -39064,7 +39072,7 @@
       <c r="B701" s="54"/>
       <c r="C701" s="55"/>
       <c r="D701" s="55"/>
-      <c r="E701" s="55"/>
+      <c r="E701" s="54"/>
       <c r="F701" s="55"/>
       <c r="G701" s="54"/>
     </row>
@@ -39072,7 +39080,7 @@
       <c r="B702" s="54"/>
       <c r="C702" s="55"/>
       <c r="D702" s="55"/>
-      <c r="E702" s="55"/>
+      <c r="E702" s="54"/>
       <c r="F702" s="55"/>
       <c r="G702" s="54"/>
     </row>
@@ -39080,7 +39088,7 @@
       <c r="B703" s="54"/>
       <c r="C703" s="55"/>
       <c r="D703" s="55"/>
-      <c r="E703" s="55"/>
+      <c r="E703" s="54"/>
       <c r="F703" s="55"/>
       <c r="G703" s="54"/>
     </row>
@@ -39088,7 +39096,7 @@
       <c r="B704" s="54"/>
       <c r="C704" s="55"/>
       <c r="D704" s="55"/>
-      <c r="E704" s="55"/>
+      <c r="E704" s="54"/>
       <c r="F704" s="55"/>
       <c r="G704" s="54"/>
     </row>
@@ -39096,7 +39104,7 @@
       <c r="B705" s="54"/>
       <c r="C705" s="55"/>
       <c r="D705" s="55"/>
-      <c r="E705" s="55"/>
+      <c r="E705" s="54"/>
       <c r="F705" s="55"/>
       <c r="G705" s="54"/>
     </row>
@@ -39104,7 +39112,7 @@
       <c r="B706" s="54"/>
       <c r="C706" s="55"/>
       <c r="D706" s="55"/>
-      <c r="E706" s="55"/>
+      <c r="E706" s="54"/>
       <c r="F706" s="55"/>
       <c r="G706" s="54"/>
     </row>
@@ -39112,7 +39120,7 @@
       <c r="B707" s="54"/>
       <c r="C707" s="55"/>
       <c r="D707" s="55"/>
-      <c r="E707" s="55"/>
+      <c r="E707" s="54"/>
       <c r="F707" s="55"/>
       <c r="G707" s="54"/>
     </row>
@@ -39120,7 +39128,7 @@
       <c r="B708" s="54"/>
       <c r="C708" s="55"/>
       <c r="D708" s="55"/>
-      <c r="E708" s="55"/>
+      <c r="E708" s="54"/>
       <c r="F708" s="55"/>
       <c r="G708" s="54"/>
     </row>
@@ -39128,7 +39136,7 @@
       <c r="B709" s="54"/>
       <c r="C709" s="55"/>
       <c r="D709" s="55"/>
-      <c r="E709" s="55"/>
+      <c r="E709" s="54"/>
       <c r="F709" s="55"/>
       <c r="G709" s="54"/>
     </row>
@@ -39136,7 +39144,7 @@
       <c r="B710" s="54"/>
       <c r="C710" s="55"/>
       <c r="D710" s="55"/>
-      <c r="E710" s="55"/>
+      <c r="E710" s="54"/>
       <c r="F710" s="55"/>
       <c r="G710" s="54"/>
     </row>
@@ -39144,7 +39152,7 @@
       <c r="B711" s="54"/>
       <c r="C711" s="55"/>
       <c r="D711" s="55"/>
-      <c r="E711" s="55"/>
+      <c r="E711" s="54"/>
       <c r="F711" s="55"/>
       <c r="G711" s="54"/>
     </row>
@@ -39152,7 +39160,7 @@
       <c r="B712" s="54"/>
       <c r="C712" s="55"/>
       <c r="D712" s="55"/>
-      <c r="E712" s="55"/>
+      <c r="E712" s="54"/>
       <c r="F712" s="55"/>
       <c r="G712" s="54"/>
     </row>
@@ -39160,7 +39168,7 @@
       <c r="B713" s="54"/>
       <c r="C713" s="55"/>
       <c r="D713" s="55"/>
-      <c r="E713" s="55"/>
+      <c r="E713" s="54"/>
       <c r="F713" s="55"/>
       <c r="G713" s="54"/>
     </row>
@@ -39168,7 +39176,7 @@
       <c r="B714" s="54"/>
       <c r="C714" s="55"/>
       <c r="D714" s="55"/>
-      <c r="E714" s="55"/>
+      <c r="E714" s="54"/>
       <c r="F714" s="55"/>
       <c r="G714" s="54"/>
     </row>
@@ -39176,7 +39184,7 @@
       <c r="B715" s="54"/>
       <c r="C715" s="55"/>
       <c r="D715" s="55"/>
-      <c r="E715" s="55"/>
+      <c r="E715" s="54"/>
       <c r="F715" s="55"/>
       <c r="G715" s="54"/>
     </row>
@@ -39184,7 +39192,7 @@
       <c r="B716" s="54"/>
       <c r="C716" s="55"/>
       <c r="D716" s="55"/>
-      <c r="E716" s="55"/>
+      <c r="E716" s="54"/>
       <c r="F716" s="55"/>
       <c r="G716" s="54"/>
     </row>
@@ -39192,7 +39200,7 @@
       <c r="B717" s="54"/>
       <c r="C717" s="55"/>
       <c r="D717" s="55"/>
-      <c r="E717" s="55"/>
+      <c r="E717" s="54"/>
       <c r="F717" s="55"/>
       <c r="G717" s="54"/>
     </row>
@@ -39200,7 +39208,7 @@
       <c r="B718" s="54"/>
       <c r="C718" s="55"/>
       <c r="D718" s="55"/>
-      <c r="E718" s="55"/>
+      <c r="E718" s="54"/>
       <c r="F718" s="55"/>
       <c r="G718" s="54"/>
     </row>
@@ -39208,7 +39216,7 @@
       <c r="B719" s="54"/>
       <c r="C719" s="55"/>
       <c r="D719" s="55"/>
-      <c r="E719" s="55"/>
+      <c r="E719" s="54"/>
       <c r="F719" s="55"/>
       <c r="G719" s="54"/>
     </row>
@@ -39216,7 +39224,7 @@
       <c r="B720" s="54"/>
       <c r="C720" s="55"/>
       <c r="D720" s="55"/>
-      <c r="E720" s="55"/>
+      <c r="E720" s="54"/>
       <c r="F720" s="55"/>
       <c r="G720" s="54"/>
     </row>
@@ -39224,7 +39232,7 @@
       <c r="B721" s="54"/>
       <c r="C721" s="55"/>
       <c r="D721" s="55"/>
-      <c r="E721" s="55"/>
+      <c r="E721" s="54"/>
       <c r="F721" s="55"/>
       <c r="G721" s="54"/>
     </row>
@@ -39232,7 +39240,7 @@
       <c r="B722" s="54"/>
       <c r="C722" s="55"/>
       <c r="D722" s="55"/>
-      <c r="E722" s="55"/>
+      <c r="E722" s="54"/>
       <c r="F722" s="55"/>
       <c r="G722" s="54"/>
     </row>
@@ -39240,7 +39248,7 @@
       <c r="B723" s="54"/>
       <c r="C723" s="55"/>
       <c r="D723" s="55"/>
-      <c r="E723" s="55"/>
+      <c r="E723" s="54"/>
       <c r="F723" s="55"/>
       <c r="G723" s="54"/>
     </row>
@@ -39248,7 +39256,7 @@
       <c r="B724" s="54"/>
       <c r="C724" s="55"/>
       <c r="D724" s="55"/>
-      <c r="E724" s="55"/>
+      <c r="E724" s="54"/>
       <c r="F724" s="55"/>
       <c r="G724" s="54"/>
     </row>
@@ -39256,7 +39264,7 @@
       <c r="B725" s="54"/>
       <c r="C725" s="55"/>
       <c r="D725" s="55"/>
-      <c r="E725" s="55"/>
+      <c r="E725" s="54"/>
       <c r="F725" s="55"/>
       <c r="G725" s="54"/>
     </row>
@@ -39264,7 +39272,7 @@
       <c r="B726" s="54"/>
       <c r="C726" s="55"/>
       <c r="D726" s="55"/>
-      <c r="E726" s="55"/>
+      <c r="E726" s="54"/>
       <c r="F726" s="55"/>
       <c r="G726" s="54"/>
     </row>
@@ -39272,7 +39280,7 @@
       <c r="B727" s="54"/>
       <c r="C727" s="55"/>
       <c r="D727" s="55"/>
-      <c r="E727" s="55"/>
+      <c r="E727" s="54"/>
       <c r="F727" s="55"/>
       <c r="G727" s="54"/>
     </row>
@@ -39280,7 +39288,7 @@
       <c r="B728" s="54"/>
       <c r="C728" s="55"/>
       <c r="D728" s="55"/>
-      <c r="E728" s="55"/>
+      <c r="E728" s="54"/>
       <c r="F728" s="55"/>
       <c r="G728" s="54"/>
     </row>
@@ -39288,7 +39296,7 @@
       <c r="B729" s="54"/>
       <c r="C729" s="55"/>
       <c r="D729" s="55"/>
-      <c r="E729" s="55"/>
+      <c r="E729" s="54"/>
       <c r="F729" s="55"/>
       <c r="G729" s="54"/>
     </row>
@@ -39296,7 +39304,7 @@
       <c r="B730" s="54"/>
       <c r="C730" s="55"/>
       <c r="D730" s="55"/>
-      <c r="E730" s="55"/>
+      <c r="E730" s="54"/>
       <c r="F730" s="55"/>
       <c r="G730" s="54"/>
     </row>
@@ -39304,7 +39312,7 @@
       <c r="B731" s="54"/>
       <c r="C731" s="55"/>
       <c r="D731" s="55"/>
-      <c r="E731" s="55"/>
+      <c r="E731" s="54"/>
       <c r="F731" s="55"/>
       <c r="G731" s="54"/>
     </row>
@@ -39312,7 +39320,7 @@
       <c r="B732" s="54"/>
       <c r="C732" s="55"/>
       <c r="D732" s="55"/>
-      <c r="E732" s="55"/>
+      <c r="E732" s="54"/>
       <c r="F732" s="55"/>
       <c r="G732" s="54"/>
     </row>
@@ -39320,7 +39328,7 @@
       <c r="B733" s="54"/>
       <c r="C733" s="55"/>
       <c r="D733" s="55"/>
-      <c r="E733" s="55"/>
+      <c r="E733" s="54"/>
       <c r="F733" s="55"/>
       <c r="G733" s="54"/>
     </row>
@@ -39328,7 +39336,7 @@
       <c r="B734" s="54"/>
       <c r="C734" s="55"/>
       <c r="D734" s="55"/>
-      <c r="E734" s="55"/>
+      <c r="E734" s="54"/>
       <c r="F734" s="55"/>
       <c r="G734" s="54"/>
     </row>
@@ -39336,7 +39344,7 @@
       <c r="B735" s="54"/>
       <c r="C735" s="55"/>
       <c r="D735" s="55"/>
-      <c r="E735" s="55"/>
+      <c r="E735" s="54"/>
       <c r="F735" s="55"/>
       <c r="G735" s="54"/>
     </row>
@@ -39344,7 +39352,7 @@
       <c r="B736" s="54"/>
       <c r="C736" s="55"/>
       <c r="D736" s="55"/>
-      <c r="E736" s="55"/>
+      <c r="E736" s="54"/>
       <c r="F736" s="55"/>
       <c r="G736" s="54"/>
     </row>
@@ -39352,7 +39360,7 @@
       <c r="B737" s="54"/>
       <c r="C737" s="55"/>
       <c r="D737" s="55"/>
-      <c r="E737" s="55"/>
+      <c r="E737" s="54"/>
       <c r="F737" s="55"/>
       <c r="G737" s="54"/>
     </row>
@@ -39360,7 +39368,7 @@
       <c r="B738" s="54"/>
       <c r="C738" s="55"/>
       <c r="D738" s="55"/>
-      <c r="E738" s="55"/>
+      <c r="E738" s="54"/>
       <c r="F738" s="55"/>
       <c r="G738" s="54"/>
     </row>
@@ -39368,7 +39376,7 @@
       <c r="B739" s="54"/>
       <c r="C739" s="55"/>
       <c r="D739" s="55"/>
-      <c r="E739" s="55"/>
+      <c r="E739" s="54"/>
       <c r="F739" s="55"/>
       <c r="G739" s="54"/>
     </row>
@@ -39376,7 +39384,7 @@
       <c r="B740" s="54"/>
       <c r="C740" s="55"/>
       <c r="D740" s="55"/>
-      <c r="E740" s="55"/>
+      <c r="E740" s="54"/>
       <c r="F740" s="55"/>
       <c r="G740" s="54"/>
     </row>
@@ -39384,7 +39392,7 @@
       <c r="B741" s="54"/>
       <c r="C741" s="55"/>
       <c r="D741" s="55"/>
-      <c r="E741" s="55"/>
+      <c r="E741" s="54"/>
       <c r="F741" s="55"/>
       <c r="G741" s="54"/>
     </row>
@@ -39392,7 +39400,7 @@
       <c r="B742" s="54"/>
       <c r="C742" s="55"/>
       <c r="D742" s="55"/>
-      <c r="E742" s="55"/>
+      <c r="E742" s="54"/>
       <c r="F742" s="55"/>
       <c r="G742" s="54"/>
     </row>
@@ -39400,7 +39408,7 @@
       <c r="B743" s="54"/>
       <c r="C743" s="55"/>
       <c r="D743" s="55"/>
-      <c r="E743" s="55"/>
+      <c r="E743" s="54"/>
       <c r="F743" s="55"/>
       <c r="G743" s="54"/>
     </row>
@@ -39408,7 +39416,7 @@
       <c r="B744" s="54"/>
       <c r="C744" s="55"/>
       <c r="D744" s="55"/>
-      <c r="E744" s="55"/>
+      <c r="E744" s="54"/>
       <c r="F744" s="55"/>
       <c r="G744" s="54"/>
     </row>
@@ -39416,7 +39424,7 @@
       <c r="B745" s="54"/>
       <c r="C745" s="55"/>
       <c r="D745" s="55"/>
-      <c r="E745" s="55"/>
+      <c r="E745" s="54"/>
       <c r="F745" s="55"/>
       <c r="G745" s="54"/>
     </row>
@@ -39424,7 +39432,7 @@
       <c r="B746" s="54"/>
       <c r="C746" s="55"/>
       <c r="D746" s="55"/>
-      <c r="E746" s="55"/>
+      <c r="E746" s="54"/>
       <c r="F746" s="55"/>
       <c r="G746" s="54"/>
     </row>
@@ -39432,7 +39440,7 @@
       <c r="B747" s="54"/>
       <c r="C747" s="55"/>
       <c r="D747" s="55"/>
-      <c r="E747" s="55"/>
+      <c r="E747" s="54"/>
       <c r="F747" s="55"/>
       <c r="G747" s="54"/>
     </row>
@@ -39440,7 +39448,7 @@
       <c r="B748" s="54"/>
       <c r="C748" s="55"/>
       <c r="D748" s="55"/>
-      <c r="E748" s="55"/>
+      <c r="E748" s="54"/>
       <c r="F748" s="55"/>
       <c r="G748" s="54"/>
     </row>
@@ -39448,7 +39456,7 @@
       <c r="B749" s="54"/>
       <c r="C749" s="55"/>
       <c r="D749" s="55"/>
-      <c r="E749" s="55"/>
+      <c r="E749" s="54"/>
       <c r="F749" s="55"/>
       <c r="G749" s="54"/>
     </row>
@@ -39456,7 +39464,7 @@
       <c r="B750" s="54"/>
       <c r="C750" s="55"/>
       <c r="D750" s="55"/>
-      <c r="E750" s="55"/>
+      <c r="E750" s="54"/>
       <c r="F750" s="55"/>
       <c r="G750" s="54"/>
     </row>
@@ -39464,7 +39472,7 @@
       <c r="B751" s="54"/>
       <c r="C751" s="55"/>
       <c r="D751" s="55"/>
-      <c r="E751" s="55"/>
+      <c r="E751" s="54"/>
       <c r="F751" s="55"/>
       <c r="G751" s="54"/>
     </row>
@@ -39472,7 +39480,7 @@
       <c r="B752" s="54"/>
       <c r="C752" s="55"/>
       <c r="D752" s="55"/>
-      <c r="E752" s="55"/>
+      <c r="E752" s="54"/>
       <c r="F752" s="55"/>
       <c r="G752" s="54"/>
     </row>
@@ -39480,7 +39488,7 @@
       <c r="B753" s="54"/>
       <c r="C753" s="55"/>
       <c r="D753" s="55"/>
-      <c r="E753" s="55"/>
+      <c r="E753" s="54"/>
       <c r="F753" s="55"/>
       <c r="G753" s="54"/>
     </row>
@@ -39488,7 +39496,7 @@
       <c r="B754" s="54"/>
       <c r="C754" s="55"/>
       <c r="D754" s="55"/>
-      <c r="E754" s="55"/>
+      <c r="E754" s="54"/>
       <c r="F754" s="55"/>
       <c r="G754" s="54"/>
     </row>
@@ -39496,7 +39504,7 @@
       <c r="B755" s="54"/>
       <c r="C755" s="55"/>
       <c r="D755" s="55"/>
-      <c r="E755" s="55"/>
+      <c r="E755" s="54"/>
       <c r="F755" s="55"/>
       <c r="G755" s="54"/>
     </row>
@@ -39504,7 +39512,7 @@
       <c r="B756" s="54"/>
       <c r="C756" s="55"/>
       <c r="D756" s="55"/>
-      <c r="E756" s="55"/>
+      <c r="E756" s="54"/>
       <c r="F756" s="55"/>
       <c r="G756" s="54"/>
     </row>
@@ -39512,7 +39520,7 @@
       <c r="B757" s="54"/>
       <c r="C757" s="55"/>
       <c r="D757" s="55"/>
-      <c r="E757" s="55"/>
+      <c r="E757" s="54"/>
       <c r="F757" s="55"/>
       <c r="G757" s="54"/>
     </row>
@@ -39520,7 +39528,7 @@
       <c r="B758" s="54"/>
       <c r="C758" s="55"/>
       <c r="D758" s="55"/>
-      <c r="E758" s="55"/>
+      <c r="E758" s="54"/>
       <c r="F758" s="55"/>
       <c r="G758" s="54"/>
     </row>
@@ -39528,7 +39536,7 @@
       <c r="B759" s="54"/>
       <c r="C759" s="55"/>
       <c r="D759" s="55"/>
-      <c r="E759" s="55"/>
+      <c r="E759" s="54"/>
       <c r="F759" s="55"/>
       <c r="G759" s="54"/>
     </row>
@@ -39536,7 +39544,7 @@
       <c r="B760" s="54"/>
       <c r="C760" s="55"/>
       <c r="D760" s="55"/>
-      <c r="E760" s="55"/>
+      <c r="E760" s="54"/>
       <c r="F760" s="55"/>
       <c r="G760" s="54"/>
     </row>
@@ -39544,7 +39552,7 @@
       <c r="B761" s="54"/>
       <c r="C761" s="55"/>
       <c r="D761" s="55"/>
-      <c r="E761" s="55"/>
+      <c r="E761" s="54"/>
       <c r="F761" s="55"/>
       <c r="G761" s="54"/>
     </row>
@@ -39552,7 +39560,7 @@
       <c r="B762" s="54"/>
       <c r="C762" s="55"/>
       <c r="D762" s="55"/>
-      <c r="E762" s="55"/>
+      <c r="E762" s="54"/>
       <c r="F762" s="55"/>
       <c r="G762" s="54"/>
     </row>
@@ -39560,7 +39568,7 @@
       <c r="B763" s="54"/>
       <c r="C763" s="55"/>
       <c r="D763" s="55"/>
-      <c r="E763" s="55"/>
+      <c r="E763" s="54"/>
       <c r="F763" s="55"/>
       <c r="G763" s="54"/>
     </row>
@@ -39568,7 +39576,7 @@
       <c r="B764" s="54"/>
       <c r="C764" s="55"/>
       <c r="D764" s="55"/>
-      <c r="E764" s="55"/>
+      <c r="E764" s="54"/>
       <c r="F764" s="55"/>
       <c r="G764" s="54"/>
     </row>
@@ -39576,7 +39584,7 @@
       <c r="B765" s="54"/>
       <c r="C765" s="55"/>
       <c r="D765" s="55"/>
-      <c r="E765" s="55"/>
+      <c r="E765" s="54"/>
       <c r="F765" s="55"/>
       <c r="G765" s="54"/>
     </row>
@@ -39584,7 +39592,7 @@
       <c r="B766" s="54"/>
       <c r="C766" s="55"/>
       <c r="D766" s="55"/>
-      <c r="E766" s="55"/>
+      <c r="E766" s="54"/>
       <c r="F766" s="55"/>
       <c r="G766" s="54"/>
     </row>
@@ -39592,7 +39600,7 @@
       <c r="B767" s="54"/>
       <c r="C767" s="55"/>
       <c r="D767" s="55"/>
-      <c r="E767" s="55"/>
+      <c r="E767" s="54"/>
       <c r="F767" s="55"/>
       <c r="G767" s="54"/>
     </row>
@@ -39600,7 +39608,7 @@
       <c r="B768" s="54"/>
       <c r="C768" s="55"/>
       <c r="D768" s="55"/>
-      <c r="E768" s="55"/>
+      <c r="E768" s="54"/>
       <c r="F768" s="55"/>
       <c r="G768" s="54"/>
     </row>
@@ -39608,7 +39616,7 @@
       <c r="B769" s="54"/>
       <c r="C769" s="55"/>
       <c r="D769" s="55"/>
-      <c r="E769" s="55"/>
+      <c r="E769" s="54"/>
       <c r="F769" s="55"/>
       <c r="G769" s="54"/>
     </row>
@@ -39616,7 +39624,7 @@
       <c r="B770" s="54"/>
       <c r="C770" s="55"/>
       <c r="D770" s="55"/>
-      <c r="E770" s="55"/>
+      <c r="E770" s="54"/>
       <c r="F770" s="55"/>
       <c r="G770" s="54"/>
     </row>
@@ -39624,7 +39632,7 @@
       <c r="B771" s="54"/>
       <c r="C771" s="55"/>
       <c r="D771" s="55"/>
-      <c r="E771" s="55"/>
+      <c r="E771" s="54"/>
       <c r="F771" s="55"/>
       <c r="G771" s="54"/>
     </row>
@@ -39632,7 +39640,7 @@
       <c r="B772" s="54"/>
       <c r="C772" s="55"/>
       <c r="D772" s="55"/>
-      <c r="E772" s="55"/>
+      <c r="E772" s="54"/>
       <c r="F772" s="55"/>
       <c r="G772" s="54"/>
     </row>
@@ -39640,7 +39648,7 @@
       <c r="B773" s="54"/>
       <c r="C773" s="55"/>
       <c r="D773" s="55"/>
-      <c r="E773" s="55"/>
+      <c r="E773" s="54"/>
       <c r="F773" s="55"/>
       <c r="G773" s="54"/>
     </row>
@@ -39648,7 +39656,7 @@
       <c r="B774" s="54"/>
       <c r="C774" s="55"/>
       <c r="D774" s="55"/>
-      <c r="E774" s="55"/>
+      <c r="E774" s="54"/>
       <c r="F774" s="55"/>
       <c r="G774" s="54"/>
     </row>
@@ -39656,7 +39664,7 @@
       <c r="B775" s="54"/>
       <c r="C775" s="55"/>
       <c r="D775" s="55"/>
-      <c r="E775" s="55"/>
+      <c r="E775" s="54"/>
       <c r="F775" s="55"/>
       <c r="G775" s="54"/>
     </row>
@@ -39664,7 +39672,7 @@
       <c r="B776" s="54"/>
       <c r="C776" s="55"/>
       <c r="D776" s="55"/>
-      <c r="E776" s="55"/>
+      <c r="E776" s="54"/>
       <c r="F776" s="55"/>
       <c r="G776" s="54"/>
     </row>
@@ -39672,7 +39680,7 @@
       <c r="B777" s="54"/>
       <c r="C777" s="55"/>
       <c r="D777" s="55"/>
-      <c r="E777" s="55"/>
+      <c r="E777" s="54"/>
       <c r="F777" s="55"/>
       <c r="G777" s="54"/>
     </row>
@@ -39680,7 +39688,7 @@
       <c r="B778" s="54"/>
       <c r="C778" s="55"/>
       <c r="D778" s="55"/>
-      <c r="E778" s="55"/>
+      <c r="E778" s="54"/>
       <c r="F778" s="55"/>
       <c r="G778" s="54"/>
     </row>
@@ -39688,7 +39696,7 @@
       <c r="B779" s="54"/>
       <c r="C779" s="55"/>
       <c r="D779" s="55"/>
-      <c r="E779" s="55"/>
+      <c r="E779" s="54"/>
       <c r="F779" s="55"/>
       <c r="G779" s="54"/>
     </row>
@@ -39696,7 +39704,7 @@
       <c r="B780" s="54"/>
       <c r="C780" s="55"/>
       <c r="D780" s="55"/>
-      <c r="E780" s="55"/>
+      <c r="E780" s="54"/>
       <c r="F780" s="55"/>
       <c r="G780" s="54"/>
     </row>
@@ -39704,7 +39712,7 @@
       <c r="B781" s="54"/>
       <c r="C781" s="55"/>
       <c r="D781" s="55"/>
-      <c r="E781" s="55"/>
+      <c r="E781" s="54"/>
       <c r="F781" s="55"/>
       <c r="G781" s="54"/>
     </row>
@@ -39712,7 +39720,7 @@
       <c r="B782" s="54"/>
       <c r="C782" s="55"/>
       <c r="D782" s="55"/>
-      <c r="E782" s="55"/>
+      <c r="E782" s="54"/>
       <c r="F782" s="55"/>
       <c r="G782" s="54"/>
     </row>
@@ -39720,7 +39728,7 @@
       <c r="B783" s="54"/>
       <c r="C783" s="55"/>
       <c r="D783" s="55"/>
-      <c r="E783" s="55"/>
+      <c r="E783" s="54"/>
       <c r="F783" s="55"/>
       <c r="G783" s="54"/>
     </row>
@@ -39728,7 +39736,7 @@
       <c r="B784" s="54"/>
       <c r="C784" s="55"/>
       <c r="D784" s="55"/>
-      <c r="E784" s="55"/>
+      <c r="E784" s="54"/>
       <c r="F784" s="55"/>
       <c r="G784" s="54"/>
     </row>
@@ -39736,7 +39744,7 @@
       <c r="B785" s="54"/>
       <c r="C785" s="55"/>
       <c r="D785" s="55"/>
-      <c r="E785" s="55"/>
+      <c r="E785" s="54"/>
       <c r="F785" s="55"/>
       <c r="G785" s="54"/>
     </row>
@@ -39744,7 +39752,7 @@
       <c r="B786" s="54"/>
       <c r="C786" s="55"/>
       <c r="D786" s="55"/>
-      <c r="E786" s="55"/>
+      <c r="E786" s="54"/>
       <c r="F786" s="55"/>
       <c r="G786" s="54"/>
     </row>
@@ -39752,7 +39760,7 @@
       <c r="B787" s="54"/>
       <c r="C787" s="55"/>
       <c r="D787" s="55"/>
-      <c r="E787" s="55"/>
+      <c r="E787" s="54"/>
       <c r="F787" s="55"/>
       <c r="G787" s="54"/>
     </row>
@@ -39760,7 +39768,7 @@
       <c r="B788" s="54"/>
       <c r="C788" s="55"/>
       <c r="D788" s="55"/>
-      <c r="E788" s="55"/>
+      <c r="E788" s="54"/>
       <c r="F788" s="55"/>
       <c r="G788" s="54"/>
     </row>
@@ -39768,7 +39776,7 @@
       <c r="B789" s="54"/>
       <c r="C789" s="55"/>
       <c r="D789" s="55"/>
-      <c r="E789" s="55"/>
+      <c r="E789" s="54"/>
       <c r="F789" s="55"/>
       <c r="G789" s="54"/>
     </row>
@@ -39776,7 +39784,7 @@
       <c r="B790" s="54"/>
       <c r="C790" s="55"/>
       <c r="D790" s="55"/>
-      <c r="E790" s="55"/>
+      <c r="E790" s="54"/>
       <c r="F790" s="55"/>
       <c r="G790" s="54"/>
     </row>
@@ -39784,7 +39792,7 @@
       <c r="B791" s="54"/>
       <c r="C791" s="55"/>
       <c r="D791" s="55"/>
-      <c r="E791" s="55"/>
+      <c r="E791" s="54"/>
       <c r="F791" s="55"/>
       <c r="G791" s="54"/>
     </row>
@@ -39792,7 +39800,7 @@
       <c r="B792" s="54"/>
       <c r="C792" s="55"/>
       <c r="D792" s="55"/>
-      <c r="E792" s="55"/>
+      <c r="E792" s="54"/>
       <c r="F792" s="55"/>
       <c r="G792" s="54"/>
     </row>
@@ -39800,7 +39808,7 @@
       <c r="B793" s="54"/>
       <c r="C793" s="55"/>
       <c r="D793" s="55"/>
-      <c r="E793" s="55"/>
+      <c r="E793" s="54"/>
       <c r="F793" s="55"/>
       <c r="G793" s="54"/>
     </row>
@@ -39808,7 +39816,7 @@
       <c r="B794" s="54"/>
       <c r="C794" s="55"/>
       <c r="D794" s="55"/>
-      <c r="E794" s="55"/>
+      <c r="E794" s="54"/>
       <c r="F794" s="55"/>
       <c r="G794" s="54"/>
     </row>
@@ -39816,7 +39824,7 @@
       <c r="B795" s="54"/>
       <c r="C795" s="55"/>
       <c r="D795" s="55"/>
-      <c r="E795" s="55"/>
+      <c r="E795" s="54"/>
       <c r="F795" s="55"/>
       <c r="G795" s="54"/>
     </row>
@@ -39824,7 +39832,7 @@
       <c r="B796" s="54"/>
       <c r="C796" s="55"/>
       <c r="D796" s="55"/>
-      <c r="E796" s="55"/>
+      <c r="E796" s="54"/>
       <c r="F796" s="55"/>
       <c r="G796" s="54"/>
     </row>
@@ -39832,7 +39840,7 @@
       <c r="B797" s="54"/>
       <c r="C797" s="55"/>
       <c r="D797" s="55"/>
-      <c r="E797" s="55"/>
+      <c r="E797" s="54"/>
       <c r="F797" s="55"/>
       <c r="G797" s="54"/>
     </row>
@@ -39840,7 +39848,7 @@
       <c r="B798" s="54"/>
       <c r="C798" s="55"/>
       <c r="D798" s="55"/>
-      <c r="E798" s="55"/>
+      <c r="E798" s="54"/>
       <c r="F798" s="55"/>
       <c r="G798" s="54"/>
     </row>
@@ -39848,7 +39856,7 @@
       <c r="B799" s="54"/>
       <c r="C799" s="55"/>
       <c r="D799" s="55"/>
-      <c r="E799" s="55"/>
+      <c r="E799" s="54"/>
       <c r="F799" s="55"/>
       <c r="G799" s="54"/>
     </row>
@@ -39856,7 +39864,7 @@
       <c r="B800" s="54"/>
       <c r="C800" s="55"/>
       <c r="D800" s="55"/>
-      <c r="E800" s="55"/>
+      <c r="E800" s="54"/>
       <c r="F800" s="55"/>
       <c r="G800" s="54"/>
     </row>
@@ -39864,7 +39872,7 @@
       <c r="B801" s="54"/>
       <c r="C801" s="55"/>
       <c r="D801" s="55"/>
-      <c r="E801" s="55"/>
+      <c r="E801" s="54"/>
       <c r="F801" s="55"/>
       <c r="G801" s="54"/>
     </row>
@@ -39872,7 +39880,7 @@
       <c r="B802" s="54"/>
       <c r="C802" s="55"/>
       <c r="D802" s="55"/>
-      <c r="E802" s="55"/>
+      <c r="E802" s="54"/>
       <c r="F802" s="55"/>
       <c r="G802" s="54"/>
     </row>
@@ -39880,7 +39888,7 @@
       <c r="B803" s="54"/>
       <c r="C803" s="55"/>
       <c r="D803" s="55"/>
-      <c r="E803" s="55"/>
+      <c r="E803" s="54"/>
       <c r="F803" s="55"/>
       <c r="G803" s="54"/>
     </row>
@@ -39888,7 +39896,7 @@
       <c r="B804" s="54"/>
       <c r="C804" s="55"/>
       <c r="D804" s="55"/>
-      <c r="E804" s="55"/>
+      <c r="E804" s="54"/>
       <c r="F804" s="55"/>
       <c r="G804" s="54"/>
     </row>
@@ -39896,7 +39904,7 @@
       <c r="B805" s="54"/>
       <c r="C805" s="55"/>
       <c r="D805" s="55"/>
-      <c r="E805" s="55"/>
+      <c r="E805" s="54"/>
       <c r="F805" s="55"/>
       <c r="G805" s="54"/>
     </row>
@@ -39904,7 +39912,7 @@
       <c r="B806" s="54"/>
       <c r="C806" s="55"/>
       <c r="D806" s="55"/>
-      <c r="E806" s="55"/>
+      <c r="E806" s="54"/>
       <c r="F806" s="55"/>
       <c r="G806" s="54"/>
     </row>
@@ -39912,7 +39920,7 @@
       <c r="B807" s="54"/>
       <c r="C807" s="55"/>
       <c r="D807" s="55"/>
-      <c r="E807" s="55"/>
+      <c r="E807" s="54"/>
       <c r="F807" s="55"/>
       <c r="G807" s="54"/>
     </row>
@@ -39920,7 +39928,7 @@
       <c r="B808" s="54"/>
       <c r="C808" s="55"/>
       <c r="D808" s="55"/>
-      <c r="E808" s="55"/>
+      <c r="E808" s="54"/>
       <c r="F808" s="55"/>
       <c r="G808" s="54"/>
     </row>
@@ -39928,7 +39936,7 @@
       <c r="B809" s="54"/>
       <c r="C809" s="55"/>
       <c r="D809" s="55"/>
-      <c r="E809" s="55"/>
+      <c r="E809" s="54"/>
       <c r="F809" s="55"/>
       <c r="G809" s="54"/>
     </row>
@@ -39936,7 +39944,7 @@
       <c r="B810" s="54"/>
       <c r="C810" s="55"/>
       <c r="D810" s="55"/>
-      <c r="E810" s="55"/>
+      <c r="E810" s="54"/>
       <c r="F810" s="55"/>
       <c r="G810" s="54"/>
     </row>
@@ -39944,7 +39952,7 @@
       <c r="B811" s="54"/>
       <c r="C811" s="55"/>
       <c r="D811" s="55"/>
-      <c r="E811" s="55"/>
+      <c r="E811" s="54"/>
       <c r="F811" s="55"/>
       <c r="G811" s="54"/>
     </row>
@@ -39952,7 +39960,7 @@
       <c r="B812" s="54"/>
       <c r="C812" s="55"/>
       <c r="D812" s="55"/>
-      <c r="E812" s="55"/>
+      <c r="E812" s="54"/>
       <c r="F812" s="55"/>
       <c r="G812" s="54"/>
     </row>
@@ -39960,7 +39968,7 @@
       <c r="B813" s="54"/>
       <c r="C813" s="55"/>
       <c r="D813" s="55"/>
-      <c r="E813" s="55"/>
+      <c r="E813" s="54"/>
       <c r="F813" s="55"/>
       <c r="G813" s="54"/>
     </row>
@@ -39968,7 +39976,7 @@
       <c r="B814" s="54"/>
       <c r="C814" s="55"/>
       <c r="D814" s="55"/>
-      <c r="E814" s="55"/>
+      <c r="E814" s="54"/>
       <c r="F814" s="55"/>
       <c r="G814" s="54"/>
     </row>
@@ -39976,7 +39984,7 @@
       <c r="B815" s="54"/>
       <c r="C815" s="55"/>
       <c r="D815" s="55"/>
-      <c r="E815" s="55"/>
+      <c r="E815" s="54"/>
       <c r="F815" s="55"/>
       <c r="G815" s="54"/>
     </row>
@@ -39984,7 +39992,7 @@
       <c r="B816" s="54"/>
       <c r="C816" s="55"/>
       <c r="D816" s="55"/>
-      <c r="E816" s="55"/>
+      <c r="E816" s="54"/>
       <c r="F816" s="55"/>
       <c r="G816" s="54"/>
     </row>
@@ -39992,7 +40000,7 @@
       <c r="B817" s="54"/>
       <c r="C817" s="55"/>
       <c r="D817" s="55"/>
-      <c r="E817" s="55"/>
+      <c r="E817" s="54"/>
       <c r="F817" s="55"/>
       <c r="G817" s="54"/>
     </row>
@@ -40000,7 +40008,7 @@
       <c r="B818" s="54"/>
       <c r="C818" s="55"/>
       <c r="D818" s="55"/>
-      <c r="E818" s="55"/>
+      <c r="E818" s="54"/>
       <c r="F818" s="55"/>
       <c r="G818" s="54"/>
     </row>
@@ -40008,7 +40016,7 @@
       <c r="B819" s="54"/>
       <c r="C819" s="55"/>
       <c r="D819" s="55"/>
-      <c r="E819" s="55"/>
+      <c r="E819" s="54"/>
       <c r="F819" s="55"/>
       <c r="G819" s="54"/>
     </row>
@@ -40016,7 +40024,7 @@
       <c r="B820" s="54"/>
       <c r="C820" s="55"/>
       <c r="D820" s="55"/>
-      <c r="E820" s="55"/>
+      <c r="E820" s="54"/>
       <c r="F820" s="55"/>
       <c r="G820" s="54"/>
     </row>
@@ -40024,7 +40032,7 @@
       <c r="B821" s="54"/>
       <c r="C821" s="55"/>
       <c r="D821" s="55"/>
-      <c r="E821" s="55"/>
+      <c r="E821" s="54"/>
       <c r="F821" s="55"/>
       <c r="G821" s="54"/>
     </row>
@@ -40032,7 +40040,7 @@
       <c r="B822" s="54"/>
       <c r="C822" s="55"/>
       <c r="D822" s="55"/>
-      <c r="E822" s="55"/>
+      <c r="E822" s="54"/>
       <c r="F822" s="55"/>
       <c r="G822" s="54"/>
     </row>
@@ -40040,7 +40048,7 @@
       <c r="B823" s="54"/>
       <c r="C823" s="55"/>
       <c r="D823" s="55"/>
-      <c r="E823" s="55"/>
+      <c r="E823" s="54"/>
       <c r="F823" s="55"/>
       <c r="G823" s="54"/>
     </row>
@@ -40048,7 +40056,7 @@
       <c r="B824" s="54"/>
       <c r="C824" s="55"/>
       <c r="D824" s="55"/>
-      <c r="E824" s="55"/>
+      <c r="E824" s="54"/>
       <c r="F824" s="55"/>
       <c r="G824" s="54"/>
     </row>
@@ -40056,7 +40064,7 @@
       <c r="B825" s="54"/>
       <c r="C825" s="55"/>
       <c r="D825" s="55"/>
-      <c r="E825" s="55"/>
+      <c r="E825" s="54"/>
       <c r="F825" s="55"/>
       <c r="G825" s="54"/>
     </row>
@@ -40064,7 +40072,7 @@
       <c r="B826" s="54"/>
       <c r="C826" s="55"/>
       <c r="D826" s="55"/>
-      <c r="E826" s="55"/>
+      <c r="E826" s="54"/>
       <c r="F826" s="55"/>
       <c r="G826" s="54"/>
     </row>
@@ -40072,7 +40080,7 @@
       <c r="B827" s="54"/>
       <c r="C827" s="55"/>
       <c r="D827" s="55"/>
-      <c r="E827" s="55"/>
+      <c r="E827" s="54"/>
       <c r="F827" s="55"/>
       <c r="G827" s="54"/>
     </row>
@@ -40080,7 +40088,7 @@
       <c r="B828" s="54"/>
       <c r="C828" s="55"/>
       <c r="D828" s="55"/>
-      <c r="E828" s="55"/>
+      <c r="E828" s="54"/>
       <c r="F828" s="55"/>
       <c r="G828" s="54"/>
     </row>
@@ -40088,7 +40096,7 @@
       <c r="B829" s="54"/>
       <c r="C829" s="55"/>
       <c r="D829" s="55"/>
-      <c r="E829" s="55"/>
+      <c r="E829" s="54"/>
       <c r="F829" s="55"/>
       <c r="G829" s="54"/>
     </row>
@@ -40096,7 +40104,7 @@
       <c r="B830" s="54"/>
       <c r="C830" s="55"/>
       <c r="D830" s="55"/>
-      <c r="E830" s="55"/>
+      <c r="E830" s="54"/>
       <c r="F830" s="55"/>
       <c r="G830" s="54"/>
     </row>
@@ -40104,7 +40112,7 @@
       <c r="B831" s="54"/>
       <c r="C831" s="55"/>
       <c r="D831" s="55"/>
-      <c r="E831" s="55"/>
+      <c r="E831" s="54"/>
       <c r="F831" s="55"/>
       <c r="G831" s="54"/>
     </row>
@@ -40112,7 +40120,7 @@
       <c r="B832" s="54"/>
       <c r="C832" s="55"/>
       <c r="D832" s="55"/>
-      <c r="E832" s="55"/>
+      <c r="E832" s="54"/>
       <c r="F832" s="55"/>
       <c r="G832" s="54"/>
     </row>
@@ -40120,7 +40128,7 @@
       <c r="B833" s="54"/>
       <c r="C833" s="55"/>
       <c r="D833" s="55"/>
-      <c r="E833" s="55"/>
+      <c r="E833" s="54"/>
       <c r="F833" s="55"/>
       <c r="G833" s="54"/>
     </row>
@@ -40128,7 +40136,7 @@
       <c r="B834" s="54"/>
       <c r="C834" s="55"/>
       <c r="D834" s="55"/>
-      <c r="E834" s="55"/>
+      <c r="E834" s="54"/>
       <c r="F834" s="55"/>
       <c r="G834" s="54"/>
     </row>
@@ -40136,7 +40144,7 @@
       <c r="B835" s="54"/>
       <c r="C835" s="55"/>
       <c r="D835" s="55"/>
-      <c r="E835" s="55"/>
+      <c r="E835" s="54"/>
       <c r="F835" s="55"/>
       <c r="G835" s="54"/>
     </row>
@@ -40144,7 +40152,7 @@
       <c r="B836" s="54"/>
       <c r="C836" s="55"/>
       <c r="D836" s="55"/>
-      <c r="E836" s="55"/>
+      <c r="E836" s="54"/>
       <c r="F836" s="55"/>
       <c r="G836" s="54"/>
     </row>
@@ -40152,7 +40160,7 @@
       <c r="B837" s="54"/>
       <c r="C837" s="55"/>
       <c r="D837" s="55"/>
-      <c r="E837" s="55"/>
+      <c r="E837" s="54"/>
       <c r="F837" s="55"/>
       <c r="G837" s="54"/>
     </row>
@@ -40160,7 +40168,7 @@
       <c r="B838" s="54"/>
       <c r="C838" s="55"/>
       <c r="D838" s="55"/>
-      <c r="E838" s="55"/>
+      <c r="E838" s="54"/>
       <c r="F838" s="55"/>
       <c r="G838" s="54"/>
     </row>
@@ -40168,7 +40176,7 @@
       <c r="B839" s="54"/>
       <c r="C839" s="55"/>
       <c r="D839" s="55"/>
-      <c r="E839" s="55"/>
+      <c r="E839" s="54"/>
       <c r="F839" s="55"/>
       <c r="G839" s="54"/>
     </row>
@@ -40176,7 +40184,7 @@
       <c r="B840" s="54"/>
       <c r="C840" s="55"/>
       <c r="D840" s="55"/>
-      <c r="E840" s="55"/>
+      <c r="E840" s="54"/>
       <c r="F840" s="55"/>
       <c r="G840" s="54"/>
     </row>
@@ -40184,7 +40192,7 @@
       <c r="B841" s="54"/>
       <c r="C841" s="55"/>
       <c r="D841" s="55"/>
-      <c r="E841" s="55"/>
+      <c r="E841" s="54"/>
       <c r="F841" s="55"/>
       <c r="G841" s="54"/>
     </row>
@@ -40192,7 +40200,7 @@
       <c r="B842" s="54"/>
       <c r="C842" s="55"/>
       <c r="D842" s="55"/>
-      <c r="E842" s="55"/>
+      <c r="E842" s="54"/>
       <c r="F842" s="55"/>
       <c r="G842" s="54"/>
     </row>
@@ -40200,7 +40208,7 @@
       <c r="B843" s="54"/>
       <c r="C843" s="55"/>
       <c r="D843" s="55"/>
-      <c r="E843" s="55"/>
+      <c r="E843" s="54"/>
       <c r="F843" s="55"/>
       <c r="G843" s="54"/>
     </row>
@@ -40208,7 +40216,7 @@
       <c r="B844" s="54"/>
       <c r="C844" s="55"/>
       <c r="D844" s="55"/>
-      <c r="E844" s="55"/>
+      <c r="E844" s="54"/>
       <c r="F844" s="55"/>
       <c r="G844" s="54"/>
     </row>
@@ -40216,7 +40224,7 @@
       <c r="B845" s="54"/>
       <c r="C845" s="55"/>
       <c r="D845" s="55"/>
-      <c r="E845" s="55"/>
+      <c r="E845" s="54"/>
       <c r="F845" s="55"/>
       <c r="G845" s="54"/>
     </row>
@@ -40224,7 +40232,7 @@
       <c r="B846" s="54"/>
       <c r="C846" s="55"/>
       <c r="D846" s="55"/>
-      <c r="E846" s="55"/>
+      <c r="E846" s="54"/>
       <c r="F846" s="55"/>
       <c r="G846" s="54"/>
     </row>
@@ -40232,7 +40240,7 @@
       <c r="B847" s="54"/>
       <c r="C847" s="55"/>
       <c r="D847" s="55"/>
-      <c r="E847" s="55"/>
+      <c r="E847" s="54"/>
       <c r="F847" s="55"/>
       <c r="G847" s="54"/>
     </row>
@@ -40240,7 +40248,7 @@
       <c r="B848" s="54"/>
       <c r="C848" s="55"/>
       <c r="D848" s="55"/>
-      <c r="E848" s="55"/>
+      <c r="E848" s="54"/>
       <c r="F848" s="55"/>
       <c r="G848" s="54"/>
     </row>
@@ -40248,7 +40256,7 @@
       <c r="B849" s="54"/>
       <c r="C849" s="55"/>
       <c r="D849" s="55"/>
-      <c r="E849" s="55"/>
+      <c r="E849" s="54"/>
       <c r="F849" s="55"/>
       <c r="G849" s="54"/>
     </row>
@@ -40256,7 +40264,7 @@
       <c r="B850" s="54"/>
       <c r="C850" s="55"/>
       <c r="D850" s="55"/>
-      <c r="E850" s="55"/>
+      <c r="E850" s="54"/>
       <c r="F850" s="55"/>
       <c r="G850" s="54"/>
     </row>
@@ -40264,7 +40272,7 @@
       <c r="B851" s="54"/>
       <c r="C851" s="55"/>
       <c r="D851" s="55"/>
-      <c r="E851" s="55"/>
+      <c r="E851" s="54"/>
       <c r="F851" s="55"/>
       <c r="G851" s="54"/>
     </row>
@@ -40272,7 +40280,7 @@
       <c r="B852" s="54"/>
       <c r="C852" s="55"/>
       <c r="D852" s="55"/>
-      <c r="E852" s="55"/>
+      <c r="E852" s="54"/>
       <c r="F852" s="55"/>
       <c r="G852" s="54"/>
     </row>
@@ -40280,7 +40288,7 @@
       <c r="B853" s="54"/>
       <c r="C853" s="55"/>
       <c r="D853" s="55"/>
-      <c r="E853" s="55"/>
+      <c r="E853" s="54"/>
       <c r="F853" s="55"/>
       <c r="G853" s="54"/>
     </row>
@@ -40288,7 +40296,7 @@
       <c r="B854" s="54"/>
       <c r="C854" s="55"/>
       <c r="D854" s="55"/>
-      <c r="E854" s="55"/>
+      <c r="E854" s="54"/>
       <c r="F854" s="55"/>
       <c r="G854" s="54"/>
     </row>
@@ -40296,7 +40304,7 @@
       <c r="B855" s="54"/>
       <c r="C855" s="55"/>
       <c r="D855" s="55"/>
-      <c r="E855" s="55"/>
+      <c r="E855" s="54"/>
       <c r="F855" s="55"/>
       <c r="G855" s="54"/>
     </row>
@@ -40304,7 +40312,7 @@
       <c r="B856" s="54"/>
       <c r="C856" s="55"/>
       <c r="D856" s="55"/>
-      <c r="E856" s="55"/>
+      <c r="E856" s="54"/>
       <c r="F856" s="55"/>
       <c r="G856" s="54"/>
     </row>
@@ -40312,7 +40320,7 @@
       <c r="B857" s="54"/>
       <c r="C857" s="55"/>
       <c r="D857" s="55"/>
-      <c r="E857" s="55"/>
+      <c r="E857" s="54"/>
       <c r="F857" s="55"/>
       <c r="G857" s="54"/>
     </row>
@@ -40320,7 +40328,7 @@
       <c r="B858" s="54"/>
       <c r="C858" s="55"/>
       <c r="D858" s="55"/>
-      <c r="E858" s="55"/>
+      <c r="E858" s="54"/>
       <c r="F858" s="55"/>
       <c r="G858" s="54"/>
     </row>
@@ -40328,7 +40336,7 @@
       <c r="B859" s="54"/>
       <c r="C859" s="55"/>
       <c r="D859" s="55"/>
-      <c r="E859" s="55"/>
+      <c r="E859" s="54"/>
       <c r="F859" s="55"/>
       <c r="G859" s="54"/>
     </row>
@@ -40336,7 +40344,7 @@
       <c r="B860" s="54"/>
       <c r="C860" s="55"/>
       <c r="D860" s="55"/>
-      <c r="E860" s="55"/>
+      <c r="E860" s="54"/>
       <c r="F860" s="55"/>
       <c r="G860" s="54"/>
     </row>
@@ -40344,7 +40352,7 @@
       <c r="B861" s="54"/>
       <c r="C861" s="55"/>
       <c r="D861" s="55"/>
-      <c r="E861" s="55"/>
+      <c r="E861" s="54"/>
       <c r="F861" s="55"/>
       <c r="G861" s="54"/>
     </row>
@@ -40352,7 +40360,7 @@
       <c r="B862" s="54"/>
       <c r="C862" s="55"/>
       <c r="D862" s="55"/>
-      <c r="E862" s="55"/>
+      <c r="E862" s="54"/>
       <c r="F862" s="55"/>
       <c r="G862" s="54"/>
     </row>
@@ -40360,7 +40368,7 @@
       <c r="B863" s="54"/>
       <c r="C863" s="55"/>
       <c r="D863" s="55"/>
-      <c r="E863" s="55"/>
+      <c r="E863" s="54"/>
       <c r="F863" s="55"/>
       <c r="G863" s="54"/>
     </row>
@@ -40368,7 +40376,7 @@
       <c r="B864" s="54"/>
       <c r="C864" s="55"/>
       <c r="D864" s="55"/>
-      <c r="E864" s="55"/>
+      <c r="E864" s="54"/>
       <c r="F864" s="55"/>
       <c r="G864" s="54"/>
     </row>
@@ -40376,7 +40384,7 @@
       <c r="B865" s="54"/>
       <c r="C865" s="55"/>
       <c r="D865" s="55"/>
-      <c r="E865" s="55"/>
+      <c r="E865" s="54"/>
       <c r="F865" s="55"/>
       <c r="G865" s="54"/>
     </row>
@@ -40384,7 +40392,7 @@
       <c r="B866" s="54"/>
       <c r="C866" s="55"/>
       <c r="D866" s="55"/>
-      <c r="E866" s="55"/>
+      <c r="E866" s="54"/>
       <c r="F866" s="55"/>
       <c r="G866" s="54"/>
     </row>
@@ -40392,7 +40400,7 @@
       <c r="B867" s="54"/>
       <c r="C867" s="55"/>
       <c r="D867" s="55"/>
-      <c r="E867" s="55"/>
+      <c r="E867" s="54"/>
       <c r="F867" s="55"/>
       <c r="G867" s="54"/>
     </row>
@@ -40400,7 +40408,7 @@
       <c r="B868" s="54"/>
       <c r="C868" s="55"/>
       <c r="D868" s="55"/>
-      <c r="E868" s="55"/>
+      <c r="E868" s="54"/>
       <c r="F868" s="55"/>
       <c r="G868" s="54"/>
     </row>
@@ -40408,7 +40416,7 @@
       <c r="B869" s="54"/>
       <c r="C869" s="55"/>
       <c r="D869" s="55"/>
-      <c r="E869" s="55"/>
+      <c r="E869" s="54"/>
       <c r="F869" s="55"/>
       <c r="G869" s="54"/>
     </row>
@@ -40416,7 +40424,7 @@
       <c r="B870" s="54"/>
       <c r="C870" s="55"/>
       <c r="D870" s="55"/>
-      <c r="E870" s="55"/>
+      <c r="E870" s="54"/>
       <c r="F870" s="55"/>
       <c r="G870" s="54"/>
     </row>
@@ -40424,7 +40432,7 @@
       <c r="B871" s="54"/>
       <c r="C871" s="55"/>
       <c r="D871" s="55"/>
-      <c r="E871" s="55"/>
+      <c r="E871" s="54"/>
       <c r="F871" s="55"/>
       <c r="G871" s="54"/>
     </row>
@@ -40432,7 +40440,7 @@
       <c r="B872" s="54"/>
       <c r="C872" s="55"/>
       <c r="D872" s="55"/>
-      <c r="E872" s="55"/>
+      <c r="E872" s="54"/>
       <c r="F872" s="55"/>
       <c r="G872" s="54"/>
     </row>
@@ -40440,7 +40448,7 @@
       <c r="B873" s="54"/>
       <c r="C873" s="55"/>
       <c r="D873" s="55"/>
-      <c r="E873" s="55"/>
+      <c r="E873" s="54"/>
       <c r="F873" s="55"/>
       <c r="G873" s="54"/>
     </row>
@@ -40448,7 +40456,7 @@
       <c r="B874" s="54"/>
       <c r="C874" s="55"/>
       <c r="D874" s="55"/>
-      <c r="E874" s="55"/>
+      <c r="E874" s="54"/>
       <c r="F874" s="55"/>
       <c r="G874" s="54"/>
     </row>
@@ -40456,7 +40464,7 @@
       <c r="B875" s="54"/>
       <c r="C875" s="55"/>
       <c r="D875" s="55"/>
-      <c r="E875" s="55"/>
+      <c r="E875" s="54"/>
       <c r="F875" s="55"/>
       <c r="G875" s="54"/>
     </row>
@@ -40464,7 +40472,7 @@
       <c r="B876" s="54"/>
       <c r="C876" s="55"/>
       <c r="D876" s="55"/>
-      <c r="E876" s="55"/>
+      <c r="E876" s="54"/>
       <c r="F876" s="55"/>
       <c r="G876" s="54"/>
     </row>
@@ -40472,7 +40480,7 @@
       <c r="B877" s="54"/>
       <c r="C877" s="55"/>
       <c r="D877" s="55"/>
-      <c r="E877" s="55"/>
+      <c r="E877" s="54"/>
       <c r="F877" s="55"/>
       <c r="G877" s="54"/>
     </row>
@@ -40480,7 +40488,7 @@
       <c r="B878" s="54"/>
       <c r="C878" s="55"/>
       <c r="D878" s="55"/>
-      <c r="E878" s="55"/>
+      <c r="E878" s="54"/>
       <c r="F878" s="55"/>
       <c r="G878" s="54"/>
     </row>
@@ -40488,7 +40496,7 @@
       <c r="B879" s="54"/>
       <c r="C879" s="55"/>
       <c r="D879" s="55"/>
-      <c r="E879" s="55"/>
+      <c r="E879" s="54"/>
       <c r="F879" s="55"/>
       <c r="G879" s="54"/>
     </row>
@@ -40496,7 +40504,7 @@
       <c r="B880" s="54"/>
       <c r="C880" s="55"/>
       <c r="D880" s="55"/>
-      <c r="E880" s="55"/>
+      <c r="E880" s="54"/>
       <c r="F880" s="55"/>
       <c r="G880" s="54"/>
     </row>
@@ -40504,7 +40512,7 @@
       <c r="B881" s="54"/>
       <c r="C881" s="55"/>
       <c r="D881" s="55"/>
-      <c r="E881" s="55"/>
+      <c r="E881" s="54"/>
       <c r="F881" s="55"/>
       <c r="G881" s="54"/>
     </row>
@@ -40512,7 +40520,7 @@
       <c r="B882" s="54"/>
       <c r="C882" s="55"/>
       <c r="D882" s="55"/>
-      <c r="E882" s="55"/>
+      <c r="E882" s="54"/>
       <c r="F882" s="55"/>
       <c r="G882" s="54"/>
     </row>
@@ -40520,7 +40528,7 @@
       <c r="B883" s="54"/>
       <c r="C883" s="55"/>
       <c r="D883" s="55"/>
-      <c r="E883" s="55"/>
+      <c r="E883" s="54"/>
       <c r="F883" s="55"/>
       <c r="G883" s="54"/>
     </row>
@@ -40528,7 +40536,7 @@
       <c r="B884" s="54"/>
       <c r="C884" s="55"/>
       <c r="D884" s="55"/>
-      <c r="E884" s="55"/>
+      <c r="E884" s="54"/>
       <c r="F884" s="55"/>
       <c r="G884" s="54"/>
     </row>
@@ -40536,7 +40544,7 @@
       <c r="B885" s="54"/>
       <c r="C885" s="55"/>
       <c r="D885" s="55"/>
-      <c r="E885" s="55"/>
+      <c r="E885" s="54"/>
       <c r="F885" s="55"/>
       <c r="G885" s="54"/>
     </row>
@@ -40544,7 +40552,7 @@
       <c r="B886" s="54"/>
       <c r="C886" s="55"/>
       <c r="D886" s="55"/>
-      <c r="E886" s="55"/>
+      <c r="E886" s="54"/>
       <c r="F886" s="55"/>
       <c r="G886" s="54"/>
     </row>
@@ -40552,7 +40560,7 @@
       <c r="B887" s="54"/>
       <c r="C887" s="55"/>
       <c r="D887" s="55"/>
-      <c r="E887" s="55"/>
+      <c r="E887" s="54"/>
       <c r="F887" s="55"/>
       <c r="G887" s="54"/>
     </row>
@@ -40560,7 +40568,7 @@
       <c r="B888" s="54"/>
       <c r="C888" s="55"/>
       <c r="D888" s="55"/>
-      <c r="E888" s="55"/>
+      <c r="E888" s="54"/>
       <c r="F888" s="55"/>
       <c r="G888" s="54"/>
     </row>
@@ -40568,7 +40576,7 @@
       <c r="B889" s="54"/>
       <c r="C889" s="55"/>
       <c r="D889" s="55"/>
-      <c r="E889" s="55"/>
+      <c r="E889" s="54"/>
       <c r="F889" s="55"/>
       <c r="G889" s="54"/>
     </row>
@@ -40576,7 +40584,7 @@
       <c r="B890" s="54"/>
       <c r="C890" s="55"/>
       <c r="D890" s="55"/>
-      <c r="E890" s="55"/>
+      <c r="E890" s="54"/>
       <c r="F890" s="55"/>
       <c r="G890" s="54"/>
     </row>
@@ -40584,7 +40592,7 @@
       <c r="B891" s="54"/>
       <c r="C891" s="55"/>
       <c r="D891" s="55"/>
-      <c r="E891" s="55"/>
+      <c r="E891" s="54"/>
       <c r="F891" s="55"/>
       <c r="G891" s="54"/>
     </row>
@@ -40592,7 +40600,7 @@
       <c r="B892" s="54"/>
       <c r="C892" s="55"/>
       <c r="D892" s="55"/>
-      <c r="E892" s="55"/>
+      <c r="E892" s="54"/>
       <c r="F892" s="55"/>
       <c r="G892" s="54"/>
     </row>
@@ -40600,7 +40608,7 @@
       <c r="B893" s="54"/>
       <c r="C893" s="55"/>
       <c r="D893" s="55"/>
-      <c r="E893" s="55"/>
+      <c r="E893" s="54"/>
       <c r="F893" s="55"/>
       <c r="G893" s="54"/>
     </row>
@@ -40608,7 +40616,7 @@
       <c r="B894" s="54"/>
       <c r="C894" s="55"/>
       <c r="D894" s="55"/>
-      <c r="E894" s="55"/>
+      <c r="E894" s="54"/>
       <c r="F894" s="55"/>
       <c r="G894" s="54"/>
     </row>
@@ -40616,7 +40624,7 @@
       <c r="B895" s="54"/>
       <c r="C895" s="55"/>
       <c r="D895" s="55"/>
-      <c r="E895" s="55"/>
+      <c r="E895" s="54"/>
       <c r="F895" s="55"/>
       <c r="G895" s="54"/>
     </row>
@@ -40624,7 +40632,7 @@
       <c r="B896" s="54"/>
       <c r="C896" s="55"/>
       <c r="D896" s="55"/>
-      <c r="E896" s="55"/>
+      <c r="E896" s="54"/>
       <c r="F896" s="55"/>
       <c r="G896" s="54"/>
     </row>
@@ -40632,7 +40640,7 @@
       <c r="B897" s="54"/>
       <c r="C897" s="55"/>
       <c r="D897" s="55"/>
-      <c r="E897" s="55"/>
+      <c r="E897" s="54"/>
       <c r="F897" s="55"/>
       <c r="G897" s="54"/>
     </row>
@@ -40640,7 +40648,7 @@
       <c r="B898" s="54"/>
       <c r="C898" s="55"/>
       <c r="D898" s="55"/>
-      <c r="E898" s="55"/>
+      <c r="E898" s="54"/>
       <c r="F898" s="55"/>
       <c r="G898" s="54"/>
     </row>
@@ -40648,7 +40656,7 @@
       <c r="B899" s="54"/>
       <c r="C899" s="55"/>
       <c r="D899" s="55"/>
-      <c r="E899" s="55"/>
+      <c r="E899" s="54"/>
       <c r="F899" s="55"/>
       <c r="G899" s="54"/>
     </row>
@@ -40656,7 +40664,7 @@
       <c r="B900" s="54"/>
       <c r="C900" s="55"/>
       <c r="D900" s="55"/>
-      <c r="E900" s="55"/>
+      <c r="E900" s="54"/>
       <c r="F900" s="55"/>
       <c r="G900" s="54"/>
     </row>
@@ -40664,7 +40672,7 @@
       <c r="B901" s="54"/>
       <c r="C901" s="55"/>
       <c r="D901" s="55"/>
-      <c r="E901" s="55"/>
+      <c r="E901" s="54"/>
       <c r="F901" s="55"/>
       <c r="G901" s="54"/>
     </row>
@@ -40672,7 +40680,7 @@
       <c r="B902" s="54"/>
       <c r="C902" s="55"/>
       <c r="D902" s="55"/>
-      <c r="E902" s="55"/>
+      <c r="E902" s="54"/>
       <c r="F902" s="55"/>
       <c r="G902" s="54"/>
     </row>
@@ -40680,7 +40688,7 @@
       <c r="B903" s="54"/>
       <c r="C903" s="55"/>
       <c r="D903" s="55"/>
-      <c r="E903" s="55"/>
+      <c r="E903" s="54"/>
       <c r="F903" s="55"/>
       <c r="G903" s="54"/>
     </row>
@@ -40688,7 +40696,7 @@
       <c r="B904" s="54"/>
       <c r="C904" s="55"/>
       <c r="D904" s="55"/>
-      <c r="E904" s="55"/>
+      <c r="E904" s="54"/>
       <c r="F904" s="55"/>
       <c r="G904" s="54"/>
     </row>
@@ -40696,7 +40704,7 @@
       <c r="B905" s="54"/>
       <c r="C905" s="55"/>
       <c r="D905" s="55"/>
-      <c r="E905" s="55"/>
+      <c r="E905" s="54"/>
       <c r="F905" s="55"/>
       <c r="G905" s="54"/>
     </row>
@@ -40704,7 +40712,7 @@
       <c r="B906" s="54"/>
       <c r="C906" s="55"/>
       <c r="D906" s="55"/>
-      <c r="E906" s="55"/>
+      <c r="E906" s="54"/>
       <c r="F906" s="55"/>
       <c r="G906" s="54"/>
     </row>
@@ -40712,7 +40720,7 @@
       <c r="B907" s="54"/>
       <c r="C907" s="55"/>
       <c r="D907" s="55"/>
-      <c r="E907" s="55"/>
+      <c r="E907" s="54"/>
       <c r="F907" s="55"/>
       <c r="G907" s="54"/>
     </row>
@@ -40720,7 +40728,7 @@
       <c r="B908" s="54"/>
       <c r="C908" s="55"/>
       <c r="D908" s="55"/>
-      <c r="E908" s="55"/>
+      <c r="E908" s="54"/>
       <c r="F908" s="55"/>
       <c r="G908" s="54"/>
     </row>
@@ -40728,7 +40736,7 @@
       <c r="B909" s="54"/>
       <c r="C909" s="55"/>
       <c r="D909" s="55"/>
-      <c r="E909" s="55"/>
+      <c r="E909" s="54"/>
       <c r="F909" s="55"/>
       <c r="G909" s="54"/>
     </row>
@@ -40736,7 +40744,7 @@
       <c r="B910" s="54"/>
       <c r="C910" s="55"/>
       <c r="D910" s="55"/>
-      <c r="E910" s="55"/>
+      <c r="E910" s="54"/>
       <c r="F910" s="55"/>
       <c r="G910" s="54"/>
     </row>
@@ -40744,7 +40752,7 @@
       <c r="B911" s="54"/>
       <c r="C911" s="55"/>
       <c r="D911" s="55"/>
-      <c r="E911" s="55"/>
+      <c r="E911" s="54"/>
       <c r="F911" s="55"/>
       <c r="G911" s="54"/>
     </row>
@@ -40752,7 +40760,7 @@
       <c r="B912" s="54"/>
       <c r="C912" s="55"/>
       <c r="D912" s="55"/>
-      <c r="E912" s="55"/>
+      <c r="E912" s="54"/>
       <c r="F912" s="55"/>
       <c r="G912" s="54"/>
     </row>
@@ -40760,7 +40768,7 @@
       <c r="B913" s="54"/>
       <c r="C913" s="55"/>
       <c r="D913" s="55"/>
-      <c r="E913" s="55"/>
+      <c r="E913" s="54"/>
       <c r="F913" s="55"/>
       <c r="G913" s="54"/>
     </row>
@@ -40768,7 +40776,7 @@
       <c r="B914" s="54"/>
       <c r="C914" s="55"/>
       <c r="D914" s="55"/>
-      <c r="E914" s="55"/>
+      <c r="E914" s="54"/>
       <c r="F914" s="55"/>
       <c r="G914" s="54"/>
     </row>
@@ -40776,7 +40784,7 @@
       <c r="B915" s="54"/>
       <c r="C915" s="55"/>
       <c r="D915" s="55"/>
-      <c r="E915" s="55"/>
+      <c r="E915" s="54"/>
       <c r="F915" s="55"/>
       <c r="G915" s="54"/>
     </row>
@@ -40784,7 +40792,7 @@
       <c r="B916" s="54"/>
       <c r="C916" s="55"/>
       <c r="D916" s="55"/>
-      <c r="E916" s="55"/>
+      <c r="E916" s="54"/>
       <c r="F916" s="55"/>
       <c r="G916" s="54"/>
     </row>
@@ -40792,7 +40800,7 @@
       <c r="B917" s="54"/>
       <c r="C917" s="55"/>
       <c r="D917" s="55"/>
-      <c r="E917" s="55"/>
+      <c r="E917" s="54"/>
       <c r="F917" s="55"/>
       <c r="G917" s="54"/>
     </row>
@@ -40800,7 +40808,7 @@
       <c r="B918" s="54"/>
       <c r="C918" s="55"/>
       <c r="D918" s="55"/>
-      <c r="E918" s="55"/>
+      <c r="E918" s="54"/>
       <c r="F918" s="55"/>
       <c r="G918" s="54"/>
     </row>
@@ -40808,7 +40816,7 @@
       <c r="B919" s="54"/>
       <c r="C919" s="55"/>
       <c r="D919" s="55"/>
-      <c r="E919" s="55"/>
+      <c r="E919" s="54"/>
       <c r="F919" s="55"/>
       <c r="G919" s="54"/>
     </row>
@@ -40816,7 +40824,7 @@
       <c r="B920" s="54"/>
       <c r="C920" s="55"/>
       <c r="D920" s="55"/>
-      <c r="E920" s="55"/>
+      <c r="E920" s="54"/>
       <c r="F920" s="55"/>
       <c r="G920" s="54"/>
     </row>
@@ -40824,7 +40832,7 @@
       <c r="B921" s="54"/>
       <c r="C921" s="55"/>
       <c r="D921" s="55"/>
-      <c r="E921" s="55"/>
+      <c r="E921" s="54"/>
       <c r="F921" s="55"/>
       <c r="G921" s="54"/>
     </row>
@@ -40832,7 +40840,7 @@
       <c r="B922" s="54"/>
       <c r="C922" s="55"/>
       <c r="D922" s="55"/>
-      <c r="E922" s="55"/>
+      <c r="E922" s="54"/>
       <c r="F922" s="55"/>
       <c r="G922" s="54"/>
     </row>
@@ -40840,7 +40848,7 @@
       <c r="B923" s="54"/>
       <c r="C923" s="55"/>
       <c r="D923" s="55"/>
-      <c r="E923" s="55"/>
+      <c r="E923" s="54"/>
       <c r="F923" s="55"/>
       <c r="G923" s="54"/>
     </row>
@@ -40848,7 +40856,7 @@
       <c r="B924" s="54"/>
       <c r="C924" s="55"/>
       <c r="D924" s="55"/>
-      <c r="E924" s="55"/>
+      <c r="E924" s="54"/>
       <c r="F924" s="55"/>
       <c r="G924" s="54"/>
     </row>
@@ -40856,7 +40864,7 @@
       <c r="B925" s="54"/>
       <c r="C925" s="55"/>
       <c r="D925" s="55"/>
-      <c r="E925" s="55"/>
+      <c r="E925" s="54"/>
       <c r="F925" s="55"/>
       <c r="G925" s="54"/>
     </row>
@@ -40864,7 +40872,7 @@
       <c r="B926" s="54"/>
       <c r="C926" s="55"/>
       <c r="D926" s="55"/>
-      <c r="E926" s="55"/>
+      <c r="E926" s="54"/>
       <c r="F926" s="55"/>
       <c r="G926" s="54"/>
     </row>
@@ -40872,7 +40880,7 @@
       <c r="B927" s="54"/>
       <c r="C927" s="55"/>
       <c r="D927" s="55"/>
-      <c r="E927" s="55"/>
+      <c r="E927" s="54"/>
       <c r="F927" s="55"/>
       <c r="G927" s="54"/>
     </row>
@@ -40880,7 +40888,7 @@
       <c r="B928" s="54"/>
       <c r="C928" s="55"/>
       <c r="D928" s="55"/>
-      <c r="E928" s="55"/>
+      <c r="E928" s="54"/>
       <c r="F928" s="55"/>
       <c r="G928" s="54"/>
     </row>
@@ -40888,7 +40896,7 @@
       <c r="B929" s="54"/>
       <c r="C929" s="55"/>
       <c r="D929" s="55"/>
-      <c r="E929" s="55"/>
+      <c r="E929" s="54"/>
       <c r="F929" s="55"/>
       <c r="G929" s="54"/>
     </row>
@@ -40896,7 +40904,7 @@
       <c r="B930" s="54"/>
       <c r="C930" s="55"/>
       <c r="D930" s="55"/>
-      <c r="E930" s="55"/>
+      <c r="E930" s="54"/>
       <c r="F930" s="55"/>
       <c r="G930" s="54"/>
     </row>
@@ -40904,7 +40912,7 @@
       <c r="B931" s="54"/>
       <c r="C931" s="55"/>
       <c r="D931" s="55"/>
-      <c r="E931" s="55"/>
+      <c r="E931" s="54"/>
       <c r="F931" s="55"/>
       <c r="G931" s="54"/>
     </row>
@@ -40912,7 +40920,7 @@
       <c r="B932" s="54"/>
       <c r="C932" s="55"/>
       <c r="D932" s="55"/>
-      <c r="E932" s="55"/>
+      <c r="E932" s="54"/>
       <c r="F932" s="55"/>
       <c r="G932" s="54"/>
     </row>
@@ -40920,7 +40928,7 @@
       <c r="B933" s="54"/>
       <c r="C933" s="55"/>
       <c r="D933" s="55"/>
-      <c r="E933" s="55"/>
+      <c r="E933" s="54"/>
       <c r="F933" s="55"/>
       <c r="G933" s="54"/>
     </row>
@@ -40928,7 +40936,7 @@
       <c r="B934" s="54"/>
       <c r="C934" s="55"/>
       <c r="D934" s="55"/>
-      <c r="E934" s="55"/>
+      <c r="E934" s="54"/>
       <c r="F934" s="55"/>
       <c r="G934" s="54"/>
     </row>
@@ -40936,7 +40944,7 @@
       <c r="B935" s="54"/>
       <c r="C935" s="55"/>
       <c r="D935" s="55"/>
-      <c r="E935" s="55"/>
+      <c r="E935" s="54"/>
       <c r="F935" s="55"/>
       <c r="G935" s="54"/>
     </row>
@@ -40944,7 +40952,7 @@
       <c r="B936" s="54"/>
       <c r="C936" s="55"/>
       <c r="D936" s="55"/>
-      <c r="E936" s="55"/>
+      <c r="E936" s="54"/>
       <c r="F936" s="55"/>
       <c r="G936" s="54"/>
     </row>
@@ -40952,7 +40960,7 @@
       <c r="B937" s="54"/>
       <c r="C937" s="55"/>
       <c r="D937" s="55"/>
-      <c r="E937" s="55"/>
+      <c r="E937" s="54"/>
       <c r="F937" s="55"/>
       <c r="G937" s="54"/>
     </row>
@@ -40960,7 +40968,7 @@
       <c r="B938" s="54"/>
       <c r="C938" s="55"/>
       <c r="D938" s="55"/>
-      <c r="E938" s="55"/>
+      <c r="E938" s="54"/>
       <c r="F938" s="55"/>
       <c r="G938" s="54"/>
     </row>
@@ -40968,7 +40976,7 @@
       <c r="B939" s="54"/>
       <c r="C939" s="55"/>
       <c r="D939" s="55"/>
-      <c r="E939" s="55"/>
+      <c r="E939" s="54"/>
       <c r="F939" s="55"/>
       <c r="G939" s="54"/>
     </row>
@@ -40976,7 +40984,7 @@
       <c r="B940" s="54"/>
       <c r="C940" s="55"/>
       <c r="D940" s="55"/>
-      <c r="E940" s="55"/>
+      <c r="E940" s="54"/>
       <c r="F940" s="55"/>
       <c r="G940" s="54"/>
     </row>
@@ -40984,7 +40992,7 @@
       <c r="B941" s="54"/>
       <c r="C941" s="55"/>
       <c r="D941" s="55"/>
-      <c r="E941" s="55"/>
+      <c r="E941" s="54"/>
       <c r="F941" s="55"/>
       <c r="G941" s="54"/>
     </row>
@@ -40992,7 +41000,7 @@
       <c r="B942" s="54"/>
       <c r="C942" s="55"/>
       <c r="D942" s="55"/>
-      <c r="E942" s="55"/>
+      <c r="E942" s="54"/>
       <c r="F942" s="55"/>
       <c r="G942" s="54"/>
     </row>
@@ -41000,7 +41008,7 @@
       <c r="B943" s="54"/>
       <c r="C943" s="55"/>
       <c r="D943" s="55"/>
-      <c r="E943" s="55"/>
+      <c r="E943" s="54"/>
       <c r="F943" s="55"/>
       <c r="G943" s="54"/>
     </row>
@@ -41008,7 +41016,7 @@
       <c r="B944" s="54"/>
       <c r="C944" s="55"/>
       <c r="D944" s="55"/>
-      <c r="E944" s="55"/>
+      <c r="E944" s="54"/>
       <c r="F944" s="55"/>
       <c r="G944" s="54"/>
     </row>
@@ -41016,7 +41024,7 @@
       <c r="B945" s="54"/>
       <c r="C945" s="55"/>
       <c r="D945" s="55"/>
-      <c r="E945" s="55"/>
+      <c r="E945" s="54"/>
       <c r="F945" s="55"/>
       <c r="G945" s="54"/>
     </row>
@@ -41024,7 +41032,7 @@
       <c r="B946" s="54"/>
       <c r="C946" s="55"/>
       <c r="D946" s="55"/>
-      <c r="E946" s="55"/>
+      <c r="E946" s="54"/>
       <c r="F946" s="55"/>
       <c r="G946" s="54"/>
     </row>
@@ -41032,7 +41040,7 @@
       <c r="B947" s="54"/>
       <c r="C947" s="55"/>
       <c r="D947" s="55"/>
-      <c r="E947" s="55"/>
+      <c r="E947" s="54"/>
       <c r="F947" s="55"/>
       <c r="G947" s="54"/>
     </row>
@@ -41040,7 +41048,7 @@
       <c r="B948" s="54"/>
       <c r="C948" s="55"/>
       <c r="D948" s="55"/>
-      <c r="E948" s="55"/>
+      <c r="E948" s="54"/>
       <c r="F948" s="55"/>
       <c r="G948" s="54"/>
     </row>
@@ -41048,7 +41056,7 @@
       <c r="B949" s="54"/>
       <c r="C949" s="55"/>
       <c r="D949" s="55"/>
-      <c r="E949" s="55"/>
+      <c r="E949" s="54"/>
       <c r="F949" s="55"/>
       <c r="G949" s="54"/>
     </row>
@@ -41056,7 +41064,7 @@
       <c r="B950" s="54"/>
       <c r="C950" s="55"/>
       <c r="D950" s="55"/>
-      <c r="E950" s="55"/>
+      <c r="E950" s="54"/>
       <c r="F950" s="55"/>
       <c r="G950" s="54"/>
     </row>
@@ -41064,7 +41072,7 @@
       <c r="B951" s="54"/>
       <c r="C951" s="55"/>
       <c r="D951" s="55"/>
-      <c r="E951" s="55"/>
+      <c r="E951" s="54"/>
       <c r="F951" s="55"/>
       <c r="G951" s="54"/>
     </row>
@@ -41072,7 +41080,7 @@
       <c r="B952" s="54"/>
       <c r="C952" s="55"/>
       <c r="D952" s="55"/>
-      <c r="E952" s="55"/>
+      <c r="E952" s="54"/>
       <c r="F952" s="55"/>
       <c r="G952" s="54"/>
     </row>
@@ -41080,7 +41088,7 @@
       <c r="B953" s="54"/>
       <c r="C953" s="55"/>
       <c r="D953" s="55"/>
-      <c r="E953" s="55"/>
+      <c r="E953" s="54"/>
       <c r="F953" s="55"/>
       <c r="G953" s="54"/>
     </row>
@@ -41088,7 +41096,7 @@
       <c r="B954" s="54"/>
       <c r="C954" s="55"/>
       <c r="D954" s="55"/>
-      <c r="E954" s="55"/>
+      <c r="E954" s="54"/>
       <c r="F954" s="55"/>
       <c r="G954" s="54"/>
     </row>
@@ -41096,7 +41104,7 @@
       <c r="B955" s="54"/>
       <c r="C955" s="55"/>
       <c r="D955" s="55"/>
-      <c r="E955" s="55"/>
+      <c r="E955" s="54"/>
       <c r="F955" s="55"/>
       <c r="G955" s="54"/>
     </row>
@@ -41104,7 +41112,7 @@
       <c r="B956" s="54"/>
       <c r="C956" s="55"/>
       <c r="D956" s="55"/>
-      <c r="E956" s="55"/>
+      <c r="E956" s="54"/>
       <c r="F956" s="55"/>
       <c r="G956" s="54"/>
     </row>
@@ -41112,7 +41120,7 @@
       <c r="B957" s="54"/>
       <c r="C957" s="55"/>
       <c r="D957" s="55"/>
-      <c r="E957" s="55"/>
+      <c r="E957" s="54"/>
       <c r="F957" s="55"/>
       <c r="G957" s="54"/>
     </row>
@@ -41120,7 +41128,7 @@
       <c r="B958" s="54"/>
       <c r="C958" s="55"/>
       <c r="D958" s="55"/>
-      <c r="E958" s="55"/>
+      <c r="E958" s="54"/>
       <c r="F958" s="55"/>
       <c r="G958" s="54"/>
     </row>
@@ -41128,7 +41136,7 @@
       <c r="B959" s="54"/>
       <c r="C959" s="55"/>
       <c r="D959" s="55"/>
-      <c r="E959" s="55"/>
+      <c r="E959" s="54"/>
       <c r="F959" s="55"/>
       <c r="G959" s="54"/>
     </row>
@@ -41136,7 +41144,7 @@
       <c r="B960" s="54"/>
       <c r="C960" s="55"/>
       <c r="D960" s="55"/>
-      <c r="E960" s="55"/>
+      <c r="E960" s="54"/>
       <c r="F960" s="55"/>
       <c r="G960" s="54"/>
     </row>
@@ -41144,7 +41152,7 @@
       <c r="B961" s="54"/>
       <c r="C961" s="55"/>
       <c r="D961" s="55"/>
-      <c r="E961" s="55"/>
+      <c r="E961" s="54"/>
       <c r="F961" s="55"/>
       <c r="G961" s="54"/>
     </row>
@@ -41152,7 +41160,7 @@
       <c r="B962" s="54"/>
       <c r="C962" s="55"/>
       <c r="D962" s="55"/>
-      <c r="E962" s="55"/>
+      <c r="E962" s="54"/>
       <c r="F962" s="55"/>
       <c r="G962" s="54"/>
     </row>
@@ -41160,7 +41168,7 @@
       <c r="B963" s="54"/>
       <c r="C963" s="55"/>
       <c r="D963" s="55"/>
-      <c r="E963" s="55"/>
+      <c r="E963" s="54"/>
       <c r="F963" s="55"/>
       <c r="G963" s="54"/>
     </row>
@@ -41168,7 +41176,7 @@
       <c r="B964" s="54"/>
       <c r="C964" s="55"/>
       <c r="D964" s="55"/>
-      <c r="E964" s="55"/>
+      <c r="E964" s="54"/>
       <c r="F964" s="55"/>
       <c r="G964" s="54"/>
     </row>
@@ -41176,7 +41184,7 @@
       <c r="B965" s="54"/>
       <c r="C965" s="55"/>
       <c r="D965" s="55"/>
-      <c r="E965" s="55"/>
+      <c r="E965" s="54"/>
       <c r="F965" s="55"/>
       <c r="G965" s="54"/>
     </row>
@@ -41184,7 +41192,7 @@
       <c r="B966" s="54"/>
       <c r="C966" s="55"/>
       <c r="D966" s="55"/>
-      <c r="E966" s="55"/>
+      <c r="E966" s="54"/>
       <c r="F966" s="55"/>
       <c r="G966" s="54"/>
     </row>
@@ -41192,7 +41200,7 @@
       <c r="B967" s="54"/>
       <c r="C967" s="55"/>
       <c r="D967" s="55"/>
-      <c r="E967" s="55"/>
+      <c r="E967" s="54"/>
       <c r="F967" s="55"/>
       <c r="G967" s="54"/>
     </row>
@@ -41200,7 +41208,7 @@
       <c r="B968" s="54"/>
       <c r="C968" s="55"/>
       <c r="D968" s="55"/>
-      <c r="E968" s="55"/>
+      <c r="E968" s="54"/>
       <c r="F968" s="55"/>
       <c r="G968" s="54"/>
     </row>
@@ -41208,7 +41216,7 @@
       <c r="B969" s="54"/>
       <c r="C969" s="55"/>
       <c r="D969" s="55"/>
-      <c r="E969" s="55"/>
+      <c r="E969" s="54"/>
       <c r="F969" s="55"/>
       <c r="G969" s="54"/>
     </row>
@@ -41216,7 +41224,7 @@
       <c r="B970" s="54"/>
       <c r="C970" s="55"/>
       <c r="D970" s="55"/>
-      <c r="E970" s="55"/>
+      <c r="E970" s="54"/>
       <c r="F970" s="55"/>
       <c r="G970" s="54"/>
     </row>
@@ -41224,7 +41232,7 @@
       <c r="B971" s="54"/>
       <c r="C971" s="55"/>
       <c r="D971" s="55"/>
-      <c r="E971" s="55"/>
+      <c r="E971" s="54"/>
       <c r="F971" s="55"/>
       <c r="G971" s="54"/>
     </row>
@@ -41232,7 +41240,7 @@
       <c r="B972" s="54"/>
       <c r="C972" s="55"/>
       <c r="D972" s="55"/>
-      <c r="E972" s="55"/>
+      <c r="E972" s="54"/>
       <c r="F972" s="55"/>
       <c r="G972" s="54"/>
     </row>
@@ -41240,7 +41248,7 @@
       <c r="B973" s="54"/>
       <c r="C973" s="55"/>
       <c r="D973" s="55"/>
-      <c r="E973" s="55"/>
+      <c r="E973" s="54"/>
       <c r="F973" s="55"/>
       <c r="G973" s="54"/>
     </row>
@@ -41248,7 +41256,7 @@
       <c r="B974" s="54"/>
       <c r="C974" s="55"/>
       <c r="D974" s="55"/>
-      <c r="E974" s="55"/>
+      <c r="E974" s="54"/>
       <c r="F974" s="55"/>
       <c r="G974" s="54"/>
     </row>
@@ -41256,7 +41264,7 @@
       <c r="B975" s="54"/>
       <c r="C975" s="55"/>
       <c r="D975" s="55"/>
-      <c r="E975" s="55"/>
+      <c r="E975" s="54"/>
       <c r="F975" s="55"/>
       <c r="G975" s="54"/>
     </row>
@@ -41264,7 +41272,7 @@
       <c r="B976" s="54"/>
       <c r="C976" s="55"/>
       <c r="D976" s="55"/>
-      <c r="E976" s="55"/>
+      <c r="E976" s="54"/>
       <c r="F976" s="55"/>
       <c r="G976" s="54"/>
     </row>
@@ -41272,7 +41280,7 @@
       <c r="B977" s="54"/>
       <c r="C977" s="55"/>
       <c r="D977" s="55"/>
-      <c r="E977" s="55"/>
+      <c r="E977" s="54"/>
       <c r="F977" s="55"/>
       <c r="G977" s="54"/>
     </row>
@@ -41280,7 +41288,7 @@
       <c r="B978" s="54"/>
       <c r="C978" s="55"/>
       <c r="D978" s="55"/>
-      <c r="E978" s="55"/>
+      <c r="E978" s="54"/>
       <c r="F978" s="55"/>
       <c r="G978" s="54"/>
     </row>
@@ -41288,7 +41296,7 @@
       <c r="B979" s="54"/>
       <c r="C979" s="55"/>
       <c r="D979" s="55"/>
-      <c r="E979" s="55"/>
+      <c r="E979" s="54"/>
       <c r="F979" s="55"/>
       <c r="G979" s="54"/>
     </row>
@@ -41296,7 +41304,7 @@
       <c r="B980" s="54"/>
       <c r="C980" s="55"/>
       <c r="D980" s="55"/>
-      <c r="E980" s="55"/>
+      <c r="E980" s="54"/>
       <c r="F980" s="55"/>
       <c r="G980" s="54"/>
     </row>
@@ -41304,7 +41312,7 @@
       <c r="B981" s="54"/>
       <c r="C981" s="55"/>
       <c r="D981" s="55"/>
-      <c r="E981" s="55"/>
+      <c r="E981" s="54"/>
       <c r="F981" s="55"/>
       <c r="G981" s="54"/>
     </row>
@@ -41312,7 +41320,7 @@
       <c r="B982" s="54"/>
       <c r="C982" s="55"/>
       <c r="D982" s="55"/>
-      <c r="E982" s="55"/>
+      <c r="E982" s="54"/>
       <c r="F982" s="55"/>
       <c r="G982" s="54"/>
     </row>
@@ -41320,7 +41328,7 @@
       <c r="B983" s="54"/>
       <c r="C983" s="55"/>
       <c r="D983" s="55"/>
-      <c r="E983" s="55"/>
+      <c r="E983" s="54"/>
       <c r="F983" s="55"/>
       <c r="G983" s="54"/>
     </row>
@@ -41328,7 +41336,7 @@
       <c r="B984" s="54"/>
       <c r="C984" s="55"/>
       <c r="D984" s="55"/>
-      <c r="E984" s="55"/>
+      <c r="E984" s="54"/>
       <c r="F984" s="55"/>
       <c r="G984" s="54"/>
     </row>
@@ -41336,7 +41344,7 @@
       <c r="B985" s="54"/>
       <c r="C985" s="55"/>
       <c r="D985" s="55"/>
-      <c r="E985" s="55"/>
+      <c r="E985" s="54"/>
       <c r="F985" s="55"/>
       <c r="G985" s="54"/>
     </row>
@@ -41344,7 +41352,7 @@
       <c r="B986" s="54"/>
       <c r="C986" s="55"/>
       <c r="D986" s="55"/>
-      <c r="E986" s="55"/>
+      <c r="E986" s="54"/>
       <c r="F986" s="55"/>
       <c r="G986" s="54"/>
     </row>
@@ -41352,7 +41360,7 @@
       <c r="B987" s="54"/>
       <c r="C987" s="55"/>
       <c r="D987" s="55"/>
-      <c r="E987" s="55"/>
+      <c r="E987" s="54"/>
       <c r="F987" s="55"/>
       <c r="G987" s="54"/>
     </row>
@@ -41360,7 +41368,7 @@
       <c r="B988" s="54"/>
       <c r="C988" s="55"/>
       <c r="D988" s="55"/>
-      <c r="E988" s="55"/>
+      <c r="E988" s="54"/>
       <c r="F988" s="55"/>
       <c r="G988" s="54"/>
     </row>
@@ -41368,7 +41376,7 @@
       <c r="B989" s="54"/>
       <c r="C989" s="55"/>
       <c r="D989" s="55"/>
-      <c r="E989" s="55"/>
+      <c r="E989" s="54"/>
       <c r="F989" s="55"/>
       <c r="G989" s="54"/>
     </row>
@@ -41376,7 +41384,7 @@
       <c r="B990" s="54"/>
       <c r="C990" s="55"/>
       <c r="D990" s="55"/>
-      <c r="E990" s="55"/>
+      <c r="E990" s="54"/>
       <c r="F990" s="55"/>
       <c r="G990" s="54"/>
     </row>
@@ -41384,7 +41392,7 @@
       <c r="B991" s="54"/>
       <c r="C991" s="55"/>
       <c r="D991" s="55"/>
-      <c r="E991" s="55"/>
+      <c r="E991" s="54"/>
       <c r="F991" s="55"/>
       <c r="G991" s="54"/>
     </row>
@@ -41392,7 +41400,7 @@
       <c r="B992" s="54"/>
       <c r="C992" s="55"/>
       <c r="D992" s="55"/>
-      <c r="E992" s="55"/>
+      <c r="E992" s="54"/>
       <c r="F992" s="55"/>
       <c r="G992" s="54"/>
     </row>
@@ -41400,7 +41408,7 @@
       <c r="B993" s="54"/>
       <c r="C993" s="55"/>
       <c r="D993" s="55"/>
-      <c r="E993" s="55"/>
+      <c r="E993" s="54"/>
       <c r="F993" s="55"/>
       <c r="G993" s="54"/>
     </row>
@@ -41408,7 +41416,7 @@
       <c r="B994" s="54"/>
       <c r="C994" s="55"/>
       <c r="D994" s="55"/>
-      <c r="E994" s="55"/>
+      <c r="E994" s="54"/>
       <c r="F994" s="55"/>
       <c r="G994" s="54"/>
     </row>
@@ -41416,7 +41424,7 @@
       <c r="B995" s="54"/>
       <c r="C995" s="55"/>
       <c r="D995" s="55"/>
-      <c r="E995" s="55"/>
+      <c r="E995" s="54"/>
       <c r="F995" s="55"/>
       <c r="G995" s="54"/>
     </row>
@@ -41424,7 +41432,7 @@
       <c r="B996" s="54"/>
       <c r="C996" s="55"/>
       <c r="D996" s="55"/>
-      <c r="E996" s="55"/>
+      <c r="E996" s="54"/>
       <c r="F996" s="55"/>
       <c r="G996" s="54"/>
     </row>
@@ -41432,7 +41440,7 @@
       <c r="B997" s="54"/>
       <c r="C997" s="55"/>
       <c r="D997" s="55"/>
-      <c r="E997" s="55"/>
+      <c r="E997" s="54"/>
       <c r="F997" s="55"/>
       <c r="G997" s="54"/>
     </row>
@@ -41440,7 +41448,7 @@
       <c r="B998" s="54"/>
       <c r="C998" s="55"/>
       <c r="D998" s="55"/>
-      <c r="E998" s="55"/>
+      <c r="E998" s="54"/>
       <c r="F998" s="55"/>
       <c r="G998" s="54"/>
     </row>
@@ -41448,7 +41456,7 @@
       <c r="B999" s="54"/>
       <c r="C999" s="55"/>
       <c r="D999" s="55"/>
-      <c r="E999" s="55"/>
+      <c r="E999" s="54"/>
       <c r="F999" s="55"/>
       <c r="G999" s="54"/>
     </row>
@@ -41456,7 +41464,7 @@
       <c r="B1000" s="54"/>
       <c r="C1000" s="55"/>
       <c r="D1000" s="55"/>
-      <c r="E1000" s="55"/>
+      <c r="E1000" s="54"/>
       <c r="F1000" s="55"/>
       <c r="G1000" s="54"/>
     </row>
@@ -41493,16 +41501,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="49" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E1" s="50" t="s">
         <v>92</v>
@@ -41533,63 +41541,63 @@
     </row>
     <row r="2">
       <c r="A2" s="52" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B2" s="52" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="52" t="s">
-        <v>108</v>
+      <c r="B3" s="52" t="s">
+        <v>112</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="C3" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="54"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="52" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="52" t="s">
-        <v>100</v>
+      <c r="D4" s="52" t="s">
+        <v>117</v>
       </c>
-      <c r="B3" s="52" t="s">
-        <v>110</v>
+      <c r="E4" s="54"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="52" t="s">
+        <v>115</v>
       </c>
-      <c r="C3" s="52" t="s">
-        <v>111</v>
+      <c r="B5" s="52" t="s">
+        <v>118</v>
       </c>
-      <c r="D3" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="54"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="52" t="s">
+      <c r="C5" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="54"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>111</v>
-      </c>
       <c r="D5" s="52" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E5" s="54"/>
     </row>
@@ -46597,28 +46605,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="62" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E1" s="63" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F1" s="62" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G1" s="62" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H1" s="62" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I1" s="49" t="s">
         <v>84</v>
@@ -46643,10 +46651,10 @@
     </row>
     <row r="2">
       <c r="A2" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C2" s="64">
         <v>4.0</v>
@@ -46655,10 +46663,10 @@
         <v>3.0</v>
       </c>
       <c r="E2" s="65" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F2" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G2" s="64">
         <v>4.0</v>
@@ -46667,7 +46675,7 @@
         <v>1.0</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
